--- a/Docs/Demais/FRM-001_formulario_avaliacao_risco_aplicabilidade_controles_IA_v1.18.xlsx
+++ b/Docs/Demais/FRM-001_formulario_avaliacao_risco_aplicabilidade_controles_IA_v1.18.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucoes" sheetId="1" r:id="R11b00cdb39d44ac0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulario" sheetId="2" r:id="R17ad40c3c7d14bfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opcoes_Definicoes" sheetId="3" r:id="R791153667d95470f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="4" r:id="Re4012d77c80f40b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucoes" sheetId="1" r:id="Rc752fc91a9fc442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulario" sheetId="2" r:id="Rd4bae0c273c04a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opcoes_Definicoes" sheetId="3" r:id="Rf3905ff3bca74179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="4" r:id="R5fce739cc0c74a51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +41,19 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF17212B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17212B"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,6 +85,31 @@
         <x:fgColor rgb="FFFFFBEA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF28465C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF0F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF182939"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF0F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF28465C"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -82,7 +118,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="58">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -183,6 +219,46 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -190,14 +266,14 @@
   <x:dxfs count="2">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -360,10 +436,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>FRM-004 — Formulário de Avaliação de Risco e Aplicabilidade de Controles de IA</x:v>
-      </x:c>
-      <x:c r="B1" s="5" t="str"/>
+      <x:c r="A1" s="53" t="str">
+        <x:v>FRM-001 — Formulário de Avaliação de Risco e Aplicabilidade de Controles de Inteligência Artificial</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20" t="str">
@@ -378,7 +454,7 @@
         <x:v>Código</x:v>
       </x:c>
       <x:c r="B3" s="22" t="str">
-        <x:v>FRM-004</x:v>
+        <x:v>FRM-001</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -418,7 +494,7 @@
         <x:v>Fonte</x:v>
       </x:c>
       <x:c r="B8" s="22" t="str">
-        <x:v>FRM-004 — Formulário Web de Avaliação de Risco e Controles de IA v1.18</x:v>
+        <x:v>Documento autossuficiente FRM-001 — Formulário de Avaliação de Risco e Aplicabilidade de Controles de Inteligência Artificial v1.18</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -446,14 +522,18 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="22" t="str"/>
-      <x:c r="B12" s="22" t="str"/>
+      <x:c r="A12" s="55" t="str">
+        <x:v>Autossuficiência</x:v>
+      </x:c>
+      <x:c r="B12" s="55" t="str">
+        <x:v>O FRM-001 reúne intake, caracterização do cenário, classificação de risco e entradas para seleção de controles. Nenhum outro formulário é pré-requisito para o preenchimento.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="23" t="str">
+      <x:c r="A13" s="57" t="str">
         <x:v>Instruções de preenchimento</x:v>
       </x:c>
-      <x:c r="B13" s="23" t="str"/>
+      <x:c r="B13" s="57" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="22" t="str">
@@ -512,21 +592,20 @@
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="22" t="str"/>
-      <x:c r="B21" s="22" t="str"/>
+      <x:c r="A21" s="22"/>
+      <x:c r="B21" s="22"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="23" t="str">
         <x:v>Progresso</x:v>
       </x:c>
-      <x:c r="B22" s="23" t="str"/>
+      <x:c r="B22" s="23"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="22" t="str">
         <x:v>Perguntas respondidas</x:v>
       </x:c>
       <x:c r="B23" s="22" t="n">
-        <x:f>COUNTA(Formulario!H2:H120)</x:f>
         <x:v>119</x:v>
       </x:c>
     </x:row>
@@ -535,11 +614,13 @@
         <x:v>Percentual preenchido</x:v>
       </x:c>
       <x:c r="B24" s="28" t="n">
-        <x:f>IFERROR(B23/B7,0)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:B1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -622,8 +703,8 @@
       <x:c r="G2" s="40" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H2" s="42" t="str"/>
-      <x:c r="I2" s="42" t="str"/>
+      <x:c r="H2" s="42"/>
+      <x:c r="I2" s="42"/>
       <x:c r="J2" s="40" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -631,9 +712,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L2" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -658,8 +738,8 @@
       <x:c r="G3" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H3" s="42" t="str"/>
-      <x:c r="I3" s="42" t="str"/>
+      <x:c r="H3" s="42"/>
+      <x:c r="I3" s="42"/>
       <x:c r="J3" s="38" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -667,9 +747,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L3" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -694,8 +773,8 @@
       <x:c r="G4" s="40" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H4" s="42" t="str"/>
-      <x:c r="I4" s="42" t="str"/>
+      <x:c r="H4" s="42"/>
+      <x:c r="I4" s="42"/>
       <x:c r="J4" s="40" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -703,9 +782,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L4" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -730,8 +808,8 @@
       <x:c r="G5" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H5" s="42" t="str"/>
-      <x:c r="I5" s="42" t="str"/>
+      <x:c r="H5" s="42"/>
+      <x:c r="I5" s="42"/>
       <x:c r="J5" s="38" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -739,9 +817,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L5" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -766,8 +843,8 @@
       <x:c r="G6" s="40" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H6" s="42" t="str"/>
-      <x:c r="I6" s="42" t="str"/>
+      <x:c r="H6" s="42"/>
+      <x:c r="I6" s="42"/>
       <x:c r="J6" s="40" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -775,9 +852,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L6" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -802,8 +878,8 @@
       <x:c r="G7" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H7" s="42" t="str"/>
-      <x:c r="I7" s="42" t="str"/>
+      <x:c r="H7" s="42"/>
+      <x:c r="I7" s="42"/>
       <x:c r="J7" s="38" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -811,9 +887,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L7" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -838,8 +913,8 @@
       <x:c r="G8" s="40" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H8" s="42" t="str"/>
-      <x:c r="I8" s="42" t="str"/>
+      <x:c r="H8" s="42"/>
+      <x:c r="I8" s="42"/>
       <x:c r="J8" s="40" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -847,9 +922,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L8" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -880,8 +954,8 @@
 • Solução existente
 • Renovação ou reavaliação</x:v>
       </x:c>
-      <x:c r="H9" s="42" t="str"/>
-      <x:c r="I9" s="42" t="str"/>
+      <x:c r="H9" s="42"/>
+      <x:c r="I9" s="42"/>
       <x:c r="J9" s="38" t="str">
         <x:v>A fase atual pode ativar requisitos operacionais. Homologação, produção, solução existente e revalidação tornam o BAS-006 aplicável e elevam a dimensão Operação e continuidade para, no mínimo, I2.</x:v>
       </x:c>
@@ -889,9 +963,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L9" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -920,8 +993,8 @@
 • Produção
 • Computador, dispositivo ou endpoint local</x:v>
       </x:c>
-      <x:c r="H10" s="42" t="str"/>
-      <x:c r="I10" s="42" t="str"/>
+      <x:c r="H10" s="42"/>
+      <x:c r="I10" s="42"/>
       <x:c r="J10" s="40" t="str">
         <x:v>Os ambientes selecionados definem controles de segregação, promoção e implantação. Homologação ou produção ativam o BAS-006; mais de um ambiente ativa controles específicos de isolamento.</x:v>
       </x:c>
@@ -929,9 +1002,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L10" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -956,8 +1028,8 @@
       <x:c r="G11" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H11" s="42" t="str"/>
-      <x:c r="I11" s="42" t="str"/>
+      <x:c r="H11" s="42"/>
+      <x:c r="I11" s="42"/>
       <x:c r="J11" s="38" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -965,9 +1037,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L11" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -992,8 +1063,8 @@
       <x:c r="G12" s="40" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H12" s="42" t="str"/>
-      <x:c r="I12" s="42" t="str"/>
+      <x:c r="H12" s="42"/>
+      <x:c r="I12" s="42"/>
       <x:c r="J12" s="40" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -1001,9 +1072,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L12" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1033,8 +1103,8 @@
 • Exceção
 • Revalidação periódica</x:v>
       </x:c>
-      <x:c r="H13" s="42" t="str"/>
-      <x:c r="I13" s="42" t="str"/>
+      <x:c r="H13" s="42"/>
+      <x:c r="I13" s="42"/>
       <x:c r="J13" s="38" t="str">
         <x:v>É utilizado para identificação, rastreabilidade, agenda da avaliação e composição do Parecer de Segurança. Não altera diretamente o nível de risco, salvo quando indicado especificamente.</x:v>
       </x:c>
@@ -1042,9 +1112,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="L13" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1080,8 +1149,8 @@
 • IA embutida em equipamento — ex.: câmera, appliance de segurança, terminal, sensor ou dispositivo
 • O fornecedor usa IA nos bastidores para entregar o serviço, mesmo que a organização não acesse a IA diretamente</x:v>
       </x:c>
-      <x:c r="H14" s="42" t="str"/>
-      <x:c r="I14" s="42" t="str"/>
+      <x:c r="H14" s="42"/>
+      <x:c r="I14" s="42"/>
       <x:c r="J14" s="40" t="str">
         <x:v>É a pergunta principal de roteamento. As opções escolhidas exibem ou ocultam os blocos condicionais e selecionam cumulativamente BAS-002, BAS-003, BAS-004 e BAS-005. BAS-001 permanece sempre aplicável.</x:v>
       </x:c>
@@ -1089,9 +1158,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L14" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1118,8 +1186,8 @@
 • Opcional — a solução continua funcionando sem a IA
 • Ainda não sabemos; será necessária confirmação</x:v>
       </x:c>
-      <x:c r="H15" s="42" t="str"/>
-      <x:c r="I15" s="42" t="str"/>
+      <x:c r="H15" s="42"/>
+      <x:c r="I15" s="42"/>
       <x:c r="J15" s="38" t="str">
         <x:v>Registra se a IA é central ou acessória. Atualmente não altera diretamente a pontuação, mas compõe o contexto, o Parecer de Segurança e a decisão de dependência tecnológica.</x:v>
       </x:c>
@@ -1127,9 +1195,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L15" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1157,8 +1224,8 @@
 • Compartilhado — organização e fornecedor atuam juntos
 • Ainda não sabemos quem é responsável</x:v>
       </x:c>
-      <x:c r="H16" s="42" t="str"/>
-      <x:c r="I16" s="42" t="str"/>
+      <x:c r="H16" s="42"/>
+      <x:c r="I16" s="42"/>
       <x:c r="J16" s="40" t="str">
         <x:v>Define quem deverá implementar e comprovar os controles. Afeta a atribuição Organização, Fornecedor ou Compartilhada, sem reduzir risco por si só.</x:v>
       </x:c>
@@ -1166,9 +1233,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L16" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1196,8 +1262,8 @@
 • Compartilhado — parte interna e parte externa
 • Ainda não sabemos quem hospeda ou opera</x:v>
       </x:c>
-      <x:c r="H17" s="42" t="str"/>
-      <x:c r="I17" s="42" t="str"/>
+      <x:c r="H17" s="42"/>
+      <x:c r="I17" s="42"/>
       <x:c r="J17" s="38" t="str">
         <x:v>Define quem opera e hospeda a solução. Afeta responsabilidade, evidências esperadas e tratamento de terceiros.</x:v>
       </x:c>
@@ -1205,9 +1271,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L17" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1232,8 +1297,8 @@
       <x:c r="G18" s="40" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H18" s="42" t="str"/>
-      <x:c r="I18" s="42" t="str"/>
+      <x:c r="H18" s="42"/>
+      <x:c r="I18" s="42"/>
       <x:c r="J18" s="40" t="str">
         <x:v>Identifica provider, modelo, versão, região e deployment. Em cenário externo, deixar esta informação em branco gera piso mínimo P3 por falta de identificação/homologação demonstrada.</x:v>
       </x:c>
@@ -1241,9 +1306,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L18" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1270,8 +1334,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H19" s="42" t="str"/>
-      <x:c r="I19" s="42" t="str"/>
+      <x:c r="H19" s="42"/>
+      <x:c r="I19" s="42"/>
       <x:c r="J19" s="38" t="str">
         <x:v>Em solução de terceiro, resposta diferente de “Sim” gera piso mínimo P3, pois a funcionalidade de IA não está comprovadamente sob controle ou não pode ser desativada.</x:v>
       </x:c>
@@ -1279,9 +1343,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L19" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1308,8 +1371,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H20" s="42" t="str"/>
-      <x:c r="I20" s="42" t="str"/>
+      <x:c r="H20" s="42"/>
+      <x:c r="I20" s="42"/>
       <x:c r="J20" s="40" t="str">
         <x:v>“Sim” ou “Não sei” ativa fator de probabilidade por modelo alterável, lacuna de terceiro e piso mínimo P3.</x:v>
       </x:c>
@@ -1317,9 +1380,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L20" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1346,8 +1408,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H21" s="42" t="str"/>
-      <x:c r="I21" s="42" t="str"/>
+      <x:c r="H21" s="42"/>
+      <x:c r="I21" s="42"/>
       <x:c r="J21" s="38" t="str">
         <x:v>Ajuda a caracterizar o cenário, definir responsabilidades e selecionar perguntas, baselines e controles aplicáveis.</x:v>
       </x:c>
@@ -1355,9 +1417,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L21" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1384,8 +1445,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H22" s="42" t="str"/>
-      <x:c r="I22" s="42" t="str"/>
+      <x:c r="H22" s="42"/>
+      <x:c r="I22" s="42"/>
       <x:c r="J22" s="40" t="str">
         <x:v>“Sim” pode ativar BAS-005, controles de modelo local, artefatos, sandbox e cadeia de suprimentos.</x:v>
       </x:c>
@@ -1393,9 +1454,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L22" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1422,8 +1482,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H23" s="42" t="str"/>
-      <x:c r="I23" s="42" t="str"/>
+      <x:c r="H23" s="42"/>
+      <x:c r="I23" s="42"/>
       <x:c r="J23" s="38" t="str">
         <x:v>“Sim” ativa controles de datasets, treinamento, fine-tuning, avaliação e MLOps do BAS-005.</x:v>
       </x:c>
@@ -1431,9 +1491,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="L23" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1460,8 +1519,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H24" s="42" t="str"/>
-      <x:c r="I24" s="42" t="str"/>
+      <x:c r="H24" s="42"/>
+      <x:c r="I24" s="42"/>
       <x:c r="J24" s="40" t="str">
         <x:v>Quando houver dados protegidos, “Sim” ou “Não sei” pode gerar piso P3 pelo possível uso dos dados para treinamento do fornecedor.</x:v>
       </x:c>
@@ -1469,9 +1528,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L24" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1496,8 +1554,8 @@
       <x:c r="G25" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H25" s="42" t="str"/>
-      <x:c r="I25" s="42" t="str"/>
+      <x:c r="H25" s="42"/>
+      <x:c r="I25" s="42"/>
       <x:c r="J25" s="38" t="str">
         <x:v>A ausência de informação sobre retenção, combinada com localização não comprovada, gera piso P3.</x:v>
       </x:c>
@@ -1505,9 +1563,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L25" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1534,8 +1591,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H26" s="42" t="str"/>
-      <x:c r="I26" s="42" t="str"/>
+      <x:c r="H26" s="42"/>
+      <x:c r="I26" s="42"/>
       <x:c r="J26" s="40" t="str">
         <x:v>Resposta diferente de “Sim” contribui para lacuna de terceiro e piso P3 por localização/processamento não comprovados.</x:v>
       </x:c>
@@ -1543,9 +1600,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L26" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1572,8 +1628,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H27" s="42" t="str"/>
-      <x:c r="I27" s="42" t="str"/>
+      <x:c r="H27" s="42"/>
+      <x:c r="I27" s="42"/>
       <x:c r="J27" s="38" t="str">
         <x:v>Resposta diferente de “Sim” contribui para lacuna de fornecedor e pode gerar condição bloqueante quando há dados sensíveis e ambiente compartilhado.</x:v>
       </x:c>
@@ -1581,9 +1637,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L27" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1610,8 +1665,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H28" s="42" t="str"/>
-      <x:c r="I28" s="42" t="str"/>
+      <x:c r="H28" s="42"/>
+      <x:c r="I28" s="42"/>
       <x:c r="J28" s="40" t="str">
         <x:v>Avalia transparência e responsabilidade do fornecedor. Respostas negativas, desconhecidas ou sem evidência não reduzem risco e podem aumentar a probabilidade ou exigir revisão técnica.</x:v>
       </x:c>
@@ -1619,9 +1674,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L28" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1648,8 +1702,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H29" s="42" t="str"/>
-      <x:c r="I29" s="42" t="str"/>
+      <x:c r="H29" s="42"/>
+      <x:c r="I29" s="42"/>
       <x:c r="J29" s="38" t="str">
         <x:v>Avalia transparência e responsabilidade do fornecedor. Respostas negativas, desconhecidas ou sem evidência não reduzem risco e podem aumentar a probabilidade ou exigir revisão técnica.</x:v>
       </x:c>
@@ -1657,9 +1711,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L29" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,8 +1739,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H30" s="42" t="str"/>
-      <x:c r="I30" s="42" t="str"/>
+      <x:c r="H30" s="42"/>
+      <x:c r="I30" s="42"/>
       <x:c r="J30" s="40" t="str">
         <x:v>Resposta diferente de “Sim” gera piso P3 por ausência de evidência mínima de segurança do fornecedor.</x:v>
       </x:c>
@@ -1695,9 +1748,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L30" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1724,8 +1776,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H31" s="42" t="str"/>
-      <x:c r="I31" s="42" t="str"/>
+      <x:c r="H31" s="42"/>
+      <x:c r="I31" s="42"/>
       <x:c r="J31" s="38" t="str">
         <x:v>Avalia transparência e responsabilidade do fornecedor. Respostas negativas, desconhecidas ou sem evidência não reduzem risco e podem aumentar a probabilidade ou exigir revisão técnica.</x:v>
       </x:c>
@@ -1733,9 +1785,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L31" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1762,8 +1813,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H32" s="42" t="str"/>
-      <x:c r="I32" s="42" t="str"/>
+      <x:c r="H32" s="42"/>
+      <x:c r="I32" s="42"/>
       <x:c r="J32" s="40" t="str">
         <x:v>Avalia transparência e responsabilidade do fornecedor. Respostas negativas, desconhecidas ou sem evidência não reduzem risco e podem aumentar a probabilidade ou exigir revisão técnica.</x:v>
       </x:c>
@@ -1771,9 +1822,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L32" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1800,8 +1850,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H33" s="42" t="str"/>
-      <x:c r="I33" s="42" t="str"/>
+      <x:c r="H33" s="42"/>
+      <x:c r="I33" s="42"/>
       <x:c r="J33" s="38" t="str">
         <x:v>“Não” ou “Não sei” aumenta a lacuna de terceiro. Para componente crítico, ausência de continuidade/fallback pode gerar piso P3.</x:v>
       </x:c>
@@ -1809,9 +1859,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L33" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1838,8 +1887,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H34" s="42" t="str"/>
-      <x:c r="I34" s="42" t="str"/>
+      <x:c r="H34" s="42"/>
+      <x:c r="I34" s="42"/>
       <x:c r="J34" s="40" t="str">
         <x:v>“Não” ou “Não sei” aumenta dependência de fornecedor e pode gerar piso P3 para componente crítico sem plano de saída.</x:v>
       </x:c>
@@ -1847,9 +1896,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L34" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1876,8 +1924,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H35" s="42" t="str"/>
-      <x:c r="I35" s="42" t="str"/>
+      <x:c r="H35" s="42"/>
+      <x:c r="I35" s="42"/>
       <x:c r="J35" s="38" t="str">
         <x:v>Resposta diferente de “Sim” aumenta a incerteza de responsabilidade e, junto com ausência de evidências, pode tornar a avaliação inconclusiva ou bloqueante.</x:v>
       </x:c>
@@ -1885,9 +1933,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L35" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1914,8 +1961,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H36" s="42" t="str"/>
-      <x:c r="I36" s="42" t="str"/>
+      <x:c r="H36" s="42"/>
+      <x:c r="I36" s="42"/>
       <x:c r="J36" s="40" t="str">
         <x:v>Avalia transparência e responsabilidade do fornecedor. Respostas negativas, desconhecidas ou sem evidência não reduzem risco e podem aumentar a probabilidade ou exigir revisão técnica.</x:v>
       </x:c>
@@ -1923,9 +1970,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L36" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1950,8 +1996,8 @@
       <x:c r="G37" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H37" s="42" t="str"/>
-      <x:c r="I37" s="42" t="str"/>
+      <x:c r="H37" s="42"/>
+      <x:c r="I37" s="42"/>
       <x:c r="J37" s="38" t="str">
         <x:v>Qualquer limitação registrada é considerada lacuna de transparência do fornecedor e participa do fator F5 de probabilidade.</x:v>
       </x:c>
@@ -1959,9 +2005,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="L37" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1993,8 +2038,8 @@
 • Dados regulados ou protegidos por sigilo — ex.: segredo bancário, fiscal, judicial, investigação ou informação classificada como restrita
 • Não sei informar — selecione esta opção quando precisar de apoio para identificar os dados</x:v>
       </x:c>
-      <x:c r="H38" s="42" t="str"/>
-      <x:c r="I38" s="42" t="str"/>
+      <x:c r="H38" s="42"/>
+      <x:c r="I38" s="42"/>
       <x:c r="J38" s="40" t="str">
         <x:v>Define a dimensão Dados e privacidade: dados públicos → I1; dados corporativos internos → I2; dados pessoais, sensíveis ou regulados → pelo menos I3; dados bancários, credenciais, segredos ou “Não sei” → I4. Também seleciona controles específicos de proteção de dados.</x:v>
       </x:c>
@@ -2002,9 +2047,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L38" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2029,8 +2073,8 @@
       <x:c r="G39" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H39" s="42" t="str"/>
-      <x:c r="I39" s="42" t="str"/>
+      <x:c r="H39" s="42"/>
+      <x:c r="I39" s="42"/>
       <x:c r="J39" s="38" t="str">
         <x:v>É usado para contextualizar a avaliação, selecionar evidências e produzir o Parecer de Segurança. Não altera a pontuação diretamente.</x:v>
       </x:c>
@@ -2038,9 +2082,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L39" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2067,8 +2110,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H40" s="42" t="str"/>
-      <x:c r="I40" s="42" t="str"/>
+      <x:c r="H40" s="42"/>
+      <x:c r="I40" s="42"/>
       <x:c r="J40" s="40" t="str">
         <x:v>Caracteriza dados e privacidade. Pode alterar impacto, selecionar controles de proteção, retenção, inspeção e exclusão.</x:v>
       </x:c>
@@ -2076,9 +2119,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L40" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2105,8 +2147,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H41" s="42" t="str"/>
-      <x:c r="I41" s="42" t="str"/>
+      <x:c r="H41" s="42"/>
+      <x:c r="I41" s="42"/>
       <x:c r="J41" s="38" t="str">
         <x:v>Caracteriza dados e privacidade. Pode alterar impacto, selecionar controles de proteção, retenção, inspeção e exclusão.</x:v>
       </x:c>
@@ -2114,9 +2156,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L41" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2143,8 +2184,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H42" s="42" t="str"/>
-      <x:c r="I42" s="42" t="str"/>
+      <x:c r="H42" s="42"/>
+      <x:c r="I42" s="42"/>
       <x:c r="J42" s="40" t="str">
         <x:v>Caracteriza dados e privacidade. Pode alterar impacto, selecionar controles de proteção, retenção, inspeção e exclusão.</x:v>
       </x:c>
@@ -2152,9 +2193,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L42" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2181,8 +2221,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H43" s="42" t="str"/>
-      <x:c r="I43" s="42" t="str"/>
+      <x:c r="H43" s="42"/>
+      <x:c r="I43" s="42"/>
       <x:c r="J43" s="38" t="str">
         <x:v>Caracteriza dados e privacidade. Pode alterar impacto, selecionar controles de proteção, retenção, inspeção e exclusão.</x:v>
       </x:c>
@@ -2190,9 +2230,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L43" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2219,8 +2258,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H44" s="42" t="str"/>
-      <x:c r="I44" s="42" t="str"/>
+      <x:c r="H44" s="42"/>
+      <x:c r="I44" s="42"/>
       <x:c r="J44" s="40" t="str">
         <x:v>Caracteriza dados e privacidade. Pode alterar impacto, selecionar controles de proteção, retenção, inspeção e exclusão.</x:v>
       </x:c>
@@ -2228,9 +2267,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L44" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2257,8 +2295,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H45" s="42" t="str"/>
-      <x:c r="I45" s="42" t="str"/>
+      <x:c r="H45" s="42"/>
+      <x:c r="I45" s="42"/>
       <x:c r="J45" s="38" t="str">
         <x:v>Caracteriza dados e privacidade. Pode alterar impacto, selecionar controles de proteção, retenção, inspeção e exclusão.</x:v>
       </x:c>
@@ -2266,9 +2304,8 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="L45" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2298,8 +2335,8 @@
 • Público geral
 • Outros sistemas ou processos automáticos</x:v>
       </x:c>
-      <x:c r="H46" s="42" t="str"/>
-      <x:c r="I46" s="42" t="str"/>
+      <x:c r="H46" s="42"/>
+      <x:c r="I46" s="42"/>
       <x:c r="J46" s="40" t="str">
         <x:v>Clientes ou público geral elevam o rigor para H4; clientes podem elevar impacto de negócio para I3; parceiros, clientes ou público ativam o fator F2 de probabilidade.</x:v>
       </x:c>
@@ -2307,9 +2344,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L46" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -2336,8 +2372,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H47" s="42" t="str"/>
-      <x:c r="I47" s="42" t="str"/>
+      <x:c r="H47" s="42"/>
+      <x:c r="I47" s="42"/>
       <x:c r="J47" s="38" t="str">
         <x:v>“Sim” eleva o rigor para H4, ativa F1 e F2, estabelece piso P3 e seleciona controles de exposição externa e gateway.</x:v>
       </x:c>
@@ -2345,9 +2381,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L47" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2374,8 +2409,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H48" s="42" t="str"/>
-      <x:c r="I48" s="42" t="str"/>
+      <x:c r="H48" s="42"/>
+      <x:c r="I48" s="42"/>
       <x:c r="J48" s="40" t="str">
         <x:v>“Sim” eleva o impacto de cliente/regulatório e seleciona controles de validação e proteção de saída.</x:v>
       </x:c>
@@ -2383,9 +2418,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L48" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -2412,8 +2446,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H49" s="42" t="str"/>
-      <x:c r="I49" s="42" t="str"/>
+      <x:c r="H49" s="42"/>
+      <x:c r="I49" s="42"/>
       <x:c r="J49" s="38" t="str">
         <x:v>“Sim” eleva o rigor para H4, impacto de cliente e segurança para pelo menos I3, ativa F4 e perguntas de revisão/contestação.</x:v>
       </x:c>
@@ -2421,9 +2455,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L49" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2450,8 +2483,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H50" s="42" t="str"/>
-      <x:c r="I50" s="42" t="str"/>
+      <x:c r="H50" s="42"/>
+      <x:c r="I50" s="42"/>
       <x:c r="J50" s="40" t="str">
         <x:v>“Sim” eleva o rigor para H4, impacto de cliente/financeiro para I4 e ativa F4. Sem fallback adequado pode gerar piso P3.</x:v>
       </x:c>
@@ -2459,9 +2492,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L50" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2488,8 +2520,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H51" s="42" t="str"/>
-      <x:c r="I51" s="42" t="str"/>
+      <x:c r="H51" s="42"/>
+      <x:c r="I51" s="42"/>
       <x:c r="J51" s="38" t="str">
         <x:v>“Sim” eleva o rigor para H4, impacto de cliente e operação para I4 e amplia requisitos de continuidade, telemetria e contenção.</x:v>
       </x:c>
@@ -2497,9 +2529,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L51" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -2526,8 +2557,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H52" s="42" t="str"/>
-      <x:c r="I52" s="42" t="str"/>
+      <x:c r="H52" s="42"/>
+      <x:c r="I52" s="42"/>
       <x:c r="J52" s="40" t="str">
         <x:v>“Sim” pode elevar impacto de cliente e operação para I3 e ativa F2 por escala.</x:v>
       </x:c>
@@ -2535,9 +2566,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L52" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2564,8 +2594,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H53" s="42" t="str"/>
-      <x:c r="I53" s="42" t="str"/>
+      <x:c r="H53" s="42"/>
+      <x:c r="I53" s="42"/>
       <x:c r="J53" s="38" t="str">
         <x:v>Caracteriza usuários, exposição e consequências. Pode alterar H1–H4, impacto e probabilidade.</x:v>
       </x:c>
@@ -2573,9 +2603,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L53" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2602,8 +2631,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H54" s="42" t="str"/>
-      <x:c r="I54" s="42" t="str"/>
+      <x:c r="H54" s="42"/>
+      <x:c r="I54" s="42"/>
       <x:c r="J54" s="40" t="str">
         <x:v>Caracteriza usuários, exposição e consequências. Pode alterar H1–H4, impacto e probabilidade.</x:v>
       </x:c>
@@ -2611,9 +2640,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L54" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2640,8 +2668,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H55" s="42" t="str"/>
-      <x:c r="I55" s="42" t="str"/>
+      <x:c r="H55" s="42"/>
+      <x:c r="I55" s="42"/>
       <x:c r="J55" s="38" t="str">
         <x:v>Caracteriza usuários, exposição e consequências. Pode alterar H1–H4, impacto e probabilidade.</x:v>
       </x:c>
@@ -2649,9 +2677,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L55" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -2678,8 +2705,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H56" s="42" t="str"/>
-      <x:c r="I56" s="42" t="str"/>
+      <x:c r="H56" s="42"/>
+      <x:c r="I56" s="42"/>
       <x:c r="J56" s="40" t="str">
         <x:v>Caracteriza usuários, exposição e consequências. Pode alterar H1–H4, impacto e probabilidade.</x:v>
       </x:c>
@@ -2687,9 +2714,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L56" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -2714,8 +2740,8 @@
       <x:c r="G57" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H57" s="42" t="str"/>
-      <x:c r="I57" s="42" t="str"/>
+      <x:c r="H57" s="42"/>
+      <x:c r="I57" s="42"/>
       <x:c r="J57" s="38" t="str">
         <x:v>Caracteriza usuários, exposição e consequências. Pode alterar H1–H4, impacto e probabilidade.</x:v>
       </x:c>
@@ -2723,9 +2749,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="L57" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -2752,8 +2777,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H58" s="42" t="str"/>
-      <x:c r="I58" s="42" t="str"/>
+      <x:c r="H58" s="42"/>
+      <x:c r="I58" s="42"/>
       <x:c r="J58" s="40" t="str">
         <x:v>Em exposição externa, resposta diferente de “Sim” pode gerar condição bloqueante por ausência de gateway ou ponto de enforcement.</x:v>
       </x:c>
@@ -2761,9 +2786,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L58" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -2792,8 +2816,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H59" s="42" t="str"/>
-      <x:c r="I59" s="42" t="str"/>
+      <x:c r="H59" s="42"/>
+      <x:c r="I59" s="42"/>
       <x:c r="J59" s="38" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -2801,9 +2825,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L59" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -2832,8 +2855,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H60" s="42" t="str"/>
-      <x:c r="I60" s="42" t="str"/>
+      <x:c r="H60" s="42"/>
+      <x:c r="I60" s="42"/>
       <x:c r="J60" s="40" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -2841,9 +2864,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L60" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -2872,8 +2894,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H61" s="42" t="str"/>
-      <x:c r="I61" s="42" t="str"/>
+      <x:c r="H61" s="42"/>
+      <x:c r="I61" s="42"/>
       <x:c r="J61" s="38" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -2881,9 +2903,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L61" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -2912,8 +2933,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H62" s="42" t="str"/>
-      <x:c r="I62" s="42" t="str"/>
+      <x:c r="H62" s="42"/>
+      <x:c r="I62" s="42"/>
       <x:c r="J62" s="40" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -2921,9 +2942,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L62" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -2952,8 +2972,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H63" s="42" t="str"/>
-      <x:c r="I63" s="42" t="str"/>
+      <x:c r="H63" s="42"/>
+      <x:c r="I63" s="42"/>
       <x:c r="J63" s="38" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -2961,9 +2981,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L63" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -2992,8 +3011,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H64" s="42" t="str"/>
-      <x:c r="I64" s="42" t="str"/>
+      <x:c r="H64" s="42"/>
+      <x:c r="I64" s="42"/>
       <x:c r="J64" s="40" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -3001,9 +3020,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L64" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3032,8 +3050,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H65" s="42" t="str"/>
-      <x:c r="I65" s="42" t="str"/>
+      <x:c r="H65" s="42"/>
+      <x:c r="I65" s="42"/>
       <x:c r="J65" s="38" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -3041,9 +3059,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L65" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3072,8 +3089,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H66" s="42" t="str"/>
-      <x:c r="I66" s="42" t="str"/>
+      <x:c r="H66" s="42"/>
+      <x:c r="I66" s="42"/>
       <x:c r="J66" s="40" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -3081,9 +3098,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L66" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3112,8 +3128,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H67" s="42" t="str"/>
-      <x:c r="I67" s="42" t="str"/>
+      <x:c r="H67" s="42"/>
+      <x:c r="I67" s="42"/>
       <x:c r="J67" s="38" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -3121,9 +3137,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L67" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3152,8 +3167,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H68" s="42" t="str"/>
-      <x:c r="I68" s="42" t="str"/>
+      <x:c r="H68" s="42"/>
+      <x:c r="I68" s="42"/>
       <x:c r="J68" s="40" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -3161,9 +3176,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L68" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3192,8 +3206,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H69" s="42" t="str"/>
-      <x:c r="I69" s="42" t="str"/>
+      <x:c r="H69" s="42"/>
+      <x:c r="I69" s="42"/>
       <x:c r="J69" s="38" t="str">
         <x:v>“Sim” ou “Não sei” eleva o rigor para H4, impacto Segurança e autonomia para I4 e ativa F4 por privilégio relevante.</x:v>
       </x:c>
@@ -3201,9 +3215,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L69" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3232,8 +3245,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H70" s="42" t="str"/>
-      <x:c r="I70" s="42" t="str"/>
+      <x:c r="H70" s="42"/>
+      <x:c r="I70" s="42"/>
       <x:c r="J70" s="40" t="str">
         <x:v>Determina aplicabilidade e evidência de controles de arquitetura, identidade, integração e acesso. Lacunas críticas podem bloquear a aprovação.</x:v>
       </x:c>
@@ -3241,9 +3254,8 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="L70" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
@@ -3272,8 +3284,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H71" s="42" t="str"/>
-      <x:c r="I71" s="42" t="str"/>
+      <x:c r="H71" s="42"/>
+      <x:c r="I71" s="42"/>
       <x:c r="J71" s="38" t="str">
         <x:v>“Sim” ou “Não sei” ativa o bloco RAG, BAS-003 e controles de fontes, ingestão, autorização, memória e recuperação.</x:v>
       </x:c>
@@ -3281,9 +3293,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L71" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3315,8 +3326,8 @@
 • Terceiros
 • Outras</x:v>
       </x:c>
-      <x:c r="H72" s="42" t="str"/>
-      <x:c r="I72" s="42" t="str"/>
+      <x:c r="H72" s="42"/>
+      <x:c r="I72" s="42"/>
       <x:c r="J72" s="40" t="str">
         <x:v>Internet, upload de usuário ou terceiros ativam F1. Internet também estabelece piso mínimo P3.</x:v>
       </x:c>
@@ -3324,9 +3335,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L72" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3354,8 +3364,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H73" s="42" t="str"/>
-      <x:c r="I73" s="42" t="str"/>
+      <x:c r="H73" s="42"/>
+      <x:c r="I73" s="42"/>
       <x:c r="J73" s="38" t="str">
         <x:v>“Sim” ativa F1 e piso P3 por conteúdo não confiável capaz de influenciar o RAG.</x:v>
       </x:c>
@@ -3363,9 +3373,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L73" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3393,8 +3402,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H74" s="42" t="str"/>
-      <x:c r="I74" s="42" t="str"/>
+      <x:c r="H74" s="42"/>
+      <x:c r="I74" s="42"/>
       <x:c r="J74" s="40" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3402,9 +3411,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L74" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3432,8 +3440,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H75" s="42" t="str"/>
-      <x:c r="I75" s="42" t="str"/>
+      <x:c r="H75" s="42"/>
+      <x:c r="I75" s="42"/>
       <x:c r="J75" s="38" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3441,9 +3449,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L75" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3471,8 +3478,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H76" s="42" t="str"/>
-      <x:c r="I76" s="42" t="str"/>
+      <x:c r="H76" s="42"/>
+      <x:c r="I76" s="42"/>
       <x:c r="J76" s="40" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3480,9 +3487,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L76" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3510,8 +3516,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H77" s="42" t="str"/>
-      <x:c r="I77" s="42" t="str"/>
+      <x:c r="H77" s="42"/>
+      <x:c r="I77" s="42"/>
       <x:c r="J77" s="38" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3519,9 +3525,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L77" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3549,8 +3554,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H78" s="42" t="str"/>
-      <x:c r="I78" s="42" t="str"/>
+      <x:c r="H78" s="42"/>
+      <x:c r="I78" s="42"/>
       <x:c r="J78" s="40" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3558,9 +3563,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L78" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3588,8 +3592,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H79" s="42" t="str"/>
-      <x:c r="I79" s="42" t="str"/>
+      <x:c r="H79" s="42"/>
+      <x:c r="I79" s="42"/>
       <x:c r="J79" s="38" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3597,9 +3601,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L79" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3627,8 +3630,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H80" s="42" t="str"/>
-      <x:c r="I80" s="42" t="str"/>
+      <x:c r="H80" s="42"/>
+      <x:c r="I80" s="42"/>
       <x:c r="J80" s="40" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3636,9 +3639,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L80" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3666,8 +3668,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H81" s="42" t="str"/>
-      <x:c r="I81" s="42" t="str"/>
+      <x:c r="H81" s="42"/>
+      <x:c r="I81" s="42"/>
       <x:c r="J81" s="38" t="str">
         <x:v>Determina controles de RAG, fontes, autorização, memória, integridade e recuperação. Algumas respostas também influenciam a probabilidade.</x:v>
       </x:c>
@@ -3675,9 +3677,8 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="L81" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
     </x:row>
@@ -3705,8 +3706,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H82" s="42" t="str"/>
-      <x:c r="I82" s="42" t="str"/>
+      <x:c r="H82" s="42"/>
+      <x:c r="I82" s="42"/>
       <x:c r="J82" s="40" t="str">
         <x:v>“Sim” ou “Não sei” ativa o bloco agentic e o BAS-004.</x:v>
       </x:c>
@@ -3714,9 +3715,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L82" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3744,8 +3744,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H83" s="42" t="str"/>
-      <x:c r="I83" s="42" t="str"/>
+      <x:c r="H83" s="42"/>
+      <x:c r="I83" s="42"/>
       <x:c r="J83" s="38" t="str">
         <x:v>“Sim” ou “Não sei” ativa somente os controles de clientes, servidores, registries, tools, resources e prompts MCP.</x:v>
       </x:c>
@@ -3753,9 +3753,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L83" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3783,8 +3782,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H84" s="42" t="str"/>
-      <x:c r="I84" s="42" t="str"/>
+      <x:c r="H84" s="42"/>
+      <x:c r="I84" s="42"/>
       <x:c r="J84" s="40" t="str">
         <x:v>“Sim” ou “Não sei” eleva H4, Segurança e autonomia para I4, ativa F4, piso P3 e controles de sandbox/computer use.</x:v>
       </x:c>
@@ -3792,9 +3791,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L84" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3820,8 +3818,8 @@
       <x:c r="G85" s="38" t="str">
         <x:v>Texto livre</x:v>
       </x:c>
-      <x:c r="H85" s="42" t="str"/>
-      <x:c r="I85" s="42" t="str"/>
+      <x:c r="H85" s="42"/>
+      <x:c r="I85" s="42"/>
       <x:c r="J85" s="38" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -3829,9 +3827,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L85" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3859,8 +3856,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H86" s="42" t="str"/>
-      <x:c r="I86" s="42" t="str"/>
+      <x:c r="H86" s="42"/>
+      <x:c r="I86" s="42"/>
       <x:c r="J86" s="40" t="str">
         <x:v>“Sim” ou “Não sei” eleva H4, Segurança e autonomia para I4, ativa F4, piso P3 e controles de autorização, confirmação, limites e contenção.</x:v>
       </x:c>
@@ -3868,9 +3865,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L86" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3898,8 +3894,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H87" s="42" t="str"/>
-      <x:c r="I87" s="42" t="str"/>
+      <x:c r="H87" s="42"/>
+      <x:c r="I87" s="42"/>
       <x:c r="J87" s="38" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -3907,9 +3903,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L87" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3937,8 +3932,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H88" s="42" t="str"/>
-      <x:c r="I88" s="42" t="str"/>
+      <x:c r="H88" s="42"/>
+      <x:c r="I88" s="42"/>
       <x:c r="J88" s="40" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -3946,9 +3941,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L88" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -3976,8 +3970,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H89" s="42" t="str"/>
-      <x:c r="I89" s="42" t="str"/>
+      <x:c r="H89" s="42"/>
+      <x:c r="I89" s="42"/>
       <x:c r="J89" s="38" t="str">
         <x:v>Para agente com ação material, resposta diferente de “Sim” gera condição bloqueante por ausência de autorização determinística.</x:v>
       </x:c>
@@ -3985,9 +3979,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L89" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4015,8 +4008,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H90" s="42" t="str"/>
-      <x:c r="I90" s="42" t="str"/>
+      <x:c r="H90" s="42"/>
+      <x:c r="I90" s="42"/>
       <x:c r="J90" s="40" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -4024,9 +4017,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L90" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4054,8 +4046,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H91" s="42" t="str"/>
-      <x:c r="I91" s="42" t="str"/>
+      <x:c r="H91" s="42"/>
+      <x:c r="I91" s="42"/>
       <x:c r="J91" s="38" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -4063,9 +4055,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L91" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4093,8 +4084,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H92" s="42" t="str"/>
-      <x:c r="I92" s="42" t="str"/>
+      <x:c r="H92" s="42"/>
+      <x:c r="I92" s="42"/>
       <x:c r="J92" s="40" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -4102,9 +4093,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L92" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4132,8 +4122,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H93" s="42" t="str"/>
-      <x:c r="I93" s="42" t="str"/>
+      <x:c r="H93" s="42"/>
+      <x:c r="I93" s="42"/>
       <x:c r="J93" s="38" t="str">
         <x:v>Para ação material ou processo crítico, a ausência de kill switch/contenção pode gerar condição bloqueante.</x:v>
       </x:c>
@@ -4141,9 +4131,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L93" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4171,8 +4160,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H94" s="42" t="str"/>
-      <x:c r="I94" s="42" t="str"/>
+      <x:c r="H94" s="42"/>
+      <x:c r="I94" s="42"/>
       <x:c r="J94" s="40" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -4180,9 +4169,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L94" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4210,8 +4198,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H95" s="42" t="str"/>
-      <x:c r="I95" s="42" t="str"/>
+      <x:c r="H95" s="42"/>
+      <x:c r="I95" s="42"/>
       <x:c r="J95" s="38" t="str">
         <x:v>Determina controles de agentes, tools, MCP, autonomia, autorização e contenção. Capacidades de ação podem elevar impacto e probabilidade.</x:v>
       </x:c>
@@ -4219,9 +4207,8 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="L95" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
     </x:row>
@@ -4249,8 +4236,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H96" s="42" t="str"/>
-      <x:c r="I96" s="42" t="str"/>
+      <x:c r="H96" s="42"/>
+      <x:c r="I96" s="42"/>
       <x:c r="J96" s="40" t="str">
         <x:v>“Sim” ou “Não sei” ativa o BAS-005 e as perguntas de desenvolvimento, artefatos, pipeline e release.</x:v>
       </x:c>
@@ -4258,9 +4245,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L96" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4288,8 +4274,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H97" s="42" t="str"/>
-      <x:c r="I97" s="42" t="str"/>
+      <x:c r="H97" s="42"/>
+      <x:c r="I97" s="42"/>
       <x:c r="J97" s="38" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4297,9 +4283,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L97" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4327,8 +4312,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H98" s="42" t="str"/>
-      <x:c r="I98" s="42" t="str"/>
+      <x:c r="H98" s="42"/>
+      <x:c r="I98" s="42"/>
       <x:c r="J98" s="40" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4336,9 +4321,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L98" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4366,8 +4350,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H99" s="42" t="str"/>
-      <x:c r="I99" s="42" t="str"/>
+      <x:c r="H99" s="42"/>
+      <x:c r="I99" s="42"/>
       <x:c r="J99" s="38" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4375,9 +4359,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L99" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4405,8 +4388,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H100" s="42" t="str"/>
-      <x:c r="I100" s="42" t="str"/>
+      <x:c r="H100" s="42"/>
+      <x:c r="I100" s="42"/>
       <x:c r="J100" s="40" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4414,9 +4397,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L100" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4444,8 +4426,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H101" s="42" t="str"/>
-      <x:c r="I101" s="42" t="str"/>
+      <x:c r="H101" s="42"/>
+      <x:c r="I101" s="42"/>
       <x:c r="J101" s="38" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4453,9 +4435,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L101" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4483,8 +4464,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H102" s="42" t="str"/>
-      <x:c r="I102" s="42" t="str"/>
+      <x:c r="H102" s="42"/>
+      <x:c r="I102" s="42"/>
       <x:c r="J102" s="40" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4492,9 +4473,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L102" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4522,8 +4502,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H103" s="42" t="str"/>
-      <x:c r="I103" s="42" t="str"/>
+      <x:c r="H103" s="42"/>
+      <x:c r="I103" s="42"/>
       <x:c r="J103" s="38" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4531,9 +4511,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L103" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4561,8 +4540,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H104" s="42" t="str"/>
-      <x:c r="I104" s="42" t="str"/>
+      <x:c r="H104" s="42"/>
+      <x:c r="I104" s="42"/>
       <x:c r="J104" s="40" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4570,9 +4549,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L104" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4600,8 +4578,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H105" s="42" t="str"/>
-      <x:c r="I105" s="42" t="str"/>
+      <x:c r="H105" s="42"/>
+      <x:c r="I105" s="42"/>
       <x:c r="J105" s="38" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4609,9 +4587,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L105" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4639,8 +4616,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H106" s="42" t="str"/>
-      <x:c r="I106" s="42" t="str"/>
+      <x:c r="H106" s="42"/>
+      <x:c r="I106" s="42"/>
       <x:c r="J106" s="40" t="str">
         <x:v>Determina controles de desenvolvimento, artefatos, cadeia de suprimentos, MLOps, testes, deploy e rollback.</x:v>
       </x:c>
@@ -4648,9 +4625,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L106" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4678,8 +4654,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H107" s="42" t="str"/>
-      <x:c r="I107" s="42" t="str"/>
+      <x:c r="H107" s="42"/>
+      <x:c r="I107" s="42"/>
       <x:c r="J107" s="38" t="str">
         <x:v>“Sim” ativa F3 por mudança dinâmica e controles de detecção de drift e atualização técnica.</x:v>
       </x:c>
@@ -4687,9 +4663,8 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="L107" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
     </x:row>
@@ -4717,8 +4692,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H108" s="42" t="str"/>
-      <x:c r="I108" s="42" t="str"/>
+      <x:c r="H108" s="42"/>
+      <x:c r="I108" s="42"/>
       <x:c r="J108" s="40" t="str">
         <x:v>Em decisão sensível ou ação material, resposta diferente de “Sim” gera condição bloqueante por ausência de trilha auditável.</x:v>
       </x:c>
@@ -4726,9 +4701,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L108" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4756,8 +4730,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H109" s="42" t="str"/>
-      <x:c r="I109" s="42" t="str"/>
+      <x:c r="H109" s="42"/>
+      <x:c r="I109" s="42"/>
       <x:c r="J109" s="38" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4765,9 +4739,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L109" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4795,8 +4768,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H110" s="42" t="str"/>
-      <x:c r="I110" s="42" t="str"/>
+      <x:c r="H110" s="42"/>
+      <x:c r="I110" s="42"/>
       <x:c r="J110" s="40" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4804,9 +4777,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L110" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4834,8 +4806,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H111" s="42" t="str"/>
-      <x:c r="I111" s="42" t="str"/>
+      <x:c r="H111" s="42"/>
+      <x:c r="I111" s="42"/>
       <x:c r="J111" s="38" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4843,9 +4815,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L111" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4873,8 +4844,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H112" s="42" t="str"/>
-      <x:c r="I112" s="42" t="str"/>
+      <x:c r="H112" s="42"/>
+      <x:c r="I112" s="42"/>
       <x:c r="J112" s="40" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4882,9 +4853,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L112" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4912,8 +4882,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H113" s="42" t="str"/>
-      <x:c r="I113" s="42" t="str"/>
+      <x:c r="H113" s="42"/>
+      <x:c r="I113" s="42"/>
       <x:c r="J113" s="38" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4921,9 +4891,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L113" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4951,8 +4920,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H114" s="42" t="str"/>
-      <x:c r="I114" s="42" t="str"/>
+      <x:c r="H114" s="42"/>
+      <x:c r="I114" s="42"/>
       <x:c r="J114" s="40" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4960,9 +4929,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L114" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -4990,8 +4958,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H115" s="42" t="str"/>
-      <x:c r="I115" s="42" t="str"/>
+      <x:c r="H115" s="42"/>
+      <x:c r="I115" s="42"/>
       <x:c r="J115" s="38" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -4999,9 +4967,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L115" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -5029,8 +4996,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H116" s="42" t="str"/>
-      <x:c r="I116" s="42" t="str"/>
+      <x:c r="H116" s="42"/>
+      <x:c r="I116" s="42"/>
       <x:c r="J116" s="40" t="str">
         <x:v>Em agente ou processo crítico, resposta diferente de “Sim”, sem kill switch, pode gerar condição bloqueante.</x:v>
       </x:c>
@@ -5038,9 +5005,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L116" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -5068,8 +5034,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H117" s="42" t="str"/>
-      <x:c r="I117" s="42" t="str"/>
+      <x:c r="H117" s="42"/>
+      <x:c r="I117" s="42"/>
       <x:c r="J117" s="38" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -5077,9 +5043,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L117" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -5107,8 +5072,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H118" s="42" t="str"/>
-      <x:c r="I118" s="42" t="str"/>
+      <x:c r="H118" s="42"/>
+      <x:c r="I118" s="42"/>
       <x:c r="J118" s="40" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -5116,9 +5081,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L118" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -5146,8 +5110,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H119" s="42" t="str"/>
-      <x:c r="I119" s="42" t="str"/>
+      <x:c r="H119" s="42"/>
+      <x:c r="I119" s="42"/>
       <x:c r="J119" s="38" t="str">
         <x:v>Determina controles de telemetria, detecção, contenção, continuidade e recuperação. Lacunas críticas podem impedir a redução do risco residual.</x:v>
       </x:c>
@@ -5155,9 +5119,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L119" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -5185,8 +5148,8 @@
 • Não
 • Não sei</x:v>
       </x:c>
-      <x:c r="H120" s="42" t="str"/>
-      <x:c r="I120" s="42" t="str"/>
+      <x:c r="H120" s="42"/>
+      <x:c r="I120" s="42"/>
       <x:c r="J120" s="40" t="str">
         <x:v>Ativa controles de desativação técnica, remoção de rotas, credenciais e dados operacionais.</x:v>
       </x:c>
@@ -5194,9 +5157,8 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="L120" s="40" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
     </x:row>
@@ -5562,7 +5524,7 @@
       <x:c r="C2" s="38" t="str">
         <x:v>Como o projeto, produto, sistema ou serviço se chama?</x:v>
       </x:c>
-      <x:c r="D2" s="38" t="str"/>
+      <x:c r="D2" s="38"/>
       <x:c r="E2" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5586,7 +5548,7 @@
       <x:c r="C3" s="38" t="str">
         <x:v>Existe um número de solicitação, contrato, processo ou chamado relacionado?</x:v>
       </x:c>
-      <x:c r="D3" s="38" t="str"/>
+      <x:c r="D3" s="38"/>
       <x:c r="E3" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5610,7 +5572,7 @@
       <x:c r="C4" s="38" t="str">
         <x:v>Qual área está solicitando ou utilizando a solução?</x:v>
       </x:c>
-      <x:c r="D4" s="38" t="str"/>
+      <x:c r="D4" s="38"/>
       <x:c r="E4" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5634,7 +5596,7 @@
       <x:c r="C5" s="38" t="str">
         <x:v>Quem é o responsável de negócio?</x:v>
       </x:c>
-      <x:c r="D5" s="38" t="str"/>
+      <x:c r="D5" s="38"/>
       <x:c r="E5" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5658,7 +5620,7 @@
       <x:c r="C6" s="38" t="str">
         <x:v>Quem é o responsável técnico?</x:v>
       </x:c>
-      <x:c r="D6" s="38" t="str"/>
+      <x:c r="D6" s="38"/>
       <x:c r="E6" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5682,7 +5644,7 @@
       <x:c r="C7" s="38" t="str">
         <x:v>Qual é o fornecedor principal?</x:v>
       </x:c>
-      <x:c r="D7" s="38" t="str"/>
+      <x:c r="D7" s="38"/>
       <x:c r="E7" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5706,7 +5668,7 @@
       <x:c r="C8" s="38" t="str">
         <x:v>O que a solução fará e qual problema pretende resolver?</x:v>
       </x:c>
-      <x:c r="D8" s="38" t="str"/>
+      <x:c r="D8" s="38"/>
       <x:c r="E8" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -5730,7 +5692,7 @@
       <x:c r="C9" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D9" s="38" t="str"/>
+      <x:c r="D9" s="38"/>
       <x:c r="E9" s="38" t="str">
         <x:v>Ideação</x:v>
       </x:c>
@@ -5754,7 +5716,7 @@
       <x:c r="C10" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D10" s="38" t="str"/>
+      <x:c r="D10" s="38"/>
       <x:c r="E10" s="38" t="str">
         <x:v>Prova de conceito (PoC)</x:v>
       </x:c>
@@ -5778,7 +5740,7 @@
       <x:c r="C11" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D11" s="38" t="str"/>
+      <x:c r="D11" s="38"/>
       <x:c r="E11" s="38" t="str">
         <x:v>Desenvolvimento</x:v>
       </x:c>
@@ -5802,7 +5764,7 @@
       <x:c r="C12" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D12" s="38" t="str"/>
+      <x:c r="D12" s="38"/>
       <x:c r="E12" s="38" t="str">
         <x:v>Homologação / validação antes do uso</x:v>
       </x:c>
@@ -5826,7 +5788,7 @@
       <x:c r="C13" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D13" s="38" t="str"/>
+      <x:c r="D13" s="38"/>
       <x:c r="E13" s="38" t="str">
         <x:v>Produção</x:v>
       </x:c>
@@ -5850,7 +5812,7 @@
       <x:c r="C14" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D14" s="38" t="str"/>
+      <x:c r="D14" s="38"/>
       <x:c r="E14" s="38" t="str">
         <x:v>Solução existente</x:v>
       </x:c>
@@ -5874,7 +5836,7 @@
       <x:c r="C15" s="38" t="str">
         <x:v>Em qual fase a solução está agora?</x:v>
       </x:c>
-      <x:c r="D15" s="38" t="str"/>
+      <x:c r="D15" s="38"/>
       <x:c r="E15" s="38" t="str">
         <x:v>Renovação ou reavaliação</x:v>
       </x:c>
@@ -5898,7 +5860,7 @@
       <x:c r="C16" s="38" t="str">
         <x:v>Em quais ambientes a solução será utilizada?</x:v>
       </x:c>
-      <x:c r="D16" s="38" t="str"/>
+      <x:c r="D16" s="38"/>
       <x:c r="E16" s="38" t="str">
         <x:v>Desenvolvimento</x:v>
       </x:c>
@@ -5922,7 +5884,7 @@
       <x:c r="C17" s="38" t="str">
         <x:v>Em quais ambientes a solução será utilizada?</x:v>
       </x:c>
-      <x:c r="D17" s="38" t="str"/>
+      <x:c r="D17" s="38"/>
       <x:c r="E17" s="38" t="str">
         <x:v>Teste</x:v>
       </x:c>
@@ -5946,7 +5908,7 @@
       <x:c r="C18" s="38" t="str">
         <x:v>Em quais ambientes a solução será utilizada?</x:v>
       </x:c>
-      <x:c r="D18" s="38" t="str"/>
+      <x:c r="D18" s="38"/>
       <x:c r="E18" s="38" t="str">
         <x:v>Homologação</x:v>
       </x:c>
@@ -5970,7 +5932,7 @@
       <x:c r="C19" s="38" t="str">
         <x:v>Em quais ambientes a solução será utilizada?</x:v>
       </x:c>
-      <x:c r="D19" s="38" t="str"/>
+      <x:c r="D19" s="38"/>
       <x:c r="E19" s="38" t="str">
         <x:v>Produção</x:v>
       </x:c>
@@ -5994,7 +5956,7 @@
       <x:c r="C20" s="38" t="str">
         <x:v>Em quais ambientes a solução será utilizada?</x:v>
       </x:c>
-      <x:c r="D20" s="38" t="str"/>
+      <x:c r="D20" s="38"/>
       <x:c r="E20" s="38" t="str">
         <x:v>Computador, dispositivo ou endpoint local</x:v>
       </x:c>
@@ -6018,7 +5980,7 @@
       <x:c r="C21" s="38" t="str">
         <x:v>Qual é a data prevista para piloto, contratação, entrada em produção ou renovação?</x:v>
       </x:c>
-      <x:c r="D21" s="38" t="str"/>
+      <x:c r="D21" s="38"/>
       <x:c r="E21" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -6042,7 +6004,7 @@
       <x:c r="C22" s="38" t="str">
         <x:v>Onde estão o desenho da solução e os documentos técnicos?</x:v>
       </x:c>
-      <x:c r="D22" s="38" t="str"/>
+      <x:c r="D22" s="38"/>
       <x:c r="E22" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -6066,7 +6028,7 @@
       <x:c r="C23" s="38" t="str">
         <x:v>Por que esta avaliação está sendo realizada?</x:v>
       </x:c>
-      <x:c r="D23" s="38" t="str"/>
+      <x:c r="D23" s="38"/>
       <x:c r="E23" s="38" t="str">
         <x:v>Novo projeto</x:v>
       </x:c>
@@ -6090,7 +6052,7 @@
       <x:c r="C24" s="38" t="str">
         <x:v>Por que esta avaliação está sendo realizada?</x:v>
       </x:c>
-      <x:c r="D24" s="38" t="str"/>
+      <x:c r="D24" s="38"/>
       <x:c r="E24" s="38" t="str">
         <x:v>Mudança material</x:v>
       </x:c>
@@ -6114,7 +6076,7 @@
       <x:c r="C25" s="38" t="str">
         <x:v>Por que esta avaliação está sendo realizada?</x:v>
       </x:c>
-      <x:c r="D25" s="38" t="str"/>
+      <x:c r="D25" s="38"/>
       <x:c r="E25" s="38" t="str">
         <x:v>Renovação</x:v>
       </x:c>
@@ -6138,7 +6100,7 @@
       <x:c r="C26" s="38" t="str">
         <x:v>Por que esta avaliação está sendo realizada?</x:v>
       </x:c>
-      <x:c r="D26" s="38" t="str"/>
+      <x:c r="D26" s="38"/>
       <x:c r="E26" s="38" t="str">
         <x:v>Incidente/achado</x:v>
       </x:c>
@@ -6162,7 +6124,7 @@
       <x:c r="C27" s="38" t="str">
         <x:v>Por que esta avaliação está sendo realizada?</x:v>
       </x:c>
-      <x:c r="D27" s="38" t="str"/>
+      <x:c r="D27" s="38"/>
       <x:c r="E27" s="38" t="str">
         <x:v>Exceção</x:v>
       </x:c>
@@ -6186,7 +6148,7 @@
       <x:c r="C28" s="38" t="str">
         <x:v>Por que esta avaliação está sendo realizada?</x:v>
       </x:c>
-      <x:c r="D28" s="38" t="str"/>
+      <x:c r="D28" s="38"/>
       <x:c r="E28" s="38" t="str">
         <x:v>Revalidação periódica</x:v>
       </x:c>
@@ -6210,7 +6172,7 @@
       <x:c r="C29" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D29" s="38" t="str"/>
+      <x:c r="D29" s="38"/>
       <x:c r="E29" s="38" t="str">
         <x:v>Uso interno pela organização — ex.: assistente para colaboradores; combine com as opções abaixo quando houver SaaS, RAG, agente ou modelo local</x:v>
       </x:c>
@@ -6234,7 +6196,7 @@
       <x:c r="C30" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D30" s="38" t="str"/>
+      <x:c r="D30" s="38"/>
       <x:c r="E30" s="38" t="str">
         <x:v>Sistema da organização conectado a uma IA externa por API — ex.: aplicação que chama Azure OpenAI, OpenAI, Gemini ou serviço equivalente</x:v>
       </x:c>
@@ -6258,7 +6220,7 @@
       <x:c r="C31" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D31" s="38" t="str"/>
+      <x:c r="D31" s="38"/>
       <x:c r="E31" s="38" t="str">
         <x:v>Software contratado que já possui IA — ex.: plataforma de RH, CRM, ERP, ferramenta jurídica ou solução de segurança</x:v>
       </x:c>
@@ -6282,7 +6244,7 @@
       <x:c r="C32" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D32" s="38" t="str"/>
+      <x:c r="D32" s="38"/>
       <x:c r="E32" s="38" t="str">
         <x:v>Aplicação construída sob encomenda por fornecedor, consultoria ou fábrica de software</x:v>
       </x:c>
@@ -6306,7 +6268,7 @@
       <x:c r="C33" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D33" s="38" t="str"/>
+      <x:c r="D33" s="38"/>
       <x:c r="E33" s="38" t="str">
         <x:v>Fornecedor hospeda e opera a solução de IA para a organização</x:v>
       </x:c>
@@ -6330,7 +6292,7 @@
       <x:c r="C34" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D34" s="38" t="str"/>
+      <x:c r="D34" s="38"/>
       <x:c r="E34" s="38" t="str">
         <x:v>A organização desenvolve, configura ou publica a própria solução de IA</x:v>
       </x:c>
@@ -6354,7 +6316,7 @@
       <x:c r="C35" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D35" s="38" t="str"/>
+      <x:c r="D35" s="38"/>
       <x:c r="E35" s="38" t="str">
         <x:v>A IA consulta documentos ou bases para responder — ex.: SharePoint, normativos, manuais, vector store ou memória</x:v>
       </x:c>
@@ -6378,7 +6340,7 @@
       <x:c r="C36" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D36" s="38" t="str"/>
+      <x:c r="D36" s="38"/>
       <x:c r="E36" s="38" t="str">
         <x:v>A IA executa tarefas ou chama sistemas — ex.: criar chamado, consultar saldo, enviar mensagem ou alterar registro</x:v>
       </x:c>
@@ -6402,7 +6364,7 @@
       <x:c r="C37" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D37" s="38" t="str"/>
+      <x:c r="D37" s="38"/>
       <x:c r="E37" s="38" t="str">
         <x:v>Ferramenta instalada ou usada por pessoas — ex.: copiloto, extensão de navegador, IDE, editor ou plugin</x:v>
       </x:c>
@@ -6426,7 +6388,7 @@
       <x:c r="C38" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D38" s="38" t="str"/>
+      <x:c r="D38" s="38"/>
       <x:c r="E38" s="38" t="str">
         <x:v>Modelo executado em computador, servidor ou nuvem controlada pela organização — ex.: Ollama, Llama ou outro open source</x:v>
       </x:c>
@@ -6450,7 +6412,7 @@
       <x:c r="C39" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D39" s="38" t="str"/>
+      <x:c r="D39" s="38"/>
       <x:c r="E39" s="38" t="str">
         <x:v>IA embutida em equipamento — ex.: câmera, appliance de segurança, terminal, sensor ou dispositivo</x:v>
       </x:c>
@@ -6474,7 +6436,7 @@
       <x:c r="C40" s="38" t="str">
         <x:v>Selecione as opções que descrevem como a IA será usada e fornecida.</x:v>
       </x:c>
-      <x:c r="D40" s="38" t="str"/>
+      <x:c r="D40" s="38"/>
       <x:c r="E40" s="38" t="str">
         <x:v>O fornecedor usa IA nos bastidores para entregar o serviço, mesmo que a organização não acesse a IA diretamente</x:v>
       </x:c>
@@ -6498,7 +6460,7 @@
       <x:c r="C41" s="38" t="str">
         <x:v>A solução depende da IA para cumprir sua finalidade principal?</x:v>
       </x:c>
-      <x:c r="D41" s="38" t="str"/>
+      <x:c r="D41" s="38"/>
       <x:c r="E41" s="38" t="str">
         <x:v>Essencial — sem a IA a solução perde sua função principal</x:v>
       </x:c>
@@ -6522,7 +6484,7 @@
       <x:c r="C42" s="38" t="str">
         <x:v>A solução depende da IA para cumprir sua finalidade principal?</x:v>
       </x:c>
-      <x:c r="D42" s="38" t="str"/>
+      <x:c r="D42" s="38"/>
       <x:c r="E42" s="38" t="str">
         <x:v>Opcional — a solução continua funcionando sem a IA</x:v>
       </x:c>
@@ -6546,7 +6508,7 @@
       <x:c r="C43" s="38" t="str">
         <x:v>A solução depende da IA para cumprir sua finalidade principal?</x:v>
       </x:c>
-      <x:c r="D43" s="38" t="str"/>
+      <x:c r="D43" s="38"/>
       <x:c r="E43" s="38" t="str">
         <x:v>Ainda não sabemos; será necessária confirmação</x:v>
       </x:c>
@@ -6570,7 +6532,7 @@
       <x:c r="C44" s="38" t="str">
         <x:v>Quem cria, adapta ou configura a parte de IA?</x:v>
       </x:c>
-      <x:c r="D44" s="38" t="str"/>
+      <x:c r="D44" s="38"/>
       <x:c r="E44" s="38" t="str">
         <x:v>Organização — equipe interna cria ou configura a IA</x:v>
       </x:c>
@@ -6594,7 +6556,7 @@
       <x:c r="C45" s="38" t="str">
         <x:v>Quem cria, adapta ou configura a parte de IA?</x:v>
       </x:c>
-      <x:c r="D45" s="38" t="str"/>
+      <x:c r="D45" s="38"/>
       <x:c r="E45" s="38" t="str">
         <x:v>Fornecedor — empresa externa controla o desenvolvimento ou configuração</x:v>
       </x:c>
@@ -6618,7 +6580,7 @@
       <x:c r="C46" s="38" t="str">
         <x:v>Quem cria, adapta ou configura a parte de IA?</x:v>
       </x:c>
-      <x:c r="D46" s="38" t="str"/>
+      <x:c r="D46" s="38"/>
       <x:c r="E46" s="38" t="str">
         <x:v>Compartilhado — organização e fornecedor atuam juntos</x:v>
       </x:c>
@@ -6642,7 +6604,7 @@
       <x:c r="C47" s="38" t="str">
         <x:v>Quem cria, adapta ou configura a parte de IA?</x:v>
       </x:c>
-      <x:c r="D47" s="38" t="str"/>
+      <x:c r="D47" s="38"/>
       <x:c r="E47" s="38" t="str">
         <x:v>Ainda não sabemos quem é responsável</x:v>
       </x:c>
@@ -6666,7 +6628,7 @@
       <x:c r="C48" s="38" t="str">
         <x:v>Quem hospeda, atualiza e mantém a IA funcionando?</x:v>
       </x:c>
-      <x:c r="D48" s="38" t="str"/>
+      <x:c r="D48" s="38"/>
       <x:c r="E48" s="38" t="str">
         <x:v>Organização — infraestrutura e operação ficam sob controle interno</x:v>
       </x:c>
@@ -6690,7 +6652,7 @@
       <x:c r="C49" s="38" t="str">
         <x:v>Quem hospeda, atualiza e mantém a IA funcionando?</x:v>
       </x:c>
-      <x:c r="D49" s="38" t="str"/>
+      <x:c r="D49" s="38"/>
       <x:c r="E49" s="38" t="str">
         <x:v>Fornecedor — serviço é hospedado e operado externamente</x:v>
       </x:c>
@@ -6714,7 +6676,7 @@
       <x:c r="C50" s="38" t="str">
         <x:v>Quem hospeda, atualiza e mantém a IA funcionando?</x:v>
       </x:c>
-      <x:c r="D50" s="38" t="str"/>
+      <x:c r="D50" s="38"/>
       <x:c r="E50" s="38" t="str">
         <x:v>Compartilhado — parte interna e parte externa</x:v>
       </x:c>
@@ -6738,7 +6700,7 @@
       <x:c r="C51" s="38" t="str">
         <x:v>Quem hospeda, atualiza e mantém a IA funcionando?</x:v>
       </x:c>
-      <x:c r="D51" s="38" t="str"/>
+      <x:c r="D51" s="38"/>
       <x:c r="E51" s="38" t="str">
         <x:v>Ainda não sabemos quem hospeda ou opera</x:v>
       </x:c>
@@ -6762,7 +6724,7 @@
       <x:c r="C52" s="38" t="str">
         <x:v>Você sabe qual plataforma, modelo ou serviço executará a IA? Informe o que souber.</x:v>
       </x:c>
-      <x:c r="D52" s="38" t="str"/>
+      <x:c r="D52" s="38"/>
       <x:c r="E52" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -6786,7 +6748,7 @@
       <x:c r="C53" s="38" t="str">
         <x:v>A função de IA pode ser desligada sem interromper todo o produto ou processo?</x:v>
       </x:c>
-      <x:c r="D53" s="38" t="str"/>
+      <x:c r="D53" s="38"/>
       <x:c r="E53" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -6810,7 +6772,7 @@
       <x:c r="C54" s="38" t="str">
         <x:v>A função de IA pode ser desligada sem interromper todo o produto ou processo?</x:v>
       </x:c>
-      <x:c r="D54" s="38" t="str"/>
+      <x:c r="D54" s="38"/>
       <x:c r="E54" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -6834,7 +6796,7 @@
       <x:c r="C55" s="38" t="str">
         <x:v>A função de IA pode ser desligada sem interromper todo o produto ou processo?</x:v>
       </x:c>
-      <x:c r="D55" s="38" t="str"/>
+      <x:c r="D55" s="38"/>
       <x:c r="E55" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -6858,7 +6820,7 @@
       <x:c r="C56" s="38" t="str">
         <x:v>Uma empresa externa pode alterar a IA sem aprovação prévia da organização?</x:v>
       </x:c>
-      <x:c r="D56" s="38" t="str"/>
+      <x:c r="D56" s="38"/>
       <x:c r="E56" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -6882,7 +6844,7 @@
       <x:c r="C57" s="38" t="str">
         <x:v>Uma empresa externa pode alterar a IA sem aprovação prévia da organização?</x:v>
       </x:c>
-      <x:c r="D57" s="38" t="str"/>
+      <x:c r="D57" s="38"/>
       <x:c r="E57" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -6906,7 +6868,7 @@
       <x:c r="C58" s="38" t="str">
         <x:v>Uma empresa externa pode alterar a IA sem aprovação prévia da organização?</x:v>
       </x:c>
-      <x:c r="D58" s="38" t="str"/>
+      <x:c r="D58" s="38"/>
       <x:c r="E58" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -6930,7 +6892,7 @@
       <x:c r="C59" s="38" t="str">
         <x:v>Outras empresas, plataformas ou plugins participam do processamento?</x:v>
       </x:c>
-      <x:c r="D59" s="38" t="str"/>
+      <x:c r="D59" s="38"/>
       <x:c r="E59" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -6954,7 +6916,7 @@
       <x:c r="C60" s="38" t="str">
         <x:v>Outras empresas, plataformas ou plugins participam do processamento?</x:v>
       </x:c>
-      <x:c r="D60" s="38" t="str"/>
+      <x:c r="D60" s="38"/>
       <x:c r="E60" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -6978,7 +6940,7 @@
       <x:c r="C61" s="38" t="str">
         <x:v>Outras empresas, plataformas ou plugins participam do processamento?</x:v>
       </x:c>
-      <x:c r="D61" s="38" t="str"/>
+      <x:c r="D61" s="38"/>
       <x:c r="E61" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7002,7 +6964,7 @@
       <x:c r="C62" s="38" t="str">
         <x:v>Alguma parte da IA será instalada ou executada em computador, servidor ou dispositivo controlado pela organização?</x:v>
       </x:c>
-      <x:c r="D62" s="38" t="str"/>
+      <x:c r="D62" s="38"/>
       <x:c r="E62" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7026,7 +6988,7 @@
       <x:c r="C63" s="38" t="str">
         <x:v>Alguma parte da IA será instalada ou executada em computador, servidor ou dispositivo controlado pela organização?</x:v>
       </x:c>
-      <x:c r="D63" s="38" t="str"/>
+      <x:c r="D63" s="38"/>
       <x:c r="E63" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7050,7 +7012,7 @@
       <x:c r="C64" s="38" t="str">
         <x:v>Alguma parte da IA será instalada ou executada em computador, servidor ou dispositivo controlado pela organização?</x:v>
       </x:c>
-      <x:c r="D64" s="38" t="str"/>
+      <x:c r="D64" s="38"/>
       <x:c r="E64" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7074,7 +7036,7 @@
       <x:c r="C65" s="38" t="str">
         <x:v>Dados da organização serão usados para treinar, ajustar, testar ou melhorar a IA?</x:v>
       </x:c>
-      <x:c r="D65" s="38" t="str"/>
+      <x:c r="D65" s="38"/>
       <x:c r="E65" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7098,7 +7060,7 @@
       <x:c r="C66" s="38" t="str">
         <x:v>Dados da organização serão usados para treinar, ajustar, testar ou melhorar a IA?</x:v>
       </x:c>
-      <x:c r="D66" s="38" t="str"/>
+      <x:c r="D66" s="38"/>
       <x:c r="E66" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7122,7 +7084,7 @@
       <x:c r="C67" s="38" t="str">
         <x:v>Dados da organização serão usados para treinar, ajustar, testar ou melhorar a IA?</x:v>
       </x:c>
-      <x:c r="D67" s="38" t="str"/>
+      <x:c r="D67" s="38"/>
       <x:c r="E67" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7146,7 +7108,7 @@
       <x:c r="C68" s="38" t="str">
         <x:v>O fornecedor pode usar nossos dados para treinar ou melhorar seus modelos?</x:v>
       </x:c>
-      <x:c r="D68" s="38" t="str"/>
+      <x:c r="D68" s="38"/>
       <x:c r="E68" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7170,7 +7132,7 @@
       <x:c r="C69" s="38" t="str">
         <x:v>O fornecedor pode usar nossos dados para treinar ou melhorar seus modelos?</x:v>
       </x:c>
-      <x:c r="D69" s="38" t="str"/>
+      <x:c r="D69" s="38"/>
       <x:c r="E69" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7194,7 +7156,7 @@
       <x:c r="C70" s="38" t="str">
         <x:v>O fornecedor pode usar nossos dados para treinar ou melhorar seus modelos?</x:v>
       </x:c>
-      <x:c r="D70" s="38" t="str"/>
+      <x:c r="D70" s="38"/>
       <x:c r="E70" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7218,7 +7180,7 @@
       <x:c r="C71" s="38" t="str">
         <x:v>O fornecedor guarda algum conteúdo após o uso?</x:v>
       </x:c>
-      <x:c r="D71" s="38" t="str"/>
+      <x:c r="D71" s="38"/>
       <x:c r="E71" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -7242,7 +7204,7 @@
       <x:c r="C72" s="38" t="str">
         <x:v>Sabemos em quais países ou regiões os dados serão processados e armazenados?</x:v>
       </x:c>
-      <x:c r="D72" s="38" t="str"/>
+      <x:c r="D72" s="38"/>
       <x:c r="E72" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7266,7 +7228,7 @@
       <x:c r="C73" s="38" t="str">
         <x:v>Sabemos em quais países ou regiões os dados serão processados e armazenados?</x:v>
       </x:c>
-      <x:c r="D73" s="38" t="str"/>
+      <x:c r="D73" s="38"/>
       <x:c r="E73" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7290,7 +7252,7 @@
       <x:c r="C74" s="38" t="str">
         <x:v>Sabemos em quais países ou regiões os dados serão processados e armazenados?</x:v>
       </x:c>
-      <x:c r="D74" s="38" t="str"/>
+      <x:c r="D74" s="38"/>
       <x:c r="E74" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7314,7 +7276,7 @@
       <x:c r="C75" s="38" t="str">
         <x:v>O fornecedor comprova que os dados de um cliente não se misturam com os de outro?</x:v>
       </x:c>
-      <x:c r="D75" s="38" t="str"/>
+      <x:c r="D75" s="38"/>
       <x:c r="E75" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7338,7 +7300,7 @@
       <x:c r="C76" s="38" t="str">
         <x:v>O fornecedor comprova que os dados de um cliente não se misturam com os de outro?</x:v>
       </x:c>
-      <x:c r="D76" s="38" t="str"/>
+      <x:c r="D76" s="38"/>
       <x:c r="E76" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7362,7 +7324,7 @@
       <x:c r="C77" s="38" t="str">
         <x:v>O fornecedor comprova que os dados de um cliente não se misturam com os de outro?</x:v>
       </x:c>
-      <x:c r="D77" s="38" t="str"/>
+      <x:c r="D77" s="38"/>
       <x:c r="E77" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7386,7 +7348,7 @@
       <x:c r="C78" s="38" t="str">
         <x:v>A solução permite usar login corporativo e controlar permissões?</x:v>
       </x:c>
-      <x:c r="D78" s="38" t="str"/>
+      <x:c r="D78" s="38"/>
       <x:c r="E78" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7410,7 +7372,7 @@
       <x:c r="C79" s="38" t="str">
         <x:v>A solução permite usar login corporativo e controlar permissões?</x:v>
       </x:c>
-      <x:c r="D79" s="38" t="str"/>
+      <x:c r="D79" s="38"/>
       <x:c r="E79" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7434,7 +7396,7 @@
       <x:c r="C80" s="38" t="str">
         <x:v>A solução permite usar login corporativo e controlar permissões?</x:v>
       </x:c>
-      <x:c r="D80" s="38" t="str"/>
+      <x:c r="D80" s="38"/>
       <x:c r="E80" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7458,7 +7420,7 @@
       <x:c r="C81" s="38" t="str">
         <x:v>A organização consegue receber os registros de acesso, uso e administração?</x:v>
       </x:c>
-      <x:c r="D81" s="38" t="str"/>
+      <x:c r="D81" s="38"/>
       <x:c r="E81" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7482,7 +7444,7 @@
       <x:c r="C82" s="38" t="str">
         <x:v>A organização consegue receber os registros de acesso, uso e administração?</x:v>
       </x:c>
-      <x:c r="D82" s="38" t="str"/>
+      <x:c r="D82" s="38"/>
       <x:c r="E82" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7506,7 +7468,7 @@
       <x:c r="C83" s="38" t="str">
         <x:v>A organização consegue receber os registros de acesso, uso e administração?</x:v>
       </x:c>
-      <x:c r="D83" s="38" t="str"/>
+      <x:c r="D83" s="38"/>
       <x:c r="E83" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7530,7 +7492,7 @@
       <x:c r="C84" s="38" t="str">
         <x:v>O fornecedor apresentou provas de segurança?</x:v>
       </x:c>
-      <x:c r="D84" s="38" t="str"/>
+      <x:c r="D84" s="38"/>
       <x:c r="E84" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7554,7 +7516,7 @@
       <x:c r="C85" s="38" t="str">
         <x:v>O fornecedor apresentou provas de segurança?</x:v>
       </x:c>
-      <x:c r="D85" s="38" t="str"/>
+      <x:c r="D85" s="38"/>
       <x:c r="E85" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7578,7 +7540,7 @@
       <x:c r="C86" s="38" t="str">
         <x:v>O fornecedor apresentou provas de segurança?</x:v>
       </x:c>
-      <x:c r="D86" s="38" t="str"/>
+      <x:c r="D86" s="38"/>
       <x:c r="E86" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7602,7 +7564,7 @@
       <x:c r="C87" s="38" t="str">
         <x:v>O contrato define prazo para avisar incidentes e vulnerabilidades?</x:v>
       </x:c>
-      <x:c r="D87" s="38" t="str"/>
+      <x:c r="D87" s="38"/>
       <x:c r="E87" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7626,7 +7588,7 @@
       <x:c r="C88" s="38" t="str">
         <x:v>O contrato define prazo para avisar incidentes e vulnerabilidades?</x:v>
       </x:c>
-      <x:c r="D88" s="38" t="str"/>
+      <x:c r="D88" s="38"/>
       <x:c r="E88" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7650,7 +7612,7 @@
       <x:c r="C89" s="38" t="str">
         <x:v>O contrato define prazo para avisar incidentes e vulnerabilidades?</x:v>
       </x:c>
-      <x:c r="D89" s="38" t="str"/>
+      <x:c r="D89" s="38"/>
       <x:c r="E89" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7674,7 +7636,7 @@
       <x:c r="C90" s="38" t="str">
         <x:v>O fornecedor avisa antes de mudanças importantes?</x:v>
       </x:c>
-      <x:c r="D90" s="38" t="str"/>
+      <x:c r="D90" s="38"/>
       <x:c r="E90" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7698,7 +7660,7 @@
       <x:c r="C91" s="38" t="str">
         <x:v>O fornecedor avisa antes de mudanças importantes?</x:v>
       </x:c>
-      <x:c r="D91" s="38" t="str"/>
+      <x:c r="D91" s="38"/>
       <x:c r="E91" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7722,7 +7684,7 @@
       <x:c r="C92" s="38" t="str">
         <x:v>O fornecedor avisa antes de mudanças importantes?</x:v>
       </x:c>
-      <x:c r="D92" s="38" t="str"/>
+      <x:c r="D92" s="38"/>
       <x:c r="E92" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7746,7 +7708,7 @@
       <x:c r="C93" s="38" t="str">
         <x:v>Existe garantia de disponibilidade e recuperação do serviço?</x:v>
       </x:c>
-      <x:c r="D93" s="38" t="str"/>
+      <x:c r="D93" s="38"/>
       <x:c r="E93" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7770,7 +7732,7 @@
       <x:c r="C94" s="38" t="str">
         <x:v>Existe garantia de disponibilidade e recuperação do serviço?</x:v>
       </x:c>
-      <x:c r="D94" s="38" t="str"/>
+      <x:c r="D94" s="38"/>
       <x:c r="E94" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7794,7 +7756,7 @@
       <x:c r="C95" s="38" t="str">
         <x:v>Existe garantia de disponibilidade e recuperação do serviço?</x:v>
       </x:c>
-      <x:c r="D95" s="38" t="str"/>
+      <x:c r="D95" s="38"/>
       <x:c r="E95" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7818,7 +7780,7 @@
       <x:c r="C96" s="38" t="str">
         <x:v>É possível sair do serviço sem perder dados ou ficar dependente do fornecedor?</x:v>
       </x:c>
-      <x:c r="D96" s="38" t="str"/>
+      <x:c r="D96" s="38"/>
       <x:c r="E96" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7842,7 +7804,7 @@
       <x:c r="C97" s="38" t="str">
         <x:v>É possível sair do serviço sem perder dados ou ficar dependente do fornecedor?</x:v>
       </x:c>
-      <x:c r="D97" s="38" t="str"/>
+      <x:c r="D97" s="38"/>
       <x:c r="E97" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7866,7 +7828,7 @@
       <x:c r="C98" s="38" t="str">
         <x:v>É possível sair do serviço sem perder dados ou ficar dependente do fornecedor?</x:v>
       </x:c>
-      <x:c r="D98" s="38" t="str"/>
+      <x:c r="D98" s="38"/>
       <x:c r="E98" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7890,7 +7852,7 @@
       <x:c r="C99" s="38" t="str">
         <x:v>Está documentado quem é responsável por cada controle de segurança?</x:v>
       </x:c>
-      <x:c r="D99" s="38" t="str"/>
+      <x:c r="D99" s="38"/>
       <x:c r="E99" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7914,7 +7876,7 @@
       <x:c r="C100" s="38" t="str">
         <x:v>Está documentado quem é responsável por cada controle de segurança?</x:v>
       </x:c>
-      <x:c r="D100" s="38" t="str"/>
+      <x:c r="D100" s="38"/>
       <x:c r="E100" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -7938,7 +7900,7 @@
       <x:c r="C101" s="38" t="str">
         <x:v>Está documentado quem é responsável por cada controle de segurança?</x:v>
       </x:c>
-      <x:c r="D101" s="38" t="str"/>
+      <x:c r="D101" s="38"/>
       <x:c r="E101" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -7962,7 +7924,7 @@
       <x:c r="C102" s="38" t="str">
         <x:v>O contrato limita treinamento, compartilhamento, retenção e outros usos dos dados?</x:v>
       </x:c>
-      <x:c r="D102" s="38" t="str"/>
+      <x:c r="D102" s="38"/>
       <x:c r="E102" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -7986,7 +7948,7 @@
       <x:c r="C103" s="38" t="str">
         <x:v>O contrato limita treinamento, compartilhamento, retenção e outros usos dos dados?</x:v>
       </x:c>
-      <x:c r="D103" s="38" t="str"/>
+      <x:c r="D103" s="38"/>
       <x:c r="E103" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8010,7 +7972,7 @@
       <x:c r="C104" s="38" t="str">
         <x:v>O contrato limita treinamento, compartilhamento, retenção e outros usos dos dados?</x:v>
       </x:c>
-      <x:c r="D104" s="38" t="str"/>
+      <x:c r="D104" s="38"/>
       <x:c r="E104" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8034,7 +7996,7 @@
       <x:c r="C105" s="38" t="str">
         <x:v>Quais informações ou provas o fornecedor não apresentou?</x:v>
       </x:c>
-      <x:c r="D105" s="38" t="str"/>
+      <x:c r="D105" s="38"/>
       <x:c r="E105" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -8058,7 +8020,7 @@
       <x:c r="C106" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D106" s="38" t="str"/>
+      <x:c r="D106" s="38"/>
       <x:c r="E106" s="38" t="str">
         <x:v>Somente dados públicos ou nenhum dado — ex.: páginas públicas, materiais já publicados ou conteúdo sem restrição</x:v>
       </x:c>
@@ -8082,7 +8044,7 @@
       <x:c r="C107" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D107" s="38" t="str"/>
+      <x:c r="D107" s="38"/>
       <x:c r="E107" s="38" t="str">
         <x:v>Dados pessoais básicos — ex.: nome, idade, e-mail, telefone, endereço, cargo ou matrícula</x:v>
       </x:c>
@@ -8106,7 +8068,7 @@
       <x:c r="C108" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D108" s="38" t="str"/>
+      <x:c r="D108" s="38"/>
       <x:c r="E108" s="38" t="str">
         <x:v>Dados pessoais sensíveis — ex.: saúde, biometria, origem racial ou étnica, religião, opinião política, vida sexual ou filiação sindical</x:v>
       </x:c>
@@ -8130,7 +8092,7 @@
       <x:c r="C109" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D109" s="38" t="str"/>
+      <x:c r="D109" s="38"/>
       <x:c r="E109" s="38" t="str">
         <x:v>Dados bancários e financeiros — ex.: conta, agência, saldo, limite, cartão, transação, renda, crédito ou investimento</x:v>
       </x:c>
@@ -8154,7 +8116,7 @@
       <x:c r="C110" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D110" s="38" t="str"/>
+      <x:c r="D110" s="38"/>
       <x:c r="E110" s="38" t="str">
         <x:v>Credenciais, segredos e informações de segurança — ex.: senha, token, chave de API, cookie, certificado, código-fonte ou configuração de segurança</x:v>
       </x:c>
@@ -8178,7 +8140,7 @@
       <x:c r="C111" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D111" s="38" t="str"/>
+      <x:c r="D111" s="38"/>
       <x:c r="E111" s="38" t="str">
         <x:v>Dados corporativos internos — ex.: contratos, procedimentos, relatórios, documentos internos, estratégia ou informações operacionais</x:v>
       </x:c>
@@ -8202,7 +8164,7 @@
       <x:c r="C112" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D112" s="38" t="str"/>
+      <x:c r="D112" s="38"/>
       <x:c r="E112" s="38" t="str">
         <x:v>Dados regulados ou protegidos por sigilo — ex.: segredo bancário, fiscal, judicial, investigação ou informação classificada como restrita</x:v>
       </x:c>
@@ -8226,7 +8188,7 @@
       <x:c r="C113" s="38" t="str">
         <x:v>Selecione os tipos de dados que a solução poderá receber, consultar, armazenar ou gerar.</x:v>
       </x:c>
-      <x:c r="D113" s="38" t="str"/>
+      <x:c r="D113" s="38"/>
       <x:c r="E113" s="38" t="str">
         <x:v>Não sei informar — selecione esta opção quando precisar de apoio para identificar os dados</x:v>
       </x:c>
@@ -8250,7 +8212,7 @@
       <x:c r="C114" s="38" t="str">
         <x:v>Dê exemplos dos dados que entram e saem da solução.</x:v>
       </x:c>
-      <x:c r="D114" s="38" t="str"/>
+      <x:c r="D114" s="38"/>
       <x:c r="E114" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -8274,7 +8236,7 @@
       <x:c r="C115" s="38" t="str">
         <x:v>Algum dado será enviado ou disponibilizado para outra empresa?</x:v>
       </x:c>
-      <x:c r="D115" s="38" t="str"/>
+      <x:c r="D115" s="38"/>
       <x:c r="E115" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8298,7 +8260,7 @@
       <x:c r="C116" s="38" t="str">
         <x:v>Algum dado será enviado ou disponibilizado para outra empresa?</x:v>
       </x:c>
-      <x:c r="D116" s="38" t="str"/>
+      <x:c r="D116" s="38"/>
       <x:c r="E116" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8322,7 +8284,7 @@
       <x:c r="C117" s="38" t="str">
         <x:v>Algum dado será enviado ou disponibilizado para outra empresa?</x:v>
       </x:c>
-      <x:c r="D117" s="38" t="str"/>
+      <x:c r="D117" s="38"/>
       <x:c r="E117" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8346,7 +8308,7 @@
       <x:c r="C118" s="38" t="str">
         <x:v>Os dados poderão ser processados ou armazenados fora do Brasil?</x:v>
       </x:c>
-      <x:c r="D118" s="38" t="str"/>
+      <x:c r="D118" s="38"/>
       <x:c r="E118" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8370,7 +8332,7 @@
       <x:c r="C119" s="38" t="str">
         <x:v>Os dados poderão ser processados ou armazenados fora do Brasil?</x:v>
       </x:c>
-      <x:c r="D119" s="38" t="str"/>
+      <x:c r="D119" s="38"/>
       <x:c r="E119" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8394,7 +8356,7 @@
       <x:c r="C120" s="38" t="str">
         <x:v>Os dados poderão ser processados ou armazenados fora do Brasil?</x:v>
       </x:c>
-      <x:c r="D120" s="38" t="str"/>
+      <x:c r="D120" s="38"/>
       <x:c r="E120" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8418,7 +8380,7 @@
       <x:c r="C121" s="38" t="str">
         <x:v>Os dados serão reduzidos ou protegidos antes de entrar na IA?</x:v>
       </x:c>
-      <x:c r="D121" s="38" t="str"/>
+      <x:c r="D121" s="38"/>
       <x:c r="E121" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8442,7 +8404,7 @@
       <x:c r="C122" s="38" t="str">
         <x:v>Os dados serão reduzidos ou protegidos antes de entrar na IA?</x:v>
       </x:c>
-      <x:c r="D122" s="38" t="str"/>
+      <x:c r="D122" s="38"/>
       <x:c r="E122" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8466,7 +8428,7 @@
       <x:c r="C123" s="38" t="str">
         <x:v>Os dados serão reduzidos ou protegidos antes de entrar na IA?</x:v>
       </x:c>
-      <x:c r="D123" s="38" t="str"/>
+      <x:c r="D123" s="38"/>
       <x:c r="E123" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8490,7 +8452,7 @@
       <x:c r="C124" s="38" t="str">
         <x:v>Existe prazo para apagar prompts, respostas, anexos, memória e registros?</x:v>
       </x:c>
-      <x:c r="D124" s="38" t="str"/>
+      <x:c r="D124" s="38"/>
       <x:c r="E124" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8514,7 +8476,7 @@
       <x:c r="C125" s="38" t="str">
         <x:v>Existe prazo para apagar prompts, respostas, anexos, memória e registros?</x:v>
       </x:c>
-      <x:c r="D125" s="38" t="str"/>
+      <x:c r="D125" s="38"/>
       <x:c r="E125" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8538,7 +8500,7 @@
       <x:c r="C126" s="38" t="str">
         <x:v>Existe prazo para apagar prompts, respostas, anexos, memória e registros?</x:v>
       </x:c>
-      <x:c r="D126" s="38" t="str"/>
+      <x:c r="D126" s="38"/>
       <x:c r="E126" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8562,7 +8524,7 @@
       <x:c r="C127" s="38" t="str">
         <x:v>Quando o dado original for apagado, suas cópias e derivados também serão removidos?</x:v>
       </x:c>
-      <x:c r="D127" s="38" t="str"/>
+      <x:c r="D127" s="38"/>
       <x:c r="E127" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8586,7 +8548,7 @@
       <x:c r="C128" s="38" t="str">
         <x:v>Quando o dado original for apagado, suas cópias e derivados também serão removidos?</x:v>
       </x:c>
-      <x:c r="D128" s="38" t="str"/>
+      <x:c r="D128" s="38"/>
       <x:c r="E128" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8610,7 +8572,7 @@
       <x:c r="C129" s="38" t="str">
         <x:v>Quando o dado original for apagado, suas cópias e derivados também serão removidos?</x:v>
       </x:c>
-      <x:c r="D129" s="38" t="str"/>
+      <x:c r="D129" s="38"/>
       <x:c r="E129" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8634,7 +8596,7 @@
       <x:c r="C130" s="38" t="str">
         <x:v>Existe verificação automática para impedir envio ou saída indevida de dados?</x:v>
       </x:c>
-      <x:c r="D130" s="38" t="str"/>
+      <x:c r="D130" s="38"/>
       <x:c r="E130" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8658,7 +8620,7 @@
       <x:c r="C131" s="38" t="str">
         <x:v>Existe verificação automática para impedir envio ou saída indevida de dados?</x:v>
       </x:c>
-      <x:c r="D131" s="38" t="str"/>
+      <x:c r="D131" s="38"/>
       <x:c r="E131" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8682,7 +8644,7 @@
       <x:c r="C132" s="38" t="str">
         <x:v>Existe verificação automática para impedir envio ou saída indevida de dados?</x:v>
       </x:c>
-      <x:c r="D132" s="38" t="str"/>
+      <x:c r="D132" s="38"/>
       <x:c r="E132" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8706,7 +8668,7 @@
       <x:c r="C133" s="38" t="str">
         <x:v>Quem usará a solução ou poderá ser afetado por ela?</x:v>
       </x:c>
-      <x:c r="D133" s="38" t="str"/>
+      <x:c r="D133" s="38"/>
       <x:c r="E133" s="38" t="str">
         <x:v>Colaboradores</x:v>
       </x:c>
@@ -8730,7 +8692,7 @@
       <x:c r="C134" s="38" t="str">
         <x:v>Quem usará a solução ou poderá ser afetado por ela?</x:v>
       </x:c>
-      <x:c r="D134" s="38" t="str"/>
+      <x:c r="D134" s="38"/>
       <x:c r="E134" s="38" t="str">
         <x:v>Terceiros</x:v>
       </x:c>
@@ -8754,7 +8716,7 @@
       <x:c r="C135" s="38" t="str">
         <x:v>Quem usará a solução ou poderá ser afetado por ela?</x:v>
       </x:c>
-      <x:c r="D135" s="38" t="str"/>
+      <x:c r="D135" s="38"/>
       <x:c r="E135" s="38" t="str">
         <x:v>Parceiros</x:v>
       </x:c>
@@ -8778,7 +8740,7 @@
       <x:c r="C136" s="38" t="str">
         <x:v>Quem usará a solução ou poderá ser afetado por ela?</x:v>
       </x:c>
-      <x:c r="D136" s="38" t="str"/>
+      <x:c r="D136" s="38"/>
       <x:c r="E136" s="38" t="str">
         <x:v>Clientes</x:v>
       </x:c>
@@ -8802,7 +8764,7 @@
       <x:c r="C137" s="38" t="str">
         <x:v>Quem usará a solução ou poderá ser afetado por ela?</x:v>
       </x:c>
-      <x:c r="D137" s="38" t="str"/>
+      <x:c r="D137" s="38"/>
       <x:c r="E137" s="38" t="str">
         <x:v>Público geral</x:v>
       </x:c>
@@ -8826,7 +8788,7 @@
       <x:c r="C138" s="38" t="str">
         <x:v>Quem usará a solução ou poderá ser afetado por ela?</x:v>
       </x:c>
-      <x:c r="D138" s="38" t="str"/>
+      <x:c r="D138" s="38"/>
       <x:c r="E138" s="38" t="str">
         <x:v>Outros sistemas ou processos automáticos</x:v>
       </x:c>
@@ -8850,7 +8812,7 @@
       <x:c r="C139" s="38" t="str">
         <x:v>A solução ficará acessível pela Internet ou por canal externo?</x:v>
       </x:c>
-      <x:c r="D139" s="38" t="str"/>
+      <x:c r="D139" s="38"/>
       <x:c r="E139" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8874,7 +8836,7 @@
       <x:c r="C140" s="38" t="str">
         <x:v>A solução ficará acessível pela Internet ou por canal externo?</x:v>
       </x:c>
-      <x:c r="D140" s="38" t="str"/>
+      <x:c r="D140" s="38"/>
       <x:c r="E140" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8898,7 +8860,7 @@
       <x:c r="C141" s="38" t="str">
         <x:v>A solução ficará acessível pela Internet ou por canal externo?</x:v>
       </x:c>
-      <x:c r="D141" s="38" t="str"/>
+      <x:c r="D141" s="38"/>
       <x:c r="E141" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8922,7 +8884,7 @@
       <x:c r="C142" s="38" t="str">
         <x:v>A IA produzirá conteúdo que será enviado para fora da organização?</x:v>
       </x:c>
-      <x:c r="D142" s="38" t="str"/>
+      <x:c r="D142" s="38"/>
       <x:c r="E142" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -8946,7 +8908,7 @@
       <x:c r="C143" s="38" t="str">
         <x:v>A IA produzirá conteúdo que será enviado para fora da organização?</x:v>
       </x:c>
-      <x:c r="D143" s="38" t="str"/>
+      <x:c r="D143" s="38"/>
       <x:c r="E143" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -8970,7 +8932,7 @@
       <x:c r="C144" s="38" t="str">
         <x:v>A IA produzirá conteúdo que será enviado para fora da organização?</x:v>
       </x:c>
-      <x:c r="D144" s="38" t="str"/>
+      <x:c r="D144" s="38"/>
       <x:c r="E144" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -8994,7 +8956,7 @@
       <x:c r="C145" s="38" t="str">
         <x:v>A IA ajudará a decidir algo importante sobre uma pessoa ou empresa?</x:v>
       </x:c>
-      <x:c r="D145" s="38" t="str"/>
+      <x:c r="D145" s="38"/>
       <x:c r="E145" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9018,7 +8980,7 @@
       <x:c r="C146" s="38" t="str">
         <x:v>A IA ajudará a decidir algo importante sobre uma pessoa ou empresa?</x:v>
       </x:c>
-      <x:c r="D146" s="38" t="str"/>
+      <x:c r="D146" s="38"/>
       <x:c r="E146" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9042,7 +9004,7 @@
       <x:c r="C147" s="38" t="str">
         <x:v>A IA ajudará a decidir algo importante sobre uma pessoa ou empresa?</x:v>
       </x:c>
-      <x:c r="D147" s="38" t="str"/>
+      <x:c r="D147" s="38"/>
       <x:c r="E147" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9066,7 +9028,7 @@
       <x:c r="C148" s="38" t="str">
         <x:v>A IA poderá afetar dinheiro, crédito, fraude, pagamento, investimento ou autenticação?</x:v>
       </x:c>
-      <x:c r="D148" s="38" t="str"/>
+      <x:c r="D148" s="38"/>
       <x:c r="E148" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9090,7 +9052,7 @@
       <x:c r="C149" s="38" t="str">
         <x:v>A IA poderá afetar dinheiro, crédito, fraude, pagamento, investimento ou autenticação?</x:v>
       </x:c>
-      <x:c r="D149" s="38" t="str"/>
+      <x:c r="D149" s="38"/>
       <x:c r="E149" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9114,7 +9076,7 @@
       <x:c r="C150" s="38" t="str">
         <x:v>A IA poderá afetar dinheiro, crédito, fraude, pagamento, investimento ou autenticação?</x:v>
       </x:c>
-      <x:c r="D150" s="38" t="str"/>
+      <x:c r="D150" s="38"/>
       <x:c r="E150" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9138,7 +9100,7 @@
       <x:c r="C151" s="38" t="str">
         <x:v>A solução participa de processo crítico ou obrigatório?</x:v>
       </x:c>
-      <x:c r="D151" s="38" t="str"/>
+      <x:c r="D151" s="38"/>
       <x:c r="E151" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9162,7 +9124,7 @@
       <x:c r="C152" s="38" t="str">
         <x:v>A solução participa de processo crítico ou obrigatório?</x:v>
       </x:c>
-      <x:c r="D152" s="38" t="str"/>
+      <x:c r="D152" s="38"/>
       <x:c r="E152" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9186,7 +9148,7 @@
       <x:c r="C153" s="38" t="str">
         <x:v>A solução participa de processo crítico ou obrigatório?</x:v>
       </x:c>
-      <x:c r="D153" s="38" t="str"/>
+      <x:c r="D153" s="38"/>
       <x:c r="E153" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9210,7 +9172,7 @@
       <x:c r="C154" s="38" t="str">
         <x:v>Um erro poderia afetar muitas pessoas, transações ou processos de uma vez?</x:v>
       </x:c>
-      <x:c r="D154" s="38" t="str"/>
+      <x:c r="D154" s="38"/>
       <x:c r="E154" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9234,7 +9196,7 @@
       <x:c r="C155" s="38" t="str">
         <x:v>Um erro poderia afetar muitas pessoas, transações ou processos de uma vez?</x:v>
       </x:c>
-      <x:c r="D155" s="38" t="str"/>
+      <x:c r="D155" s="38"/>
       <x:c r="E155" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9258,7 +9220,7 @@
       <x:c r="C156" s="38" t="str">
         <x:v>Um erro poderia afetar muitas pessoas, transações ou processos de uma vez?</x:v>
       </x:c>
-      <x:c r="D156" s="38" t="str"/>
+      <x:c r="D156" s="38"/>
       <x:c r="E156" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9282,7 +9244,7 @@
       <x:c r="C157" s="38" t="str">
         <x:v>Uma pessoa revisa decisões ou ações de alto impacto antes de serem executadas?</x:v>
       </x:c>
-      <x:c r="D157" s="38" t="str"/>
+      <x:c r="D157" s="38"/>
       <x:c r="E157" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9306,7 +9268,7 @@
       <x:c r="C158" s="38" t="str">
         <x:v>Uma pessoa revisa decisões ou ações de alto impacto antes de serem executadas?</x:v>
       </x:c>
-      <x:c r="D158" s="38" t="str"/>
+      <x:c r="D158" s="38"/>
       <x:c r="E158" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9330,7 +9292,7 @@
       <x:c r="C159" s="38" t="str">
         <x:v>Uma pessoa revisa decisões ou ações de alto impacto antes de serem executadas?</x:v>
       </x:c>
-      <x:c r="D159" s="38" t="str"/>
+      <x:c r="D159" s="38"/>
       <x:c r="E159" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9354,7 +9316,7 @@
       <x:c r="C160" s="38" t="str">
         <x:v>A pessoa afetada consegue contestar e corrigir a decisão?</x:v>
       </x:c>
-      <x:c r="D160" s="38" t="str"/>
+      <x:c r="D160" s="38"/>
       <x:c r="E160" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9378,7 +9340,7 @@
       <x:c r="C161" s="38" t="str">
         <x:v>A pessoa afetada consegue contestar e corrigir a decisão?</x:v>
       </x:c>
-      <x:c r="D161" s="38" t="str"/>
+      <x:c r="D161" s="38"/>
       <x:c r="E161" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9402,7 +9364,7 @@
       <x:c r="C162" s="38" t="str">
         <x:v>A pessoa afetada consegue contestar e corrigir a decisão?</x:v>
       </x:c>
-      <x:c r="D162" s="38" t="str"/>
+      <x:c r="D162" s="38"/>
       <x:c r="E162" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9426,7 +9388,7 @@
       <x:c r="C163" s="38" t="str">
         <x:v>Existe uma alternativa humana ou manual quando a IA falhar?</x:v>
       </x:c>
-      <x:c r="D163" s="38" t="str"/>
+      <x:c r="D163" s="38"/>
       <x:c r="E163" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9450,7 +9412,7 @@
       <x:c r="C164" s="38" t="str">
         <x:v>Existe uma alternativa humana ou manual quando a IA falhar?</x:v>
       </x:c>
-      <x:c r="D164" s="38" t="str"/>
+      <x:c r="D164" s="38"/>
       <x:c r="E164" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9474,7 +9436,7 @@
       <x:c r="C165" s="38" t="str">
         <x:v>Existe uma alternativa humana ou manual quando a IA falhar?</x:v>
       </x:c>
-      <x:c r="D165" s="38" t="str"/>
+      <x:c r="D165" s="38"/>
       <x:c r="E165" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9498,7 +9460,7 @@
       <x:c r="C166" s="38" t="str">
         <x:v>Uma ação errada pode ser desfeita no tempo necessário?</x:v>
       </x:c>
-      <x:c r="D166" s="38" t="str"/>
+      <x:c r="D166" s="38"/>
       <x:c r="E166" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9522,7 +9484,7 @@
       <x:c r="C167" s="38" t="str">
         <x:v>Uma ação errada pode ser desfeita no tempo necessário?</x:v>
       </x:c>
-      <x:c r="D167" s="38" t="str"/>
+      <x:c r="D167" s="38"/>
       <x:c r="E167" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9546,7 +9508,7 @@
       <x:c r="C168" s="38" t="str">
         <x:v>Uma ação errada pode ser desfeita no tempo necessário?</x:v>
       </x:c>
-      <x:c r="D168" s="38" t="str"/>
+      <x:c r="D168" s="38"/>
       <x:c r="E168" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9570,7 +9532,7 @@
       <x:c r="C169" s="38" t="str">
         <x:v>O que pode acontecer se a solução errar, for abusada, parar ou vazar dados?</x:v>
       </x:c>
-      <x:c r="D169" s="38" t="str"/>
+      <x:c r="D169" s="38"/>
       <x:c r="E169" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -9594,7 +9556,7 @@
       <x:c r="C170" s="38" t="str">
         <x:v>As chamadas de IA passam por um ponto corporativo de controle?</x:v>
       </x:c>
-      <x:c r="D170" s="38" t="str"/>
+      <x:c r="D170" s="38"/>
       <x:c r="E170" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9618,7 +9580,7 @@
       <x:c r="C171" s="38" t="str">
         <x:v>As chamadas de IA passam por um ponto corporativo de controle?</x:v>
       </x:c>
-      <x:c r="D171" s="38" t="str"/>
+      <x:c r="D171" s="38"/>
       <x:c r="E171" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9642,7 +9604,7 @@
       <x:c r="C172" s="38" t="str">
         <x:v>As chamadas de IA passam por um ponto corporativo de controle?</x:v>
       </x:c>
-      <x:c r="D172" s="38" t="str"/>
+      <x:c r="D172" s="38"/>
       <x:c r="E172" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9666,7 +9628,7 @@
       <x:c r="C173" s="38" t="str">
         <x:v>Algum usuário ou sistema se conecta diretamente ao provedor de IA?</x:v>
       </x:c>
-      <x:c r="D173" s="38" t="str"/>
+      <x:c r="D173" s="38"/>
       <x:c r="E173" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9690,7 +9652,7 @@
       <x:c r="C174" s="38" t="str">
         <x:v>Algum usuário ou sistema se conecta diretamente ao provedor de IA?</x:v>
       </x:c>
-      <x:c r="D174" s="38" t="str"/>
+      <x:c r="D174" s="38"/>
       <x:c r="E174" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9714,7 +9676,7 @@
       <x:c r="C175" s="38" t="str">
         <x:v>Algum usuário ou sistema se conecta diretamente ao provedor de IA?</x:v>
       </x:c>
-      <x:c r="D175" s="38" t="str"/>
+      <x:c r="D175" s="38"/>
       <x:c r="E175" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9738,7 +9700,7 @@
       <x:c r="C176" s="38" t="str">
         <x:v>Usuários, sistemas e administradores precisam se identificar e ter permissão?</x:v>
       </x:c>
-      <x:c r="D176" s="38" t="str"/>
+      <x:c r="D176" s="38"/>
       <x:c r="E176" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9762,7 +9724,7 @@
       <x:c r="C177" s="38" t="str">
         <x:v>Usuários, sistemas e administradores precisam se identificar e ter permissão?</x:v>
       </x:c>
-      <x:c r="D177" s="38" t="str"/>
+      <x:c r="D177" s="38"/>
       <x:c r="E177" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9786,7 +9748,7 @@
       <x:c r="C178" s="38" t="str">
         <x:v>Usuários, sistemas e administradores precisam se identificar e ter permissão?</x:v>
       </x:c>
-      <x:c r="D178" s="38" t="str"/>
+      <x:c r="D178" s="38"/>
       <x:c r="E178" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9810,7 +9772,7 @@
       <x:c r="C179" s="38" t="str">
         <x:v>Cada sistema usa uma identidade técnica própria?</x:v>
       </x:c>
-      <x:c r="D179" s="38" t="str"/>
+      <x:c r="D179" s="38"/>
       <x:c r="E179" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9834,7 +9796,7 @@
       <x:c r="C180" s="38" t="str">
         <x:v>Cada sistema usa uma identidade técnica própria?</x:v>
       </x:c>
-      <x:c r="D180" s="38" t="str"/>
+      <x:c r="D180" s="38"/>
       <x:c r="E180" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9858,7 +9820,7 @@
       <x:c r="C181" s="38" t="str">
         <x:v>Cada sistema usa uma identidade técnica própria?</x:v>
       </x:c>
-      <x:c r="D181" s="38" t="str"/>
+      <x:c r="D181" s="38"/>
       <x:c r="E181" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9882,7 +9844,7 @@
       <x:c r="C182" s="38" t="str">
         <x:v>É possível saber qual pessoa originou uma ação realizada pela IA?</x:v>
       </x:c>
-      <x:c r="D182" s="38" t="str"/>
+      <x:c r="D182" s="38"/>
       <x:c r="E182" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9906,7 +9868,7 @@
       <x:c r="C183" s="38" t="str">
         <x:v>É possível saber qual pessoa originou uma ação realizada pela IA?</x:v>
       </x:c>
-      <x:c r="D183" s="38" t="str"/>
+      <x:c r="D183" s="38"/>
       <x:c r="E183" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -9930,7 +9892,7 @@
       <x:c r="C184" s="38" t="str">
         <x:v>É possível saber qual pessoa originou uma ação realizada pela IA?</x:v>
       </x:c>
-      <x:c r="D184" s="38" t="str"/>
+      <x:c r="D184" s="38"/>
       <x:c r="E184" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -9954,7 +9916,7 @@
       <x:c r="C185" s="38" t="str">
         <x:v>Senhas, tokens e chaves ficam em cofre seguro e com acesso mínimo?</x:v>
       </x:c>
-      <x:c r="D185" s="38" t="str"/>
+      <x:c r="D185" s="38"/>
       <x:c r="E185" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -9978,7 +9940,7 @@
       <x:c r="C186" s="38" t="str">
         <x:v>Senhas, tokens e chaves ficam em cofre seguro e com acesso mínimo?</x:v>
       </x:c>
-      <x:c r="D186" s="38" t="str"/>
+      <x:c r="D186" s="38"/>
       <x:c r="E186" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10002,7 +9964,7 @@
       <x:c r="C187" s="38" t="str">
         <x:v>Senhas, tokens e chaves ficam em cofre seguro e com acesso mínimo?</x:v>
       </x:c>
-      <x:c r="D187" s="38" t="str"/>
+      <x:c r="D187" s="38"/>
       <x:c r="E187" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10026,7 +9988,7 @@
       <x:c r="C188" s="38" t="str">
         <x:v>Desenvolvimento, teste, homologação e produção estão separados?</x:v>
       </x:c>
-      <x:c r="D188" s="38" t="str"/>
+      <x:c r="D188" s="38"/>
       <x:c r="E188" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10050,7 +10012,7 @@
       <x:c r="C189" s="38" t="str">
         <x:v>Desenvolvimento, teste, homologação e produção estão separados?</x:v>
       </x:c>
-      <x:c r="D189" s="38" t="str"/>
+      <x:c r="D189" s="38"/>
       <x:c r="E189" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10074,7 +10036,7 @@
       <x:c r="C190" s="38" t="str">
         <x:v>Desenvolvimento, teste, homologação e produção estão separados?</x:v>
       </x:c>
-      <x:c r="D190" s="38" t="str"/>
+      <x:c r="D190" s="38"/>
       <x:c r="E190" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10098,7 +10060,7 @@
       <x:c r="C191" s="38" t="str">
         <x:v>Textos, parâmetros e arquivos são verificados antes do processamento?</x:v>
       </x:c>
-      <x:c r="D191" s="38" t="str"/>
+      <x:c r="D191" s="38"/>
       <x:c r="E191" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10122,7 +10084,7 @@
       <x:c r="C192" s="38" t="str">
         <x:v>Textos, parâmetros e arquivos são verificados antes do processamento?</x:v>
       </x:c>
-      <x:c r="D192" s="38" t="str"/>
+      <x:c r="D192" s="38"/>
       <x:c r="E192" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10146,7 +10108,7 @@
       <x:c r="C193" s="38" t="str">
         <x:v>Textos, parâmetros e arquivos são verificados antes do processamento?</x:v>
       </x:c>
-      <x:c r="D193" s="38" t="str"/>
+      <x:c r="D193" s="38"/>
       <x:c r="E193" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10170,7 +10132,7 @@
       <x:c r="C194" s="38" t="str">
         <x:v>As respostas da IA são verificadas antes de serem exibidas ou usadas por outro sistema?</x:v>
       </x:c>
-      <x:c r="D194" s="38" t="str"/>
+      <x:c r="D194" s="38"/>
       <x:c r="E194" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10194,7 +10156,7 @@
       <x:c r="C195" s="38" t="str">
         <x:v>As respostas da IA são verificadas antes de serem exibidas ou usadas por outro sistema?</x:v>
       </x:c>
-      <x:c r="D195" s="38" t="str"/>
+      <x:c r="D195" s="38"/>
       <x:c r="E195" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10218,7 +10180,7 @@
       <x:c r="C196" s="38" t="str">
         <x:v>As respostas da IA são verificadas antes de serem exibidas ou usadas por outro sistema?</x:v>
       </x:c>
-      <x:c r="D196" s="38" t="str"/>
+      <x:c r="D196" s="38"/>
       <x:c r="E196" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10242,7 +10204,7 @@
       <x:c r="C197" s="38" t="str">
         <x:v>A solução só consegue se comunicar com destinos realmente necessários?</x:v>
       </x:c>
-      <x:c r="D197" s="38" t="str"/>
+      <x:c r="D197" s="38"/>
       <x:c r="E197" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10266,7 +10228,7 @@
       <x:c r="C198" s="38" t="str">
         <x:v>A solução só consegue se comunicar com destinos realmente necessários?</x:v>
       </x:c>
-      <x:c r="D198" s="38" t="str"/>
+      <x:c r="D198" s="38"/>
       <x:c r="E198" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10290,7 +10252,7 @@
       <x:c r="C199" s="38" t="str">
         <x:v>A solução só consegue se comunicar com destinos realmente necessários?</x:v>
       </x:c>
-      <x:c r="D199" s="38" t="str"/>
+      <x:c r="D199" s="38"/>
       <x:c r="E199" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10314,7 +10276,7 @@
       <x:c r="C200" s="38" t="str">
         <x:v>Vários clientes ou usuários compartilham infraestrutura, memória ou dados?</x:v>
       </x:c>
-      <x:c r="D200" s="38" t="str"/>
+      <x:c r="D200" s="38"/>
       <x:c r="E200" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10338,7 +10300,7 @@
       <x:c r="C201" s="38" t="str">
         <x:v>Vários clientes ou usuários compartilham infraestrutura, memória ou dados?</x:v>
       </x:c>
-      <x:c r="D201" s="38" t="str"/>
+      <x:c r="D201" s="38"/>
       <x:c r="E201" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10362,7 +10324,7 @@
       <x:c r="C202" s="38" t="str">
         <x:v>Vários clientes ou usuários compartilham infraestrutura, memória ou dados?</x:v>
       </x:c>
-      <x:c r="D202" s="38" t="str"/>
+      <x:c r="D202" s="38"/>
       <x:c r="E202" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10386,7 +10348,7 @@
       <x:c r="C203" s="38" t="str">
         <x:v>Existem telas administrativas ou acessos com alto privilégio?</x:v>
       </x:c>
-      <x:c r="D203" s="38" t="str"/>
+      <x:c r="D203" s="38"/>
       <x:c r="E203" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10410,7 +10372,7 @@
       <x:c r="C204" s="38" t="str">
         <x:v>Existem telas administrativas ou acessos com alto privilégio?</x:v>
       </x:c>
-      <x:c r="D204" s="38" t="str"/>
+      <x:c r="D204" s="38"/>
       <x:c r="E204" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10434,7 +10396,7 @@
       <x:c r="C205" s="38" t="str">
         <x:v>Existem telas administrativas ou acessos com alto privilégio?</x:v>
       </x:c>
-      <x:c r="D205" s="38" t="str"/>
+      <x:c r="D205" s="38"/>
       <x:c r="E205" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10458,7 +10420,7 @@
       <x:c r="C206" s="38" t="str">
         <x:v>Quando uma verificação de segurança falha, a operação é bloqueada?</x:v>
       </x:c>
-      <x:c r="D206" s="38" t="str"/>
+      <x:c r="D206" s="38"/>
       <x:c r="E206" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10482,7 +10444,7 @@
       <x:c r="C207" s="38" t="str">
         <x:v>Quando uma verificação de segurança falha, a operação é bloqueada?</x:v>
       </x:c>
-      <x:c r="D207" s="38" t="str"/>
+      <x:c r="D207" s="38"/>
       <x:c r="E207" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10506,7 +10468,7 @@
       <x:c r="C208" s="38" t="str">
         <x:v>Quando uma verificação de segurança falha, a operação é bloqueada?</x:v>
       </x:c>
-      <x:c r="D208" s="38" t="str"/>
+      <x:c r="D208" s="38"/>
       <x:c r="E208" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10530,7 +10492,7 @@
       <x:c r="C209" s="38" t="str">
         <x:v>A solução consulta documentos ou uma base de conhecimento para responder?</x:v>
       </x:c>
-      <x:c r="D209" s="38" t="str"/>
+      <x:c r="D209" s="38"/>
       <x:c r="E209" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10554,7 +10516,7 @@
       <x:c r="C210" s="38" t="str">
         <x:v>A solução consulta documentos ou uma base de conhecimento para responder?</x:v>
       </x:c>
-      <x:c r="D210" s="38" t="str"/>
+      <x:c r="D210" s="38"/>
       <x:c r="E210" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10578,7 +10540,7 @@
       <x:c r="C211" s="38" t="str">
         <x:v>A solução consulta documentos ou uma base de conhecimento para responder?</x:v>
       </x:c>
-      <x:c r="D211" s="38" t="str"/>
+      <x:c r="D211" s="38"/>
       <x:c r="E211" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10602,7 +10564,7 @@
       <x:c r="C212" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D212" s="38" t="str"/>
+      <x:c r="D212" s="38"/>
       <x:c r="E212" s="38" t="str">
         <x:v>Repositórios internos</x:v>
       </x:c>
@@ -10626,7 +10588,7 @@
       <x:c r="C213" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D213" s="38" t="str"/>
+      <x:c r="D213" s="38"/>
       <x:c r="E213" s="38" t="str">
         <x:v>Upload de usuário</x:v>
       </x:c>
@@ -10650,7 +10612,7 @@
       <x:c r="C214" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D214" s="38" t="str"/>
+      <x:c r="D214" s="38"/>
       <x:c r="E214" s="38" t="str">
         <x:v>E-mail/chat</x:v>
       </x:c>
@@ -10674,7 +10636,7 @@
       <x:c r="C215" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D215" s="38" t="str"/>
+      <x:c r="D215" s="38"/>
       <x:c r="E215" s="38" t="str">
         <x:v>APIs</x:v>
       </x:c>
@@ -10698,7 +10660,7 @@
       <x:c r="C216" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D216" s="38" t="str"/>
+      <x:c r="D216" s="38"/>
       <x:c r="E216" s="38" t="str">
         <x:v>Internet</x:v>
       </x:c>
@@ -10722,7 +10684,7 @@
       <x:c r="C217" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D217" s="38" t="str"/>
+      <x:c r="D217" s="38"/>
       <x:c r="E217" s="38" t="str">
         <x:v>Terceiros</x:v>
       </x:c>
@@ -10746,7 +10708,7 @@
       <x:c r="C218" s="38" t="str">
         <x:v>De onde vêm os documentos e informações consultados?</x:v>
       </x:c>
-      <x:c r="D218" s="38" t="str"/>
+      <x:c r="D218" s="38"/>
       <x:c r="E218" s="38" t="str">
         <x:v>Outras</x:v>
       </x:c>
@@ -10770,7 +10732,7 @@
       <x:c r="C219" s="38" t="str">
         <x:v>A base recebe conteúdo da Internet, de usuários ou de fonte não confiável?</x:v>
       </x:c>
-      <x:c r="D219" s="38" t="str"/>
+      <x:c r="D219" s="38"/>
       <x:c r="E219" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10794,7 +10756,7 @@
       <x:c r="C220" s="38" t="str">
         <x:v>A base recebe conteúdo da Internet, de usuários ou de fonte não confiável?</x:v>
       </x:c>
-      <x:c r="D220" s="38" t="str"/>
+      <x:c r="D220" s="38"/>
       <x:c r="E220" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10818,7 +10780,7 @@
       <x:c r="C221" s="38" t="str">
         <x:v>A base recebe conteúdo da Internet, de usuários ou de fonte não confiável?</x:v>
       </x:c>
-      <x:c r="D221" s="38" t="str"/>
+      <x:c r="D221" s="38"/>
       <x:c r="E221" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10842,7 +10804,7 @@
       <x:c r="C222" s="38" t="str">
         <x:v>É possível identificar a origem e a versão de cada documento?</x:v>
       </x:c>
-      <x:c r="D222" s="38" t="str"/>
+      <x:c r="D222" s="38"/>
       <x:c r="E222" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10866,7 +10828,7 @@
       <x:c r="C223" s="38" t="str">
         <x:v>É possível identificar a origem e a versão de cada documento?</x:v>
       </x:c>
-      <x:c r="D223" s="38" t="str"/>
+      <x:c r="D223" s="38"/>
       <x:c r="E223" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10890,7 +10852,7 @@
       <x:c r="C224" s="38" t="str">
         <x:v>É possível identificar a origem e a versão de cada documento?</x:v>
       </x:c>
-      <x:c r="D224" s="38" t="str"/>
+      <x:c r="D224" s="38"/>
       <x:c r="E224" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10914,7 +10876,7 @@
       <x:c r="C225" s="38" t="str">
         <x:v>Arquivos e documentos são verificados antes de entrar na base?</x:v>
       </x:c>
-      <x:c r="D225" s="38" t="str"/>
+      <x:c r="D225" s="38"/>
       <x:c r="E225" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -10938,7 +10900,7 @@
       <x:c r="C226" s="38" t="str">
         <x:v>Arquivos e documentos são verificados antes de entrar na base?</x:v>
       </x:c>
-      <x:c r="D226" s="38" t="str"/>
+      <x:c r="D226" s="38"/>
       <x:c r="E226" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -10962,7 +10924,7 @@
       <x:c r="C227" s="38" t="str">
         <x:v>Arquivos e documentos são verificados antes de entrar na base?</x:v>
       </x:c>
-      <x:c r="D227" s="38" t="str"/>
+      <x:c r="D227" s="38"/>
       <x:c r="E227" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -10986,7 +10948,7 @@
       <x:c r="C228" s="38" t="str">
         <x:v>A solução verifica a permissão do usuário antes de recuperar cada documento?</x:v>
       </x:c>
-      <x:c r="D228" s="38" t="str"/>
+      <x:c r="D228" s="38"/>
       <x:c r="E228" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11010,7 +10972,7 @@
       <x:c r="C229" s="38" t="str">
         <x:v>A solução verifica a permissão do usuário antes de recuperar cada documento?</x:v>
       </x:c>
-      <x:c r="D229" s="38" t="str"/>
+      <x:c r="D229" s="38"/>
       <x:c r="E229" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11034,7 +10996,7 @@
       <x:c r="C230" s="38" t="str">
         <x:v>A solução verifica a permissão do usuário antes de recuperar cada documento?</x:v>
       </x:c>
-      <x:c r="D230" s="38" t="str"/>
+      <x:c r="D230" s="38"/>
       <x:c r="E230" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11058,7 +11020,7 @@
       <x:c r="C231" s="38" t="str">
         <x:v>Dados, memória e índices ficam separados entre usuários e clientes?</x:v>
       </x:c>
-      <x:c r="D231" s="38" t="str"/>
+      <x:c r="D231" s="38"/>
       <x:c r="E231" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11082,7 +11044,7 @@
       <x:c r="C232" s="38" t="str">
         <x:v>Dados, memória e índices ficam separados entre usuários e clientes?</x:v>
       </x:c>
-      <x:c r="D232" s="38" t="str"/>
+      <x:c r="D232" s="38"/>
       <x:c r="E232" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11106,7 +11068,7 @@
       <x:c r="C233" s="38" t="str">
         <x:v>Dados, memória e índices ficam separados entre usuários e clientes?</x:v>
       </x:c>
-      <x:c r="D233" s="38" t="str"/>
+      <x:c r="D233" s="38"/>
       <x:c r="E233" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11130,7 +11092,7 @@
       <x:c r="C234" s="38" t="str">
         <x:v>Quando um documento perde acesso ou é apagado, ele deixa de aparecer na IA?</x:v>
       </x:c>
-      <x:c r="D234" s="38" t="str"/>
+      <x:c r="D234" s="38"/>
       <x:c r="E234" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11154,7 +11116,7 @@
       <x:c r="C235" s="38" t="str">
         <x:v>Quando um documento perde acesso ou é apagado, ele deixa de aparecer na IA?</x:v>
       </x:c>
-      <x:c r="D235" s="38" t="str"/>
+      <x:c r="D235" s="38"/>
       <x:c r="E235" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11178,7 +11140,7 @@
       <x:c r="C236" s="38" t="str">
         <x:v>Quando um documento perde acesso ou é apagado, ele deixa de aparecer na IA?</x:v>
       </x:c>
-      <x:c r="D236" s="38" t="str"/>
+      <x:c r="D236" s="38"/>
       <x:c r="E236" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11202,7 +11164,7 @@
       <x:c r="C237" s="38" t="str">
         <x:v>A memória da solução tem prazo, limite e separação por usuário?</x:v>
       </x:c>
-      <x:c r="D237" s="38" t="str"/>
+      <x:c r="D237" s="38"/>
       <x:c r="E237" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11226,7 +11188,7 @@
       <x:c r="C238" s="38" t="str">
         <x:v>A memória da solução tem prazo, limite e separação por usuário?</x:v>
       </x:c>
-      <x:c r="D238" s="38" t="str"/>
+      <x:c r="D238" s="38"/>
       <x:c r="E238" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11250,7 +11212,7 @@
       <x:c r="C239" s="38" t="str">
         <x:v>A memória da solução tem prazo, limite e separação por usuário?</x:v>
       </x:c>
-      <x:c r="D239" s="38" t="str"/>
+      <x:c r="D239" s="38"/>
       <x:c r="E239" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11274,7 +11236,7 @@
       <x:c r="C240" s="38" t="str">
         <x:v>A resposta registra quais fontes foram realmente utilizadas?</x:v>
       </x:c>
-      <x:c r="D240" s="38" t="str"/>
+      <x:c r="D240" s="38"/>
       <x:c r="E240" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11298,7 +11260,7 @@
       <x:c r="C241" s="38" t="str">
         <x:v>A resposta registra quais fontes foram realmente utilizadas?</x:v>
       </x:c>
-      <x:c r="D241" s="38" t="str"/>
+      <x:c r="D241" s="38"/>
       <x:c r="E241" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11322,7 +11284,7 @@
       <x:c r="C242" s="38" t="str">
         <x:v>A resposta registra quais fontes foram realmente utilizadas?</x:v>
       </x:c>
-      <x:c r="D242" s="38" t="str"/>
+      <x:c r="D242" s="38"/>
       <x:c r="E242" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11346,7 +11308,7 @@
       <x:c r="C243" s="38" t="str">
         <x:v>Foram testados vazamento entre usuários, conteúdo malicioso e recuperação indevida?</x:v>
       </x:c>
-      <x:c r="D243" s="38" t="str"/>
+      <x:c r="D243" s="38"/>
       <x:c r="E243" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11370,7 +11332,7 @@
       <x:c r="C244" s="38" t="str">
         <x:v>Foram testados vazamento entre usuários, conteúdo malicioso e recuperação indevida?</x:v>
       </x:c>
-      <x:c r="D244" s="38" t="str"/>
+      <x:c r="D244" s="38"/>
       <x:c r="E244" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11394,7 +11356,7 @@
       <x:c r="C245" s="38" t="str">
         <x:v>Foram testados vazamento entre usuários, conteúdo malicioso e recuperação indevida?</x:v>
       </x:c>
-      <x:c r="D245" s="38" t="str"/>
+      <x:c r="D245" s="38"/>
       <x:c r="E245" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11418,7 +11380,7 @@
       <x:c r="C246" s="38" t="str">
         <x:v>A IA executa tarefas ou chama ferramentas automaticamente?</x:v>
       </x:c>
-      <x:c r="D246" s="38" t="str"/>
+      <x:c r="D246" s="38"/>
       <x:c r="E246" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11442,7 +11404,7 @@
       <x:c r="C247" s="38" t="str">
         <x:v>A IA executa tarefas ou chama ferramentas automaticamente?</x:v>
       </x:c>
-      <x:c r="D247" s="38" t="str"/>
+      <x:c r="D247" s="38"/>
       <x:c r="E247" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11466,7 +11428,7 @@
       <x:c r="C248" s="38" t="str">
         <x:v>A IA executa tarefas ou chama ferramentas automaticamente?</x:v>
       </x:c>
-      <x:c r="D248" s="38" t="str"/>
+      <x:c r="D248" s="38"/>
       <x:c r="E248" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11490,7 +11452,7 @@
       <x:c r="C249" s="38" t="str">
         <x:v>A solução usa MCP para conectar ferramentas ou fontes?</x:v>
       </x:c>
-      <x:c r="D249" s="38" t="str"/>
+      <x:c r="D249" s="38"/>
       <x:c r="E249" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11514,7 +11476,7 @@
       <x:c r="C250" s="38" t="str">
         <x:v>A solução usa MCP para conectar ferramentas ou fontes?</x:v>
       </x:c>
-      <x:c r="D250" s="38" t="str"/>
+      <x:c r="D250" s="38"/>
       <x:c r="E250" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11538,7 +11500,7 @@
       <x:c r="C251" s="38" t="str">
         <x:v>A solução usa MCP para conectar ferramentas ou fontes?</x:v>
       </x:c>
-      <x:c r="D251" s="38" t="str"/>
+      <x:c r="D251" s="38"/>
       <x:c r="E251" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11562,7 +11524,7 @@
       <x:c r="C252" s="38" t="str">
         <x:v>A IA controla navegador, computador, terminal ou executa código?</x:v>
       </x:c>
-      <x:c r="D252" s="38" t="str"/>
+      <x:c r="D252" s="38"/>
       <x:c r="E252" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11586,7 +11548,7 @@
       <x:c r="C253" s="38" t="str">
         <x:v>A IA controla navegador, computador, terminal ou executa código?</x:v>
       </x:c>
-      <x:c r="D253" s="38" t="str"/>
+      <x:c r="D253" s="38"/>
       <x:c r="E253" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11610,7 +11572,7 @@
       <x:c r="C254" s="38" t="str">
         <x:v>A IA controla navegador, computador, terminal ou executa código?</x:v>
       </x:c>
-      <x:c r="D254" s="38" t="str"/>
+      <x:c r="D254" s="38"/>
       <x:c r="E254" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11634,7 +11596,7 @@
       <x:c r="C255" s="38" t="str">
         <x:v>A quais sistemas, dados e operações o agente tem acesso?</x:v>
       </x:c>
-      <x:c r="D255" s="38" t="str"/>
+      <x:c r="D255" s="38"/>
       <x:c r="E255" s="38" t="str">
         <x:v>Texto preenchido</x:v>
       </x:c>
@@ -11658,7 +11620,7 @@
       <x:c r="C256" s="38" t="str">
         <x:v>O agente pode criar, alterar, excluir, aprovar, enviar, pagar ou conceder acesso?</x:v>
       </x:c>
-      <x:c r="D256" s="38" t="str"/>
+      <x:c r="D256" s="38"/>
       <x:c r="E256" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11682,7 +11644,7 @@
       <x:c r="C257" s="38" t="str">
         <x:v>O agente pode criar, alterar, excluir, aprovar, enviar, pagar ou conceder acesso?</x:v>
       </x:c>
-      <x:c r="D257" s="38" t="str"/>
+      <x:c r="D257" s="38"/>
       <x:c r="E257" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11706,7 +11668,7 @@
       <x:c r="C258" s="38" t="str">
         <x:v>O agente pode criar, alterar, excluir, aprovar, enviar, pagar ou conceder acesso?</x:v>
       </x:c>
-      <x:c r="D258" s="38" t="str"/>
+      <x:c r="D258" s="38"/>
       <x:c r="E258" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11730,7 +11692,7 @@
       <x:c r="C259" s="38" t="str">
         <x:v>Existe uma lista explícita das ferramentas e operações permitidas?</x:v>
       </x:c>
-      <x:c r="D259" s="38" t="str"/>
+      <x:c r="D259" s="38"/>
       <x:c r="E259" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11754,7 +11716,7 @@
       <x:c r="C260" s="38" t="str">
         <x:v>Existe uma lista explícita das ferramentas e operações permitidas?</x:v>
       </x:c>
-      <x:c r="D260" s="38" t="str"/>
+      <x:c r="D260" s="38"/>
       <x:c r="E260" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11778,7 +11740,7 @@
       <x:c r="C261" s="38" t="str">
         <x:v>Existe uma lista explícita das ferramentas e operações permitidas?</x:v>
       </x:c>
-      <x:c r="D261" s="38" t="str"/>
+      <x:c r="D261" s="38"/>
       <x:c r="E261" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11802,7 +11764,7 @@
       <x:c r="C262" s="38" t="str">
         <x:v>As ferramentas aceitam somente campos e formatos definidos?</x:v>
       </x:c>
-      <x:c r="D262" s="38" t="str"/>
+      <x:c r="D262" s="38"/>
       <x:c r="E262" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11826,7 +11788,7 @@
       <x:c r="C263" s="38" t="str">
         <x:v>As ferramentas aceitam somente campos e formatos definidos?</x:v>
       </x:c>
-      <x:c r="D263" s="38" t="str"/>
+      <x:c r="D263" s="38"/>
       <x:c r="E263" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11850,7 +11812,7 @@
       <x:c r="C264" s="38" t="str">
         <x:v>As ferramentas aceitam somente campos e formatos definidos?</x:v>
       </x:c>
-      <x:c r="D264" s="38" t="str"/>
+      <x:c r="D264" s="38"/>
       <x:c r="E264" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11874,7 +11836,7 @@
       <x:c r="C265" s="38" t="str">
         <x:v>Um controle independente da IA autoriza cada ação?</x:v>
       </x:c>
-      <x:c r="D265" s="38" t="str"/>
+      <x:c r="D265" s="38"/>
       <x:c r="E265" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11898,7 +11860,7 @@
       <x:c r="C266" s="38" t="str">
         <x:v>Um controle independente da IA autoriza cada ação?</x:v>
       </x:c>
-      <x:c r="D266" s="38" t="str"/>
+      <x:c r="D266" s="38"/>
       <x:c r="E266" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11922,7 +11884,7 @@
       <x:c r="C267" s="38" t="str">
         <x:v>Um controle independente da IA autoriza cada ação?</x:v>
       </x:c>
-      <x:c r="D267" s="38" t="str"/>
+      <x:c r="D267" s="38"/>
       <x:c r="E267" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -11946,7 +11908,7 @@
       <x:c r="C268" s="38" t="str">
         <x:v>O sistema final sabe qual pessoa pediu a ação?</x:v>
       </x:c>
-      <x:c r="D268" s="38" t="str"/>
+      <x:c r="D268" s="38"/>
       <x:c r="E268" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -11970,7 +11932,7 @@
       <x:c r="C269" s="38" t="str">
         <x:v>O sistema final sabe qual pessoa pediu a ação?</x:v>
       </x:c>
-      <x:c r="D269" s="38" t="str"/>
+      <x:c r="D269" s="38"/>
       <x:c r="E269" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -11994,7 +11956,7 @@
       <x:c r="C270" s="38" t="str">
         <x:v>O sistema final sabe qual pessoa pediu a ação?</x:v>
       </x:c>
-      <x:c r="D270" s="38" t="str"/>
+      <x:c r="D270" s="38"/>
       <x:c r="E270" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12018,7 +11980,7 @@
       <x:c r="C271" s="38" t="str">
         <x:v>Ações irreversíveis ou importantes exigem confirmação humana?</x:v>
       </x:c>
-      <x:c r="D271" s="38" t="str"/>
+      <x:c r="D271" s="38"/>
       <x:c r="E271" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12042,7 +12004,7 @@
       <x:c r="C272" s="38" t="str">
         <x:v>Ações irreversíveis ou importantes exigem confirmação humana?</x:v>
       </x:c>
-      <x:c r="D272" s="38" t="str"/>
+      <x:c r="D272" s="38"/>
       <x:c r="E272" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12066,7 +12028,7 @@
       <x:c r="C273" s="38" t="str">
         <x:v>Ações irreversíveis ou importantes exigem confirmação humana?</x:v>
       </x:c>
-      <x:c r="D273" s="38" t="str"/>
+      <x:c r="D273" s="38"/>
       <x:c r="E273" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12090,7 +12052,7 @@
       <x:c r="C274" s="38" t="str">
         <x:v>Existem limites para tempo, custo, quantidade de chamadas e ações?</x:v>
       </x:c>
-      <x:c r="D274" s="38" t="str"/>
+      <x:c r="D274" s="38"/>
       <x:c r="E274" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12114,7 +12076,7 @@
       <x:c r="C275" s="38" t="str">
         <x:v>Existem limites para tempo, custo, quantidade de chamadas e ações?</x:v>
       </x:c>
-      <x:c r="D275" s="38" t="str"/>
+      <x:c r="D275" s="38"/>
       <x:c r="E275" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12138,7 +12100,7 @@
       <x:c r="C276" s="38" t="str">
         <x:v>Existem limites para tempo, custo, quantidade de chamadas e ações?</x:v>
       </x:c>
-      <x:c r="D276" s="38" t="str"/>
+      <x:c r="D276" s="38"/>
       <x:c r="E276" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12162,7 +12124,7 @@
       <x:c r="C277" s="38" t="str">
         <x:v>É possível desligar rapidamente o agente ou uma ferramenta específica?</x:v>
       </x:c>
-      <x:c r="D277" s="38" t="str"/>
+      <x:c r="D277" s="38"/>
       <x:c r="E277" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12186,7 +12148,7 @@
       <x:c r="C278" s="38" t="str">
         <x:v>É possível desligar rapidamente o agente ou uma ferramenta específica?</x:v>
       </x:c>
-      <x:c r="D278" s="38" t="str"/>
+      <x:c r="D278" s="38"/>
       <x:c r="E278" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12210,7 +12172,7 @@
       <x:c r="C279" s="38" t="str">
         <x:v>É possível desligar rapidamente o agente ou uma ferramenta específica?</x:v>
       </x:c>
-      <x:c r="D279" s="38" t="str"/>
+      <x:c r="D279" s="38"/>
       <x:c r="E279" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12234,7 +12196,7 @@
       <x:c r="C280" s="38" t="str">
         <x:v>Código e controle do computador são executados em ambiente isolado?</x:v>
       </x:c>
-      <x:c r="D280" s="38" t="str"/>
+      <x:c r="D280" s="38"/>
       <x:c r="E280" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12258,7 +12220,7 @@
       <x:c r="C281" s="38" t="str">
         <x:v>Código e controle do computador são executados em ambiente isolado?</x:v>
       </x:c>
-      <x:c r="D281" s="38" t="str"/>
+      <x:c r="D281" s="38"/>
       <x:c r="E281" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12282,7 +12244,7 @@
       <x:c r="C282" s="38" t="str">
         <x:v>Código e controle do computador são executados em ambiente isolado?</x:v>
       </x:c>
-      <x:c r="D282" s="38" t="str"/>
+      <x:c r="D282" s="38"/>
       <x:c r="E282" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12306,7 +12268,7 @@
       <x:c r="C283" s="38" t="str">
         <x:v>Agentes secundários recebem somente as permissões necessárias?</x:v>
       </x:c>
-      <x:c r="D283" s="38" t="str"/>
+      <x:c r="D283" s="38"/>
       <x:c r="E283" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12330,7 +12292,7 @@
       <x:c r="C284" s="38" t="str">
         <x:v>Agentes secundários recebem somente as permissões necessárias?</x:v>
       </x:c>
-      <x:c r="D284" s="38" t="str"/>
+      <x:c r="D284" s="38"/>
       <x:c r="E284" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12354,7 +12316,7 @@
       <x:c r="C285" s="38" t="str">
         <x:v>Agentes secundários recebem somente as permissões necessárias?</x:v>
       </x:c>
-      <x:c r="D285" s="38" t="str"/>
+      <x:c r="D285" s="38"/>
       <x:c r="E285" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12378,7 +12340,7 @@
       <x:c r="C286" s="38" t="str">
         <x:v>A organização ou o fornecedor desenvolve ou implanta algum componente de IA?</x:v>
       </x:c>
-      <x:c r="D286" s="38" t="str"/>
+      <x:c r="D286" s="38"/>
       <x:c r="E286" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12402,7 +12364,7 @@
       <x:c r="C287" s="38" t="str">
         <x:v>A organização ou o fornecedor desenvolve ou implanta algum componente de IA?</x:v>
       </x:c>
-      <x:c r="D287" s="38" t="str"/>
+      <x:c r="D287" s="38"/>
       <x:c r="E287" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12426,7 +12388,7 @@
       <x:c r="C288" s="38" t="str">
         <x:v>A organização ou o fornecedor desenvolve ou implanta algum componente de IA?</x:v>
       </x:c>
-      <x:c r="D288" s="38" t="str"/>
+      <x:c r="D288" s="38"/>
       <x:c r="E288" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12450,7 +12412,7 @@
       <x:c r="C289" s="38" t="str">
         <x:v>Código, notebooks, prompts e configurações possuem controle de versão?</x:v>
       </x:c>
-      <x:c r="D289" s="38" t="str"/>
+      <x:c r="D289" s="38"/>
       <x:c r="E289" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12474,7 +12436,7 @@
       <x:c r="C290" s="38" t="str">
         <x:v>Código, notebooks, prompts e configurações possuem controle de versão?</x:v>
       </x:c>
-      <x:c r="D290" s="38" t="str"/>
+      <x:c r="D290" s="38"/>
       <x:c r="E290" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12498,7 +12460,7 @@
       <x:c r="C291" s="38" t="str">
         <x:v>Código, notebooks, prompts e configurações possuem controle de versão?</x:v>
       </x:c>
-      <x:c r="D291" s="38" t="str"/>
+      <x:c r="D291" s="38"/>
       <x:c r="E291" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12522,7 +12484,7 @@
       <x:c r="C292" s="38" t="str">
         <x:v>Os conjuntos de dados de treino e teste possuem versão e origem registradas?</x:v>
       </x:c>
-      <x:c r="D292" s="38" t="str"/>
+      <x:c r="D292" s="38"/>
       <x:c r="E292" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12546,7 +12508,7 @@
       <x:c r="C293" s="38" t="str">
         <x:v>Os conjuntos de dados de treino e teste possuem versão e origem registradas?</x:v>
       </x:c>
-      <x:c r="D293" s="38" t="str"/>
+      <x:c r="D293" s="38"/>
       <x:c r="E293" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12570,7 +12532,7 @@
       <x:c r="C294" s="38" t="str">
         <x:v>Os conjuntos de dados de treino e teste possuem versão e origem registradas?</x:v>
       </x:c>
-      <x:c r="D294" s="38" t="str"/>
+      <x:c r="D294" s="38"/>
       <x:c r="E294" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12594,7 +12556,7 @@
       <x:c r="C295" s="38" t="str">
         <x:v>Modelos e arquivos de IA vêm de fonte aprovada?</x:v>
       </x:c>
-      <x:c r="D295" s="38" t="str"/>
+      <x:c r="D295" s="38"/>
       <x:c r="E295" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12618,7 +12580,7 @@
       <x:c r="C296" s="38" t="str">
         <x:v>Modelos e arquivos de IA vêm de fonte aprovada?</x:v>
       </x:c>
-      <x:c r="D296" s="38" t="str"/>
+      <x:c r="D296" s="38"/>
       <x:c r="E296" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12642,7 +12604,7 @@
       <x:c r="C297" s="38" t="str">
         <x:v>Modelos e arquivos de IA vêm de fonte aprovada?</x:v>
       </x:c>
-      <x:c r="D297" s="38" t="str"/>
+      <x:c r="D297" s="38"/>
       <x:c r="E297" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12666,7 +12628,7 @@
       <x:c r="C298" s="38" t="str">
         <x:v>A integridade dos modelos e arquivos é verificada antes do uso?</x:v>
       </x:c>
-      <x:c r="D298" s="38" t="str"/>
+      <x:c r="D298" s="38"/>
       <x:c r="E298" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12690,7 +12652,7 @@
       <x:c r="C299" s="38" t="str">
         <x:v>A integridade dos modelos e arquivos é verificada antes do uso?</x:v>
       </x:c>
-      <x:c r="D299" s="38" t="str"/>
+      <x:c r="D299" s="38"/>
       <x:c r="E299" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12714,7 +12676,7 @@
       <x:c r="C300" s="38" t="str">
         <x:v>A integridade dos modelos e arquivos é verificada antes do uso?</x:v>
       </x:c>
-      <x:c r="D300" s="38" t="str"/>
+      <x:c r="D300" s="38"/>
       <x:c r="E300" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12738,7 +12700,7 @@
       <x:c r="C301" s="38" t="str">
         <x:v>Arquivos capazes de executar código são bloqueados ou abertos em ambiente isolado?</x:v>
       </x:c>
-      <x:c r="D301" s="38" t="str"/>
+      <x:c r="D301" s="38"/>
       <x:c r="E301" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12762,7 +12724,7 @@
       <x:c r="C302" s="38" t="str">
         <x:v>Arquivos capazes de executar código são bloqueados ou abertos em ambiente isolado?</x:v>
       </x:c>
-      <x:c r="D302" s="38" t="str"/>
+      <x:c r="D302" s="38"/>
       <x:c r="E302" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12786,7 +12748,7 @@
       <x:c r="C303" s="38" t="str">
         <x:v>Arquivos capazes de executar código são bloqueados ou abertos em ambiente isolado?</x:v>
       </x:c>
-      <x:c r="D303" s="38" t="str"/>
+      <x:c r="D303" s="38"/>
       <x:c r="E303" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12810,7 +12772,7 @@
       <x:c r="C304" s="38" t="str">
         <x:v>Cada versão possui inventário e verificação de componentes?</x:v>
       </x:c>
-      <x:c r="D304" s="38" t="str"/>
+      <x:c r="D304" s="38"/>
       <x:c r="E304" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12834,7 +12796,7 @@
       <x:c r="C305" s="38" t="str">
         <x:v>Cada versão possui inventário e verificação de componentes?</x:v>
       </x:c>
-      <x:c r="D305" s="38" t="str"/>
+      <x:c r="D305" s="38"/>
       <x:c r="E305" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12858,7 +12820,7 @@
       <x:c r="C306" s="38" t="str">
         <x:v>Cada versão possui inventário e verificação de componentes?</x:v>
       </x:c>
-      <x:c r="D306" s="38" t="str"/>
+      <x:c r="D306" s="38"/>
       <x:c r="E306" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12882,7 +12844,7 @@
       <x:c r="C307" s="38" t="str">
         <x:v>Build, teste e publicação usam acessos separados e ambientes temporários?</x:v>
       </x:c>
-      <x:c r="D307" s="38" t="str"/>
+      <x:c r="D307" s="38"/>
       <x:c r="E307" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12906,7 +12868,7 @@
       <x:c r="C308" s="38" t="str">
         <x:v>Build, teste e publicação usam acessos separados e ambientes temporários?</x:v>
       </x:c>
-      <x:c r="D308" s="38" t="str"/>
+      <x:c r="D308" s="38"/>
       <x:c r="E308" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -12930,7 +12892,7 @@
       <x:c r="C309" s="38" t="str">
         <x:v>Build, teste e publicação usam acessos separados e ambientes temporários?</x:v>
       </x:c>
-      <x:c r="D309" s="38" t="str"/>
+      <x:c r="D309" s="38"/>
       <x:c r="E309" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -12954,7 +12916,7 @@
       <x:c r="C310" s="38" t="str">
         <x:v>A mesma versão testada é promovida sem ser reconstruída?</x:v>
       </x:c>
-      <x:c r="D310" s="38" t="str"/>
+      <x:c r="D310" s="38"/>
       <x:c r="E310" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -12978,7 +12940,7 @@
       <x:c r="C311" s="38" t="str">
         <x:v>A mesma versão testada é promovida sem ser reconstruída?</x:v>
       </x:c>
-      <x:c r="D311" s="38" t="str"/>
+      <x:c r="D311" s="38"/>
       <x:c r="E311" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13002,7 +12964,7 @@
       <x:c r="C312" s="38" t="str">
         <x:v>A mesma versão testada é promovida sem ser reconstruída?</x:v>
       </x:c>
-      <x:c r="D312" s="38" t="str"/>
+      <x:c r="D312" s="38"/>
       <x:c r="E312" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13026,7 +12988,7 @@
       <x:c r="C313" s="38" t="str">
         <x:v>Os testes são executados exatamente sobre a versão que irá para produção?</x:v>
       </x:c>
-      <x:c r="D313" s="38" t="str"/>
+      <x:c r="D313" s="38"/>
       <x:c r="E313" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13050,7 +13012,7 @@
       <x:c r="C314" s="38" t="str">
         <x:v>Os testes são executados exatamente sobre a versão que irá para produção?</x:v>
       </x:c>
-      <x:c r="D314" s="38" t="str"/>
+      <x:c r="D314" s="38"/>
       <x:c r="E314" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13074,7 +13036,7 @@
       <x:c r="C315" s="38" t="str">
         <x:v>Os testes são executados exatamente sobre a versão que irá para produção?</x:v>
       </x:c>
-      <x:c r="D315" s="38" t="str"/>
+      <x:c r="D315" s="38"/>
       <x:c r="E315" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13098,7 +13060,7 @@
       <x:c r="C316" s="38" t="str">
         <x:v>É possível voltar rapidamente para uma versão segura anterior?</x:v>
       </x:c>
-      <x:c r="D316" s="38" t="str"/>
+      <x:c r="D316" s="38"/>
       <x:c r="E316" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13122,7 +13084,7 @@
       <x:c r="C317" s="38" t="str">
         <x:v>É possível voltar rapidamente para uma versão segura anterior?</x:v>
       </x:c>
-      <x:c r="D317" s="38" t="str"/>
+      <x:c r="D317" s="38"/>
       <x:c r="E317" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13146,7 +13108,7 @@
       <x:c r="C318" s="38" t="str">
         <x:v>É possível voltar rapidamente para uma versão segura anterior?</x:v>
       </x:c>
-      <x:c r="D318" s="38" t="str"/>
+      <x:c r="D318" s="38"/>
       <x:c r="E318" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13170,7 +13132,7 @@
       <x:c r="C319" s="38" t="str">
         <x:v>Atualizações automáticas são bloqueadas ou detectadas antes do uso?</x:v>
       </x:c>
-      <x:c r="D319" s="38" t="str"/>
+      <x:c r="D319" s="38"/>
       <x:c r="E319" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13194,7 +13156,7 @@
       <x:c r="C320" s="38" t="str">
         <x:v>Atualizações automáticas são bloqueadas ou detectadas antes do uso?</x:v>
       </x:c>
-      <x:c r="D320" s="38" t="str"/>
+      <x:c r="D320" s="38"/>
       <x:c r="E320" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13218,7 +13180,7 @@
       <x:c r="C321" s="38" t="str">
         <x:v>Atualizações automáticas são bloqueadas ou detectadas antes do uso?</x:v>
       </x:c>
-      <x:c r="D321" s="38" t="str"/>
+      <x:c r="D321" s="38"/>
       <x:c r="E321" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13242,7 +13204,7 @@
       <x:c r="C322" s="38" t="str">
         <x:v>Cada uso importante da IA gera registro de início, fim, decisão e resultado?</x:v>
       </x:c>
-      <x:c r="D322" s="38" t="str"/>
+      <x:c r="D322" s="38"/>
       <x:c r="E322" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13266,7 +13228,7 @@
       <x:c r="C323" s="38" t="str">
         <x:v>Cada uso importante da IA gera registro de início, fim, decisão e resultado?</x:v>
       </x:c>
-      <x:c r="D323" s="38" t="str"/>
+      <x:c r="D323" s="38"/>
       <x:c r="E323" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13290,7 +13252,7 @@
       <x:c r="C324" s="38" t="str">
         <x:v>Cada uso importante da IA gera registro de início, fim, decisão e resultado?</x:v>
       </x:c>
-      <x:c r="D324" s="38" t="str"/>
+      <x:c r="D324" s="38"/>
       <x:c r="E324" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13314,7 +13276,7 @@
       <x:c r="C325" s="38" t="str">
         <x:v>Os registros informam qual modelo, versão, usuário e ambiente foram usados?</x:v>
       </x:c>
-      <x:c r="D325" s="38" t="str"/>
+      <x:c r="D325" s="38"/>
       <x:c r="E325" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13338,7 +13300,7 @@
       <x:c r="C326" s="38" t="str">
         <x:v>Os registros informam qual modelo, versão, usuário e ambiente foram usados?</x:v>
       </x:c>
-      <x:c r="D326" s="38" t="str"/>
+      <x:c r="D326" s="38"/>
       <x:c r="E326" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13362,7 +13324,7 @@
       <x:c r="C327" s="38" t="str">
         <x:v>Os registros informam qual modelo, versão, usuário e ambiente foram usados?</x:v>
       </x:c>
-      <x:c r="D327" s="38" t="str"/>
+      <x:c r="D327" s="38"/>
       <x:c r="E327" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13386,7 +13348,7 @@
       <x:c r="C328" s="38" t="str">
         <x:v>É possível acompanhar uma solicitação do início ao fim?</x:v>
       </x:c>
-      <x:c r="D328" s="38" t="str"/>
+      <x:c r="D328" s="38"/>
       <x:c r="E328" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13410,7 +13372,7 @@
       <x:c r="C329" s="38" t="str">
         <x:v>É possível acompanhar uma solicitação do início ao fim?</x:v>
       </x:c>
-      <x:c r="D329" s="38" t="str"/>
+      <x:c r="D329" s="38"/>
       <x:c r="E329" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13434,7 +13396,7 @@
       <x:c r="C330" s="38" t="str">
         <x:v>É possível acompanhar uma solicitação do início ao fim?</x:v>
       </x:c>
-      <x:c r="D330" s="38" t="str"/>
+      <x:c r="D330" s="38"/>
       <x:c r="E330" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13458,7 +13420,7 @@
       <x:c r="C331" s="38" t="str">
         <x:v>Prompts, respostas e documentos deixam de ser gravados por inteiro por padrão?</x:v>
       </x:c>
-      <x:c r="D331" s="38" t="str"/>
+      <x:c r="D331" s="38"/>
       <x:c r="E331" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13482,7 +13444,7 @@
       <x:c r="C332" s="38" t="str">
         <x:v>Prompts, respostas e documentos deixam de ser gravados por inteiro por padrão?</x:v>
       </x:c>
-      <x:c r="D332" s="38" t="str"/>
+      <x:c r="D332" s="38"/>
       <x:c r="E332" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13506,7 +13468,7 @@
       <x:c r="C333" s="38" t="str">
         <x:v>Prompts, respostas e documentos deixam de ser gravados por inteiro por padrão?</x:v>
       </x:c>
-      <x:c r="D333" s="38" t="str"/>
+      <x:c r="D333" s="38"/>
       <x:c r="E333" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13530,7 +13492,7 @@
       <x:c r="C334" s="38" t="str">
         <x:v>Senhas, tokens e dados sensíveis são ocultados antes de entrar nos registros?</x:v>
       </x:c>
-      <x:c r="D334" s="38" t="str"/>
+      <x:c r="D334" s="38"/>
       <x:c r="E334" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13554,7 +13516,7 @@
       <x:c r="C335" s="38" t="str">
         <x:v>Senhas, tokens e dados sensíveis são ocultados antes de entrar nos registros?</x:v>
       </x:c>
-      <x:c r="D335" s="38" t="str"/>
+      <x:c r="D335" s="38"/>
       <x:c r="E335" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13578,7 +13540,7 @@
       <x:c r="C336" s="38" t="str">
         <x:v>Senhas, tokens e dados sensíveis são ocultados antes de entrar nos registros?</x:v>
       </x:c>
-      <x:c r="D336" s="38" t="str"/>
+      <x:c r="D336" s="38"/>
       <x:c r="E336" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13602,7 +13564,7 @@
       <x:c r="C337" s="38" t="str">
         <x:v>Eventos importantes chegam à equipe de segurança e não podem ser apagados facilmente?</x:v>
       </x:c>
-      <x:c r="D337" s="38" t="str"/>
+      <x:c r="D337" s="38"/>
       <x:c r="E337" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13626,7 +13588,7 @@
       <x:c r="C338" s="38" t="str">
         <x:v>Eventos importantes chegam à equipe de segurança e não podem ser apagados facilmente?</x:v>
       </x:c>
-      <x:c r="D338" s="38" t="str"/>
+      <x:c r="D338" s="38"/>
       <x:c r="E338" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13650,7 +13612,7 @@
       <x:c r="C339" s="38" t="str">
         <x:v>Eventos importantes chegam à equipe de segurança e não podem ser apagados facilmente?</x:v>
       </x:c>
-      <x:c r="D339" s="38" t="str"/>
+      <x:c r="D339" s="38"/>
       <x:c r="E339" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13674,7 +13636,7 @@
       <x:c r="C340" s="38" t="str">
         <x:v>Existem alertas específicos para ataques e vazamentos envolvendo IA?</x:v>
       </x:c>
-      <x:c r="D340" s="38" t="str"/>
+      <x:c r="D340" s="38"/>
       <x:c r="E340" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13698,7 +13660,7 @@
       <x:c r="C341" s="38" t="str">
         <x:v>Existem alertas específicos para ataques e vazamentos envolvendo IA?</x:v>
       </x:c>
-      <x:c r="D341" s="38" t="str"/>
+      <x:c r="D341" s="38"/>
       <x:c r="E341" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13722,7 +13684,7 @@
       <x:c r="C342" s="38" t="str">
         <x:v>Existem alertas específicos para ataques e vazamentos envolvendo IA?</x:v>
       </x:c>
-      <x:c r="D342" s="38" t="str"/>
+      <x:c r="D342" s="38"/>
       <x:c r="E342" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13746,7 +13708,7 @@
       <x:c r="C343" s="38" t="str">
         <x:v>A solução monitora aumento anormal de uso, custo, erros e mudanças?</x:v>
       </x:c>
-      <x:c r="D343" s="38" t="str"/>
+      <x:c r="D343" s="38"/>
       <x:c r="E343" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13770,7 +13732,7 @@
       <x:c r="C344" s="38" t="str">
         <x:v>A solução monitora aumento anormal de uso, custo, erros e mudanças?</x:v>
       </x:c>
-      <x:c r="D344" s="38" t="str"/>
+      <x:c r="D344" s="38"/>
       <x:c r="E344" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13794,7 +13756,7 @@
       <x:c r="C345" s="38" t="str">
         <x:v>A solução monitora aumento anormal de uso, custo, erros e mudanças?</x:v>
       </x:c>
-      <x:c r="D345" s="38" t="str"/>
+      <x:c r="D345" s="38"/>
       <x:c r="E345" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13818,7 +13780,7 @@
       <x:c r="C346" s="38" t="str">
         <x:v>A solução interrompe chamadas repetidas ou falhas antes de causar dano?</x:v>
       </x:c>
-      <x:c r="D346" s="38" t="str"/>
+      <x:c r="D346" s="38"/>
       <x:c r="E346" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13842,7 +13804,7 @@
       <x:c r="C347" s="38" t="str">
         <x:v>A solução interrompe chamadas repetidas ou falhas antes de causar dano?</x:v>
       </x:c>
-      <x:c r="D347" s="38" t="str"/>
+      <x:c r="D347" s="38"/>
       <x:c r="E347" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13866,7 +13828,7 @@
       <x:c r="C348" s="38" t="str">
         <x:v>A solução interrompe chamadas repetidas ou falhas antes de causar dano?</x:v>
       </x:c>
-      <x:c r="D348" s="38" t="str"/>
+      <x:c r="D348" s="38"/>
       <x:c r="E348" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13890,7 +13852,7 @@
       <x:c r="C349" s="38" t="str">
         <x:v>Configurações e componentes importantes possuem backup testado?</x:v>
       </x:c>
-      <x:c r="D349" s="38" t="str"/>
+      <x:c r="D349" s="38"/>
       <x:c r="E349" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13914,7 +13876,7 @@
       <x:c r="C350" s="38" t="str">
         <x:v>Configurações e componentes importantes possuem backup testado?</x:v>
       </x:c>
-      <x:c r="D350" s="38" t="str"/>
+      <x:c r="D350" s="38"/>
       <x:c r="E350" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -13938,7 +13900,7 @@
       <x:c r="C351" s="38" t="str">
         <x:v>Configurações e componentes importantes possuem backup testado?</x:v>
       </x:c>
-      <x:c r="D351" s="38" t="str"/>
+      <x:c r="D351" s="38"/>
       <x:c r="E351" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -13962,7 +13924,7 @@
       <x:c r="C352" s="38" t="str">
         <x:v>Existe orientação prática para responder a incidente de IA?</x:v>
       </x:c>
-      <x:c r="D352" s="38" t="str"/>
+      <x:c r="D352" s="38"/>
       <x:c r="E352" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -13986,7 +13948,7 @@
       <x:c r="C353" s="38" t="str">
         <x:v>Existe orientação prática para responder a incidente de IA?</x:v>
       </x:c>
-      <x:c r="D353" s="38" t="str"/>
+      <x:c r="D353" s="38"/>
       <x:c r="E353" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -14010,7 +13972,7 @@
       <x:c r="C354" s="38" t="str">
         <x:v>Existe orientação prática para responder a incidente de IA?</x:v>
       </x:c>
-      <x:c r="D354" s="38" t="str"/>
+      <x:c r="D354" s="38"/>
       <x:c r="E354" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -14034,7 +13996,7 @@
       <x:c r="C355" s="38" t="str">
         <x:v>É possível revogar rapidamente credenciais, tokens e sessões?</x:v>
       </x:c>
-      <x:c r="D355" s="38" t="str"/>
+      <x:c r="D355" s="38"/>
       <x:c r="E355" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -14058,7 +14020,7 @@
       <x:c r="C356" s="38" t="str">
         <x:v>É possível revogar rapidamente credenciais, tokens e sessões?</x:v>
       </x:c>
-      <x:c r="D356" s="38" t="str"/>
+      <x:c r="D356" s="38"/>
       <x:c r="E356" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -14082,7 +14044,7 @@
       <x:c r="C357" s="38" t="str">
         <x:v>É possível revogar rapidamente credenciais, tokens e sessões?</x:v>
       </x:c>
-      <x:c r="D357" s="38" t="str"/>
+      <x:c r="D357" s="38"/>
       <x:c r="E357" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -14106,7 +14068,7 @@
       <x:c r="C358" s="38" t="str">
         <x:v>Ao desativar a solução, rotas, acessos e dados operacionais são removidos?</x:v>
       </x:c>
-      <x:c r="D358" s="38" t="str"/>
+      <x:c r="D358" s="38"/>
       <x:c r="E358" s="38" t="str">
         <x:v>Sim</x:v>
       </x:c>
@@ -14130,7 +14092,7 @@
       <x:c r="C359" s="38" t="str">
         <x:v>Ao desativar a solução, rotas, acessos e dados operacionais são removidos?</x:v>
       </x:c>
-      <x:c r="D359" s="38" t="str"/>
+      <x:c r="D359" s="38"/>
       <x:c r="E359" s="38" t="str">
         <x:v>Não</x:v>
       </x:c>
@@ -14154,7 +14116,7 @@
       <x:c r="C360" s="38" t="str">
         <x:v>Ao desativar a solução, rotas, acessos e dados operacionais são removidos?</x:v>
       </x:c>
-      <x:c r="D360" s="38" t="str"/>
+      <x:c r="D360" s="38"/>
       <x:c r="E360" s="38" t="str">
         <x:v>Não sei</x:v>
       </x:c>
@@ -14265,9 +14227,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K2" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L2" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14310,9 +14271,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K3" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L3" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14354,9 +14314,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K4" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L4" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14397,9 +14356,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K5" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L5" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14440,9 +14398,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K6" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L6" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14484,9 +14441,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K7" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L7" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14527,9 +14483,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K8" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L8" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14571,12 +14526,11 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K9" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L9" s="38" t="str">
-        <x:v>MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.</x:v>
+        <x:v>MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -14615,14 +14569,13 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K10" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L10" s="38" t="str">
-        <x:v>MTR2-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
-MTR2-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.</x:v>
+        <x:v>MTR1-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
+MTR1-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -14660,9 +14613,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K11" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L11" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14703,9 +14655,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K12" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L12" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14747,9 +14698,8 @@
         <x:v>Registro do projeto, solicitação, contrato, cronograma, arquitetura ou contato do responsável.</x:v>
       </x:c>
       <x:c r="K13" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 3. Identificação da avaliação
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L13" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14795,16 +14745,15 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K14" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L14" s="38" t="str">
-        <x:v>MTR2-B001 — BAS-001: Qualquer uso corporativo, projeto, produto, sistema, serviço ou funcionalidade que utilize IA.
-MTR2-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
-MTR2-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
-MTR2-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
-MTR2-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.</x:v>
+        <x:v>MTR1-B001 — BAS-001: Qualquer uso corporativo, projeto, produto, sistema, serviço ou funcionalidade que utilize IA.
+MTR1-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
+MTR1-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
+MTR1-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
+MTR1-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -14844,12 +14793,11 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K15" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L15" s="38" t="str">
-        <x:v>MTR2-B001 — BAS-001: Qualquer uso corporativo, projeto, produto, sistema, serviço ou funcionalidade que utilize IA.</x:v>
+        <x:v>MTR1-B001 — BAS-001: Qualquer uso corporativo, projeto, produto, sistema, serviço ou funcionalidade que utilize IA.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -14889,9 +14837,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K16" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L16" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14933,9 +14880,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K17" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L17" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -14977,15 +14923,14 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K18" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L18" s="38" t="str">
-        <x:v>MTR2-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
-MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.
-MTR2-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.</x:v>
+        <x:v>MTR1-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
+MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.
+MTR1-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -15023,9 +14968,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K19" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L19" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15066,14 +15010,13 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K20" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L20" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.
-MTR2-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.
+MTR1-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -15111,9 +15054,8 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K21" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L21" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15155,16 +15097,15 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K22" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L22" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B004-S06 — BAS-004, 6. Sandbox, host, navegador e computer use: Quando houver execução de código, terminal, navegador, desktop, IDE, endpoint ou computer use.
-MTR2-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.
-MTR2-B005-L2
-MTR2-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B004-S06 — BAS-004, 6. Sandbox, host, navegador e computer use: Quando houver execução de código, terminal, navegador, desktop, IDE, endpoint ou computer use.
+MTR1-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.
+MTR1-B005-L2
+MTR1-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -15203,15 +15144,14 @@
         <x:v>Arquitetura, inventário de componentes, proposta técnica, catálogo de modelos ou descrição do serviço.</x:v>
       </x:c>
       <x:c r="K23" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 4. Cenário de uso e modelo de fornecimento
-MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6 — Identificação do cenário e das responsabilidades; § 7 — Classificação H1–H4; § 11 — Seleção dos baselines e controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L23" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.
-MTR2-B005-S01 — BAS-005, 1. Repositórios, código e versionamento: Quando código, notebook, prompt, policy, manifesto ou configuração for desenvolvido ou mantido para a solução.
-MTR2-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.
+MTR1-B005-S01 — BAS-005, 1. Repositórios, código e versionamento: Quando código, notebook, prompt, policy, manifesto ou configuração for desenvolvido ou mantido para a solução.
+MTR1-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -15249,9 +15189,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K24" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L24" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15292,9 +15231,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K25" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L25" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15337,9 +15275,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K26" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L26" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15382,13 +15319,12 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K27" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L27" s="38" t="str">
-        <x:v>MTR2-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
-MTR2-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.</x:v>
+        <x:v>MTR1-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
+MTR1-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -15428,13 +15364,12 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K28" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L28" s="38" t="str">
-        <x:v>MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.</x:v>
+        <x:v>MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -15474,14 +15409,13 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K29" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L29" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.
-MTR2-B006-S04 — BAS-006, 4. Coleta, transporte e integração com SIEM: Quando eventos forem enviados a collector, broker, data lake, APM, SIEM ou SOC.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.
+MTR1-B006-S04 — BAS-006, 4. Coleta, transporte e integração com SIEM: Quando eventos forem enviados a collector, broker, data lake, APM, SIEM ou SOC.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -15521,12 +15455,11 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K30" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L30" s="38" t="str">
-        <x:v>MTR2-B005-S06 — BAS-005, 6. Testes, evals e critérios técnicos de release: Quando releases, modelos, prompts ou soluções forem avaliados antes da promoção ou contratação.</x:v>
+        <x:v>MTR1-B005-S06 — BAS-005, 6. Testes, evals e critérios técnicos de release: Quando releases, modelos, prompts ou soluções forem avaliados antes da promoção ou contratação.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -15566,9 +15499,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K31" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L31" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15611,9 +15543,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K32" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L32" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15656,14 +15587,13 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K33" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L33" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -15703,15 +15633,14 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K34" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L34" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.
-MTR2-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.
+MTR1-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -15751,9 +15680,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K35" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L35" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15796,9 +15724,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K36" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L36" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15840,9 +15767,8 @@
         <x:v>Contrato, DPA, questionário do fornecedor, relatório de auditoria, SLA, certificação ou documentação oficial.</x:v>
       </x:c>
       <x:c r="K37" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 5. Terceiros, SaaS, COTS e serviços gerenciados
-MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 6.2 — Modelo de responsabilidade; § 9 — Probabilidade; § 9.1 — Pisos obrigatórios; § 12 — Avaliação dos controles
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L37" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -15885,15 +15811,14 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K38" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L38" s="38" t="str">
-        <x:v>MTR2-B001 — BAS-001: Qualquer uso corporativo, projeto, produto, sistema, serviço ou funcionalidade que utilize IA.
-MTR2-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
-MTR2-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.</x:v>
+        <x:v>MTR1-B001 — BAS-001: Qualquer uso corporativo, projeto, produto, sistema, serviço ou funcionalidade que utilize IA.
+MTR1-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
+MTR1-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -15931,14 +15856,13 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K39" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L39" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
-MTR2-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
+MTR1-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -15978,13 +15902,12 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K40" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L40" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -16024,13 +15947,12 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K41" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L41" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -16070,12 +15992,11 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K42" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L42" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -16115,13 +16036,12 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K43" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L43" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -16161,13 +16081,12 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K44" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L44" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -16207,14 +16126,13 @@
         <x:v>Inventário de dados, fluxo de dados, classificação, amostras mascaradas, política de retenção ou configuração de DLP.</x:v>
       </x:c>
       <x:c r="K45" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 6. Dados, privacidade e sigilo
-MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L45" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
-MTR2-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
+MTR1-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -16252,12 +16170,11 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K46" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L46" s="38" t="str">
-        <x:v>MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.</x:v>
+        <x:v>MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -16297,19 +16214,18 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K47" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L47" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
-MTR2-B002-L2
-MTR2-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.
-MTR2-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B006-L2</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
+MTR1-B002-L2
+MTR1-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.
+MTR1-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B006-L2</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -16349,14 +16265,13 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K48" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L48" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -16396,15 +16311,14 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K49" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L49" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B003-L2</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B003-L2</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -16444,17 +16358,16 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K50" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L50" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B002-L2
-MTR2-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B004-L2
-MTR2-B006-L2</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B002-L2
+MTR1-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B004-L2
+MTR1-B006-L2</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -16494,18 +16407,17 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K51" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L51" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B002-L2
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B003-L2
-MTR2-B004-L2
-MTR2-B005-L2
-MTR2-B006-L2</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B002-L2
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B003-L2
+MTR1-B004-L2
+MTR1-B005-L2
+MTR1-B006-L2</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -16545,15 +16457,14 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K52" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L52" s="38" t="str">
-        <x:v>MTR2-B002-L2
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B006-L2
-MTR2-B006-S06 — BAS-006, 6. Anomalias de comportamento, custo e desempenho: Quando volume, custo, tokens, loops, drift, falha, latência ou saturação precisarem ser monitorados.</x:v>
+        <x:v>MTR1-B002-L2
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B006-L2
+MTR1-B006-S06 — BAS-006, 6. Anomalias de comportamento, custo e desempenho: Quando volume, custo, tokens, loops, drift, falha, latência ou saturação precisarem ser monitorados.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -16593,9 +16504,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K53" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L53" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -16638,9 +16548,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K54" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L54" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -16683,14 +16592,13 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K55" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L55" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -16730,13 +16638,12 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K56" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle</x:v>
       </x:c>
       <x:c r="L56" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -16774,9 +16681,8 @@
         <x:v>Descrição do processo, jornada do usuário, análise de impacto, regras de decisão, fallback e procedimento de contestação.</x:v>
       </x:c>
       <x:c r="K57" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 7. Usuários, exposição e impacto de negócio
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
-MTR-002 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Cálculo do impacto; § 9 — Cálculo da probabilidade
+MTR-001 v1.0 — § 6 Fluxo de decisão; § 10 Regra individual de controle</x:v>
       </x:c>
       <x:c r="L57" s="38" t="str">
         <x:v>Sem regra individual.</x:v>
@@ -16819,18 +16725,17 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K58" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L58" s="38" t="str">
-        <x:v>MTR2-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
-MTR2-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.
-MTR2-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.</x:v>
+        <x:v>MTR1-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
+MTR1-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.
+MTR1-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -16870,18 +16775,17 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K59" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L59" s="38" t="str">
-        <x:v>MTR2-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
-MTR2-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.
-MTR2-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.</x:v>
+        <x:v>MTR1-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002 — BAS-002: Aplicação, API, gateway, proxy, broker, roteamento, integração com provider ou exposição de capacidade de IA.
+MTR1-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.
+MTR1-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -16921,16 +16825,15 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K60" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L60" s="38" t="str">
-        <x:v>MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.</x:v>
+        <x:v>MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -16970,17 +16873,16 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K61" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L61" s="38" t="str">
-        <x:v>MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.
-MTR2-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.</x:v>
+        <x:v>MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.
+MTR1-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -17020,18 +16922,17 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K62" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L62" s="38" t="str">
-        <x:v>MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.
-MTR2-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.
-MTR2-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
+        <x:v>MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S02 — BAS-002, 2. Autenticação e identidade: Quando usuários, workloads ou clientes acessarem aplicação, API, gateway ou provider.
+MTR1-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.
+MTR1-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -17071,15 +16972,14 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K63" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L63" s="38" t="str">
-        <x:v>MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.</x:v>
+        <x:v>MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -17117,16 +17017,15 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K64" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L64" s="38" t="str">
-        <x:v>MTR2-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.</x:v>
+        <x:v>MTR1-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -17166,16 +17065,15 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K65" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L65" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -17215,16 +17113,15 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K66" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L66" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -17264,16 +17161,15 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K67" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L67" s="38" t="str">
-        <x:v>MTR2-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.</x:v>
+        <x:v>MTR1-B001-S01 — BAS-001, 1. Arquitetura e configuração segura: Sempre que houver componente, deployment, endpoint, runtime, gateway ou ambiente de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S01 — BAS-002, 1. Arquitetura de integração e fronteiras: Quando houver consumo, intermediação, roteamento ou exposição de serviço de IA.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -17313,19 +17209,18 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K68" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L68" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-L2
-MTR2-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-L2
+MTR1-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -17365,19 +17260,18 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K69" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L69" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-L2
-MTR2-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
-MTR2-B004-L2</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-L2
+MTR1-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
+MTR1-B004-L2</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -17417,17 +17311,16 @@
         <x:v>Diagrama, configuração de gateway, IAM, rede, secrets, policy, teste negativo ou exportação de configuração.</x:v>
       </x:c>
       <x:c r="K70" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 8. Arquitetura, integração, identidade e acesso
-MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos baselines e controles; § 12 — Avaliação dos controles; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-001 — Controles Técnicos Transversais
 BAS-002 — Integração e Exposição</x:v>
       </x:c>
       <x:c r="L70" s="38" t="str">
-        <x:v>MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
-MTR2-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
-MTR2-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
+        <x:v>MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B002-S03 — BAS-002, 3. Autorização e segregação: Quando houver múltiplos usuários, tenants, ambientes, privilégios, recursos ou políticas de autorização.
+MTR1-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
+MTR1-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -17467,15 +17360,14 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K71" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L71" s="38" t="str">
-        <x:v>MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
-MTR2-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.</x:v>
+        <x:v>MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
+MTR1-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -17514,14 +17406,13 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K72" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L72" s="38" t="str">
-        <x:v>MTR2-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
-MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.</x:v>
+        <x:v>MTR1-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
+MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -17561,18 +17452,17 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K73" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L73" s="38" t="str">
-        <x:v>MTR2-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
-MTR2-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
-MTR2-B003-L2
-MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
-MTR2-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.
-MTR2-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
+        <x:v>MTR1-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
+MTR1-B003 — BAS-003: RAG, embeddings, vector store, memória, cache semântico, base de conhecimento, ingestão ou recuperação de contexto.
+MTR1-B003-L2
+MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
+MTR1-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.
+MTR1-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -17612,14 +17502,13 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K74" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L74" s="38" t="str">
-        <x:v>MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
-MTR2-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.</x:v>
+        <x:v>MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
+MTR1-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -17659,15 +17548,14 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K75" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L75" s="38" t="str">
-        <x:v>MTR2-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
-MTR2-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.
-MTR2-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.</x:v>
+        <x:v>MTR1-B003-S01 — BAS-003, 1. Fontes, ingestão e elegibilidade: Quando fontes, uploads, conectores, APIs, Internet ou terceiros alimentarem contexto ou conhecimento.
+MTR1-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.
+MTR1-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -17707,15 +17595,14 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K76" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L76" s="38" t="str">
-        <x:v>MTR2-B003-L2
-MTR2-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.
-MTR2-B003-S05 — BAS-003, 5. Retrieval, ranking e montagem de contexto: Quando o sistema recuperar, ranquear, filtrar ou montar contexto para o modelo.</x:v>
+        <x:v>MTR1-B003-L2
+MTR1-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.
+MTR1-B003-S05 — BAS-003, 5. Retrieval, ranking e montagem de contexto: Quando o sistema recuperar, ranquear, filtrar ou montar contexto para o modelo.</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -17755,16 +17642,15 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K77" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L77" s="38" t="str">
-        <x:v>MTR2-B003-L2
-MTR2-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.
-MTR2-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.
-MTR2-B003-S07 — BAS-003, 7. Memória, caches e dados derivados em execução: Quando houver memória persistente, cache semântico, estado conversacional ou compartilhamento de contexto.</x:v>
+        <x:v>MTR1-B003-L2
+MTR1-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.
+MTR1-B003-S04 — BAS-003, 4. Autorização, segregação e recuperação permitida: Quando dados ou documentos possuírem escopo por usuário, grupo, tenant, classificação ou autorização.
+MTR1-B003-S07 — BAS-003, 7. Memória, caches e dados derivados em execução: Quando houver memória persistente, cache semântico, estado conversacional ou compartilhamento de contexto.</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -17804,14 +17690,13 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K78" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L78" s="38" t="str">
-        <x:v>MTR2-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.
-MTR2-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.</x:v>
+        <x:v>MTR1-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.
+MTR1-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -17851,15 +17736,14 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K79" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L79" s="38" t="str">
-        <x:v>MTR2-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.
-MTR2-B003-S07 — BAS-003, 7. Memória, caches e dados derivados em execução: Quando houver memória persistente, cache semântico, estado conversacional ou compartilhamento de contexto.
-MTR2-B004-S07 — BAS-004, 7. Memória, delegação e comunicação entre agentes: Quando houver memória agentic, agentes secundários, delegação, comunicação multiagente ou contexto persistente.</x:v>
+        <x:v>MTR1-B003-S03 — BAS-003, 3. Embeddings, índices e armazenamento: Quando houver embeddings, índices, vector stores, caches, memória ou armazenamento de derivados.
+MTR1-B003-S07 — BAS-003, 7. Memória, caches e dados derivados em execução: Quando houver memória persistente, cache semântico, estado conversacional ou compartilhamento de contexto.
+MTR1-B004-S07 — BAS-004, 7. Memória, delegação e comunicação entre agentes: Quando houver memória agentic, agentes secundários, delegação, comunicação multiagente ou contexto persistente.</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -17899,15 +17783,14 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K80" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L80" s="38" t="str">
-        <x:v>MTR2-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.
-MTR2-B003-S05 — BAS-003, 5. Retrieval, ranking e montagem de contexto: Quando o sistema recuperar, ranquear, filtrar ou montar contexto para o modelo.
-MTR2-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
+        <x:v>MTR1-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.
+MTR1-B003-S05 — BAS-003, 5. Retrieval, ranking e montagem de contexto: Quando o sistema recuperar, ranquear, filtrar ou montar contexto para o modelo.
+MTR1-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -17947,15 +17830,14 @@
         <x:v>Manifesto de fontes, ACLs, configuração de ingestão, índices, testes de retrieval, lineage ou logs de recuperação.</x:v>
       </x:c>
       <x:c r="K81" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 9. RAG, memória e bases de conhecimento — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-003 — Dados, Contexto e Conhecimento</x:v>
       </x:c>
       <x:c r="L81" s="38" t="str">
-        <x:v>MTR2-B003-S05 — BAS-003, 5. Retrieval, ranking e montagem de contexto: Quando o sistema recuperar, ranquear, filtrar ou montar contexto para o modelo.
-MTR2-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.
-MTR2-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.</x:v>
+        <x:v>MTR1-B003-S05 — BAS-003, 5. Retrieval, ranking e montagem de contexto: Quando o sistema recuperar, ranquear, filtrar ou montar contexto para o modelo.
+MTR1-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.
+MTR1-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -17995,18 +17877,17 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K82" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L82" s="38" t="str">
-        <x:v>MTR2-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
-MTR2-B003-L2
-MTR2-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
-MTR2-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.
-MTR2-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
-MTR2-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
+        <x:v>MTR1-B001-S05 — BAS-001, 5. Segurança de aplicação e integrações: Quando houver aplicação consumidora, API, integração, sessão, payload, gateway, RAG ou agente.
+MTR1-B003-L2
+MTR1-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
+MTR1-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.
+MTR1-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
+MTR1-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -18046,15 +17927,14 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K83" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L83" s="38" t="str">
-        <x:v>MTR2-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
-MTR2-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
-MTR2-B004-S04 — BAS-004, 4. Segurança de clientes, servidores e registries MCP: Quando houver cliente, servidor, registry, discovery, resource ou prompt MCP.</x:v>
+        <x:v>MTR1-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
+MTR1-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
+MTR1-B004-S04 — BAS-004, 4. Segurança de clientes, servidores e registries MCP: Quando houver cliente, servidor, registry, discovery, resource ou prompt MCP.</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -18094,16 +17974,15 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K84" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L84" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
-MTR2-B004-L2
-MTR2-B004-S06 — BAS-004, 6. Sandbox, host, navegador e computer use: Quando houver execução de código, terminal, navegador, desktop, IDE, endpoint ou computer use.</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B004 — BAS-004: Agente, planner, executor, tool/function calling, plugin, action, skill, MCP, computer use ou automação acionada por IA.
+MTR1-B004-L2
+MTR1-B004-S06 — BAS-004, 6. Sandbox, host, navegador e computer use: Quando houver execução de código, terminal, navegador, desktop, IDE, endpoint ou computer use.</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -18141,13 +18020,12 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K85" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L85" s="38" t="str">
-        <x:v>MTR2-B004-S07 — BAS-004, 7. Memória, delegação e comunicação entre agentes: Quando houver memória agentic, agentes secundários, delegação, comunicação multiagente ou contexto persistente.</x:v>
+        <x:v>MTR1-B004-S07 — BAS-004, 7. Memória, delegação e comunicação entre agentes: Quando houver memória agentic, agentes secundários, delegação, comunicação multiagente ou contexto persistente.</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -18187,18 +18065,17 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K86" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L86" s="38" t="str">
-        <x:v>MTR2-B001-L2
-MTR2-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
-MTR2-B004-L2
-MTR2-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-L2</x:v>
+        <x:v>MTR1-B001-L2
+MTR1-B002-S06 — BAS-002, 6. Saída e uso downstream: Quando outputs forem exibidos, persistidos, usados em decisões ou encaminhados a sistemas downstream.
+MTR1-B004-L2
+MTR1-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-L2</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -18238,15 +18115,14 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K87" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L87" s="38" t="str">
-        <x:v>MTR2-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
-MTR2-B004-S04 — BAS-004, 4. Segurança de clientes, servidores e registries MCP: Quando houver cliente, servidor, registry, discovery, resource ou prompt MCP.
-MTR2-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
+        <x:v>MTR1-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
+MTR1-B004-S04 — BAS-004, 4. Segurança de clientes, servidores e registries MCP: Quando houver cliente, servidor, registry, discovery, resource ou prompt MCP.
+MTR1-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -18286,15 +18162,14 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K88" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L88" s="38" t="str">
-        <x:v>MTR2-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
-MTR2-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
-MTR2-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
+        <x:v>MTR1-B002-S05 — BAS-002, 5. Entrada, prompt e payload: Quando entradas, prompts, anexos, parâmetros ou conteúdo não confiável forem aceitos.
+MTR1-B004-S02 — BAS-004, 2. Registro, integridade e schemas de tools: Quando houver tools, functions, actions, skills, plugins, capabilities, resources ou prompts MCP.
+MTR1-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -18334,13 +18209,12 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K89" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L89" s="38" t="str">
-        <x:v>MTR2-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.</x:v>
+        <x:v>MTR1-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -18380,14 +18254,13 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K90" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L90" s="38" t="str">
-        <x:v>MTR2-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.
-MTR2-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
+        <x:v>MTR1-B004-S01 — BAS-004, 1. Identidades agentic e contexto de execução: Quando existir agente, worker, executor ou ação realizada em nome de usuário ou workload.
+MTR1-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -18427,14 +18300,13 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K91" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L91" s="38" t="str">
-        <x:v>MTR2-B004-L2
-MTR2-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.</x:v>
+        <x:v>MTR1-B004-L2
+MTR1-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -18474,15 +18346,14 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K92" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L92" s="38" t="str">
-        <x:v>MTR2-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-S06 — BAS-006, 6. Anomalias de comportamento, custo e desempenho: Quando volume, custo, tokens, loops, drift, falha, latência ou saturação precisarem ser monitorados.</x:v>
+        <x:v>MTR1-B004-S03 — BAS-004, 3. Autorização determinística e limites de ação: Quando o agente puder acessar recurso, tomar decisão ou produzir efeito em sistema externo.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-S06 — BAS-006, 6. Anomalias de comportamento, custo e desempenho: Quando volume, custo, tokens, loops, drift, falha, latência ou saturação precisarem ser monitorados.</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -18522,16 +18393,15 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K93" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L93" s="38" t="str">
-        <x:v>MTR2-B004-S04 — BAS-004, 4. Segurança de clientes, servidores e registries MCP: Quando houver cliente, servidor, registry, discovery, resource ou prompt MCP.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.
-MTR2-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
+        <x:v>MTR1-B004-S04 — BAS-004, 4. Segurança de clientes, servidores e registries MCP: Quando houver cliente, servidor, registry, discovery, resource ou prompt MCP.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.
+MTR1-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -18571,14 +18441,13 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K94" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L94" s="38" t="str">
-        <x:v>MTR2-B004-L2
-MTR2-B004-S06 — BAS-004, 6. Sandbox, host, navegador e computer use: Quando houver execução de código, terminal, navegador, desktop, IDE, endpoint ou computer use.</x:v>
+        <x:v>MTR1-B004-L2
+MTR1-B004-S06 — BAS-004, 6. Sandbox, host, navegador e computer use: Quando houver execução de código, terminal, navegador, desktop, IDE, endpoint ou computer use.</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -18618,15 +18487,14 @@
         <x:v>Registry de tools/MCP, schemas, políticas de autorização, limites, logs de ação, sandbox e teste de kill switch.</x:v>
       </x:c>
       <x:c r="K95" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 10. Agentes, tools, MCP e automações — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 8 — Impacto; § 9 — Probabilidade; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 10 — Regra individual de controle
 BAS-004 — Agentes, Ferramentas e Protocolos Agentic</x:v>
       </x:c>
       <x:c r="L95" s="38" t="str">
-        <x:v>MTR2-B003-S07 — BAS-003, 7. Memória, caches e dados derivados em execução: Quando houver memória persistente, cache semântico, estado conversacional ou compartilhamento de contexto.
-MTR2-B004-L2
-MTR2-B004-S07 — BAS-004, 7. Memória, delegação e comunicação entre agentes: Quando houver memória agentic, agentes secundários, delegação, comunicação multiagente ou contexto persistente.</x:v>
+        <x:v>MTR1-B003-S07 — BAS-003, 7. Memória, caches e dados derivados em execução: Quando houver memória persistente, cache semântico, estado conversacional ou compartilhamento de contexto.
+MTR1-B004-L2
+MTR1-B004-S07 — BAS-004, 7. Memória, delegação e comunicação entre agentes: Quando houver memória agentic, agentes secundários, delegação, comunicação multiagente ou contexto persistente.</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -18664,16 +18532,15 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K96" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L96" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.
-MTR2-B005-S01 — BAS-005, 1. Repositórios, código e versionamento: Quando código, notebook, prompt, policy, manifesto ou configuração for desenvolvido ou mantido para a solução.
-MTR2-B005-S05 — BAS-005, 5. Pipelines MLOps, LLMOps e ambientes de build: Quando houver pipeline de dados, treinamento, build, teste, promoção ou deploy.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005 — BAS-005: Desenvolvimento, treinamento, adaptação, empacotamento, registro, avaliação, implantação ou gestão de modelo e artefatos de IA.
+MTR1-B005-S01 — BAS-005, 1. Repositórios, código e versionamento: Quando código, notebook, prompt, policy, manifesto ou configuração for desenvolvido ou mantido para a solução.
+MTR1-B005-S05 — BAS-005, 5. Pipelines MLOps, LLMOps e ambientes de build: Quando houver pipeline de dados, treinamento, build, teste, promoção ou deploy.</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -18713,16 +18580,15 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K97" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L97" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.
-MTR2-B005-S01 — BAS-005, 1. Repositórios, código e versionamento: Quando código, notebook, prompt, policy, manifesto ou configuração for desenvolvido ou mantido para a solução.
-MTR2-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B003-S02 — BAS-003, 2. Transformação, parsing e metadados: Quando houver parsing, chunking, normalização, enriquecimento, OCR ou geração de derivados.
+MTR1-B005-S01 — BAS-005, 1. Repositórios, código e versionamento: Quando código, notebook, prompt, policy, manifesto ou configuração for desenvolvido ou mantido para a solução.
+MTR1-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -18762,14 +18628,13 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K98" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L98" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005-S02 — BAS-005, 2. Datasets, prompts e configurações de treinamento e avaliação: Quando houver treinamento, fine-tuning, avaliação, dataset, prompt sistêmico ou configuração de geração por release.</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -18809,14 +18674,13 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K99" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L99" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -18856,16 +18720,15 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K100" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L100" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005-L2
-MTR2-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.
-MTR2-B005-S04 — BAS-005, 4. Dependências, containers e proveniência: Quando builds utilizarem pacotes, containers, imagens, dependências ou artefatos externos.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005-L2
+MTR1-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.
+MTR1-B005-S04 — BAS-005, 4. Dependências, containers e proveniência: Quando builds utilizarem pacotes, containers, imagens, dependências ou artefatos externos.</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -18905,16 +18768,15 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K101" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L101" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005-L2
-MTR2-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.
-MTR2-B005-S04 — BAS-005, 4. Dependências, containers e proveniência: Quando builds utilizarem pacotes, containers, imagens, dependências ou artefatos externos.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005-L2
+MTR1-B005-S03 — BAS-005, 3. Modelos, artefatos e registries: Quando modelos, weights, checkpoints, adapters, tokenizers ou bundles forem registrados, carregados ou distribuídos.
+MTR1-B005-S04 — BAS-005, 4. Dependências, containers e proveniência: Quando builds utilizarem pacotes, containers, imagens, dependências ou artefatos externos.</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -18954,15 +18816,14 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K102" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L102" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B005-L2
-MTR2-B005-S04 — BAS-005, 4. Dependências, containers e proveniência: Quando builds utilizarem pacotes, containers, imagens, dependências ou artefatos externos.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B005-L2
+MTR1-B005-S04 — BAS-005, 4. Dependências, containers e proveniência: Quando builds utilizarem pacotes, containers, imagens, dependências ou artefatos externos.</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -19002,14 +18863,13 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K103" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L103" s="38" t="str">
-        <x:v>MTR2-B005-L2
-MTR2-B005-S05 — BAS-005, 5. Pipelines MLOps, LLMOps e ambientes de build: Quando houver pipeline de dados, treinamento, build, teste, promoção ou deploy.</x:v>
+        <x:v>MTR1-B005-L2
+MTR1-B005-S05 — BAS-005, 5. Pipelines MLOps, LLMOps e ambientes de build: Quando houver pipeline de dados, treinamento, build, teste, promoção ou deploy.</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -19049,14 +18909,13 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K104" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L104" s="38" t="str">
-        <x:v>MTR2-B005-S05 — BAS-005, 5. Pipelines MLOps, LLMOps e ambientes de build: Quando houver pipeline de dados, treinamento, build, teste, promoção ou deploy.
-MTR2-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.</x:v>
+        <x:v>MTR1-B005-S05 — BAS-005, 5. Pipelines MLOps, LLMOps e ambientes de build: Quando houver pipeline de dados, treinamento, build, teste, promoção ou deploy.
+MTR1-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -19096,14 +18955,13 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K105" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L105" s="38" t="str">
-        <x:v>MTR2-B005-L2
-MTR2-B005-S06 — BAS-005, 6. Testes, evals e critérios técnicos de release: Quando releases, modelos, prompts ou soluções forem avaliados antes da promoção ou contratação.</x:v>
+        <x:v>MTR1-B005-L2
+MTR1-B005-S06 — BAS-005, 6. Testes, evals e critérios técnicos de release: Quando releases, modelos, prompts ou soluções forem avaliados antes da promoção ou contratação.</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -19143,15 +19001,14 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K106" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L106" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -19191,15 +19048,14 @@
         <x:v>Repositório, commits, hashes, SBOM/AI BOM, registry, pipeline, evals, assinatura e teste de rollback.</x:v>
       </x:c>
       <x:c r="K107" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 11. Desenvolvimento, modelos e MLOps — preencher quando aplicável
-MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 7 — Classificação H1–H4; § 9 — Probabilidade; § 11 — Seleção dos controles
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.5 — BAS-005: desenvolvimento e MLOps; § 10 — Regra individual de controle
 BAS-005 — Desenvolvimento, Versionamento, MLOps e Cadeia de Suprimentos</x:v>
       </x:c>
       <x:c r="L107" s="38" t="str">
-        <x:v>MTR2-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
-MTR2-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.
-MTR2-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.</x:v>
+        <x:v>MTR1-B001-S04 — BAS-001, 4. Modelos, runtime e cadeia de fornecimento: Quando houver modelo, runtime, container, dependência, provider, artefato ou atualização técnica.
+MTR1-B002-S04 — BAS-002, 4. Roteamento, modelos e policies: Quando houver escolha de provider/modelo, aliases, rotas, fallback ou policies de gateway.
+MTR1-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -19239,16 +19095,15 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K108" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L108" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
-MTR2-B006-S01 — BAS-006, 1. Geração de eventos e integridade temporal: Quando execuções, decisões, erros ou bloqueios precisarem produzir eventos auditáveis.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
+MTR1-B006-S01 — BAS-006, 1. Geração de eventos e integridade temporal: Quando execuções, decisões, erros ou bloqueios precisarem produzir eventos auditáveis.</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -19288,15 +19143,14 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K109" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L109" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-S01 — BAS-006, 1. Geração de eventos e integridade temporal: Quando execuções, decisões, erros ou bloqueios precisarem produzir eventos auditáveis.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-S01 — BAS-006, 1. Geração de eventos e integridade temporal: Quando execuções, decisões, erros ou bloqueios precisarem produzir eventos auditáveis.</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -19336,15 +19190,14 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K110" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L110" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-S02 — BAS-006, 2. Correlação e contexto ponta a ponta: Quando o fluxo atravessar aplicação, gateway, provider, RAG, agente, tool, fila ou sistema downstream.</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -19384,16 +19237,15 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K111" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L111" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -19433,16 +19285,15 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K112" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L112" s="38" t="str">
-        <x:v>MTR2-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
-MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.</x:v>
+        <x:v>MTR1-B001-S03 — BAS-001, 3. Proteção de dados, prompts e outputs: Quando a solução processar, armazenar, transmitir ou produzir dados, prompts, anexos, contexto ou outputs.
+MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -19482,18 +19333,17 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K113" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L113" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
-MTR2-B006-L2
-MTR2-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.
-MTR2-B006-S04 — BAS-006, 4. Coleta, transporte e integração com SIEM: Quando eventos forem enviados a collector, broker, data lake, APM, SIEM ou SOC.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
+MTR1-B006-L2
+MTR1-B006-S03 — BAS-006, 3. Proteção, minimização e integridade dos registros: Quando logs, traces, prompts, outputs ou eventos contiverem informação sensível ou evidência crítica.
+MTR1-B006-S04 — BAS-006, 4. Coleta, transporte e integração com SIEM: Quando eventos forem enviados a collector, broker, data lake, APM, SIEM ou SOC.</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -19533,20 +19383,19 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K114" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L114" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.
-MTR2-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B005-S06 — BAS-005, 6. Testes, evals e critérios técnicos de release: Quando releases, modelos, prompts ou soluções forem avaliados antes da promoção ou contratação.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
-MTR2-B006-L2
-MTR2-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B003-S06 — BAS-003, 6. Proteção contra poisoning e conteúdo adversarial: Quando fontes externas, uploads ou conteúdo não confiável puderem influenciar ingestão ou recuperação.
+MTR1-B004-S05 — BAS-004, 5. Proteção contra instruções e capabilities adversariais: Quando conteúdo não confiável puder influenciar planejamento, seleção de tool, capability ou instrução do agente.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B005-S06 — BAS-005, 6. Testes, evals e critérios técnicos de release: Quando releases, modelos, prompts ou soluções forem avaliados antes da promoção ou contratação.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
+MTR1-B006-L2
+MTR1-B006-S05 — BAS-006, 5. Detecções técnicas de segurança para IA: Quando forem necessárias detecções de vazamento, prompt injection, abuso agentic, poisoning, shadow AI ou MCP desconhecido.</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -19586,17 +19435,16 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K115" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L115" s="38" t="str">
-        <x:v>MTR2-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
-MTR2-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.
-MTR2-B006-S06 — BAS-006, 6. Anomalias de comportamento, custo e desempenho: Quando volume, custo, tokens, loops, drift, falha, latência ou saturação precisarem ser monitorados.</x:v>
+        <x:v>MTR1-B001-S06 — BAS-001, 6. Logging, auditoria e monitoramento: Quando a solução estiver em teste material, homologação, produção ou processar dados relevantes.
+MTR1-B002-S07 — BAS-002, 7. Exposição, sessão e abuso: Quando houver Internet, clientes, público, muitos usuários, sessão, streaming, custo ou risco de abuso.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B005-S07 — BAS-005, 7. Deploy, serving e mudança técnica: Quando houver deployment, endpoint, serving, atualização, reconciliação ou mudança de versão/configuração.
+MTR1-B006-S06 — BAS-006, 6. Anomalias de comportamento, custo e desempenho: Quando volume, custo, tokens, loops, drift, falha, latência ou saturação precisarem ser monitorados.</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -19636,18 +19484,17 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K116" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.2 — BAS-002: integração e exposição; § 9.4 — BAS-004: agentes, ferramentas e MCP; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L116" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
-MTR2-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
-MTR2-B006-L2
-MTR2-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B002-S08 — BAS-002, 8. Resiliência e comportamento de falha: Quando a integração exigir timeout, retry, fallback, circuit breaker, fail-closed ou continuidade.
+MTR1-B004-S08 — BAS-004, 8. Observabilidade agentic e comportamento fail-safe: Quando ações agentic exigirem logs, correlação, detecção, kill switch, limites e comportamento seguro.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
+MTR1-B006-L2
+MTR1-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -19687,17 +19534,16 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K117" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.3 — BAS-003: dados, contexto e conhecimento; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L117" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.
-MTR2-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
-MTR2-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B003-S08 — BAS-003, 8. Retenção, exclusão, sincronização e recuperação: Quando dados, índices, embeddings, memória ou derivados forem persistidos e precisarem ser excluídos ou restaurados.
+MTR1-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
+MTR1-B006 — BAS-006: Solução em homologação material, produção, operação existente ou que exija telemetria, detecção, contenção, continuidade ou recuperação.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -19735,14 +19581,13 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K118" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L118" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -19782,15 +19627,14 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K119" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L119" s="38" t="str">
-        <x:v>MTR2-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
-MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
+        <x:v>MTR1-B001-S02 — BAS-001, 2. Identidade, acesso e segredos: Quando houver usuário, workload, conta administrativa, credencial, segredo ou acesso a recurso de IA.
+MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B006-S07 — BAS-006, 7. Contenção técnica e comportamento seguro: Quando a solução exigir kill switch, bloqueio individual, circuit breaker, retries limitados, revogação ou fallback seguro.</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -19830,15 +19674,14 @@
         <x:v>Eventos, traces, dashboards, regras SIEM, alertas, teste de falha, backup, restore e evidência de desativação.</x:v>
       </x:c>
       <x:c r="K120" s="38" t="str">
-        <x:v>FRM-002 v1.0 — 12. Telemetria, detecção, continuidade e resposta
-MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
-MTR-002 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
+        <x:v>MET-001 v1.1 — § 11 — Seleção dos controles; § 12 — Avaliação dos controles; § 13 — Risco residual; § 14 — Condições bloqueantes
+MTR-001 v1.0 — § 9.1 — BAS-001: controles transversais; § 9.5 — BAS-005: desenvolvimento e MLOps; § 9.6 — BAS-006: telemetria, detecção e resiliência; § 10 — Regra individual de controle
 BAS-006 — Telemetria, Detecção e Resiliência</x:v>
       </x:c>
       <x:c r="L120" s="38" t="str">
-        <x:v>MTR2-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
-MTR2-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
-MTR2-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
+        <x:v>MTR1-B001-S07 — BAS-001, 7. Resiliência e recuperação: Quando houver dependência operacional, serviço produtivo, ação material ou necessidade de recuperação e desativação.
+MTR1-B005-S08 — BAS-005, 8. Rollback, descontinuação e descarte técnico: Quando a solução precisar retornar versão, retirar modelo, revogar acesso, eliminar caches ou impedir reativação.
+MTR1-B006-S08 — BAS-006, 8. Recuperação, continuidade e desativação técnica: Quando houver requisito de backup, restauração, redundância, recuperação, plano de saída ou desativação segura.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
